--- a/output7/【河洛白話注音-閩拼調符】《秋離》.xlsx
+++ b/output7/【河洛白話注音-閩拼調符】《秋離》.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\work\Piau-Im\output7\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3612C6E-18F2-4D03-BECC-F6CB5214446E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{014A3801-C3E3-480C-9C3E-AA8DEE415042}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="1335" windowWidth="27735" windowHeight="13035" tabRatio="689" activeTab="4" xr2:uid="{25A76161-EFED-4AC8-8EAA-A42737AE1909}"/>
+    <workbookView xWindow="-28920" yWindow="-15" windowWidth="29040" windowHeight="15720" tabRatio="689" activeTab="4" xr2:uid="{25A76161-EFED-4AC8-8EAA-A42737AE1909}"/>
   </bookViews>
   <sheets>
     <sheet name="env" sheetId="8" r:id="rId1"/>
@@ -62,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1978" uniqueCount="769">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1978" uniqueCount="773">
   <si>
     <t>Key</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -1210,10 +1210,6 @@
   </si>
   <si>
     <t>上及右</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Tai_Gi_Zu_Im_Bun.xlsx</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -2692,6 +2688,26 @@
   </si>
   <si>
     <t>huē</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>漢字</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>台語音標</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>校正音標</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>座標</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>【河洛白話注音-閩拼調符】《秋離》.xlsx</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -3101,7 +3117,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="59">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3273,13 +3289,7 @@
     <xf numFmtId="0" fontId="17" fillId="2" borderId="5" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" shrinkToFit="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="3" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
@@ -3293,31 +3303,7 @@
     <cellStyle name="超連結" xfId="4" builtinId="8"/>
     <cellStyle name="超連結 2" xfId="2" xr:uid="{35CF4CF4-6C05-4C83-A404-416353358D27}"/>
   </cellStyles>
-  <dxfs count="72">
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="70">
     <dxf>
       <font>
         <b/>
@@ -4510,7 +4496,7 @@
     </row>
     <row r="2" spans="2:11">
       <c r="B2" s="4" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C2" s="53">
         <v>1</v>
@@ -4527,7 +4513,7 @@
         <v>3</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>367</v>
+        <v>772</v>
       </c>
     </row>
     <row r="5" spans="2:11">
@@ -4535,7 +4521,7 @@
         <v>4</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
     </row>
     <row r="6" spans="2:11">
@@ -4543,7 +4529,7 @@
         <v>5</v>
       </c>
       <c r="C6" s="50" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="D6" s="51"/>
       <c r="E6" s="51"/>
@@ -4559,7 +4545,7 @@
         <v>6</v>
       </c>
       <c r="C7" s="48" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="8" spans="2:11" ht="30">
@@ -4567,7 +4553,7 @@
         <v>7</v>
       </c>
       <c r="C8" s="47" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="9" spans="2:11">
@@ -4599,7 +4585,7 @@
         <v>11</v>
       </c>
       <c r="C12" s="46" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
     </row>
     <row r="13" spans="2:11" ht="30">
@@ -4607,7 +4593,7 @@
         <v>12</v>
       </c>
       <c r="C13" s="46" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="14" spans="2:11" ht="30">
@@ -4615,7 +4601,7 @@
         <v>13</v>
       </c>
       <c r="C14" s="46" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="15" spans="2:11" ht="30">
@@ -4639,7 +4625,7 @@
         <v>16</v>
       </c>
       <c r="C17" s="46" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="30">
@@ -4647,7 +4633,7 @@
         <v>17</v>
       </c>
       <c r="C18" s="46" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="19" spans="2:3" ht="30">
@@ -4691,16 +4677,16 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" t="s">
-        <v>28</v>
+        <v>768</v>
       </c>
       <c r="B1" t="s">
-        <v>29</v>
+        <v>769</v>
       </c>
       <c r="C1" t="s">
-        <v>36</v>
+        <v>770</v>
       </c>
       <c r="D1" t="s">
-        <v>103</v>
+        <v>771</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -4708,13 +4694,13 @@
         <v>312</v>
       </c>
       <c r="B2" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C2" t="s">
         <v>104</v>
       </c>
       <c r="D2" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -4728,7 +4714,7 @@
         <v>104</v>
       </c>
       <c r="D3" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -4742,7 +4728,7 @@
         <v>104</v>
       </c>
       <c r="D4" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -4756,7 +4742,7 @@
         <v>104</v>
       </c>
       <c r="D5" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -4770,7 +4756,7 @@
         <v>104</v>
       </c>
       <c r="D6" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -4798,7 +4784,7 @@
         <v>263</v>
       </c>
       <c r="D8" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -4812,7 +4798,7 @@
         <v>79</v>
       </c>
       <c r="D9" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -4826,7 +4812,7 @@
         <v>104</v>
       </c>
       <c r="D10" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -4840,12 +4826,12 @@
         <v>104</v>
       </c>
       <c r="D11" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B12" t="s">
         <v>285</v>
@@ -4854,7 +4840,7 @@
         <v>104</v>
       </c>
       <c r="D12" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -4882,7 +4868,7 @@
         <v>104</v>
       </c>
       <c r="D14" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -4896,7 +4882,7 @@
         <v>104</v>
       </c>
       <c r="D15" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -4910,7 +4896,7 @@
         <v>104</v>
       </c>
       <c r="D16" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -4924,7 +4910,7 @@
         <v>104</v>
       </c>
       <c r="D17" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -4938,7 +4924,7 @@
         <v>181</v>
       </c>
       <c r="D18" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -4960,13 +4946,13 @@
         <v>185</v>
       </c>
       <c r="B20" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="C20" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="D20" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -5008,7 +4994,7 @@
         <v>104</v>
       </c>
       <c r="D23" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -5022,7 +5008,7 @@
         <v>104</v>
       </c>
       <c r="D24" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -5036,7 +5022,7 @@
         <v>271</v>
       </c>
       <c r="D25" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -5050,7 +5036,7 @@
         <v>104</v>
       </c>
       <c r="D26" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -5064,7 +5050,7 @@
         <v>104</v>
       </c>
       <c r="D27" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -5089,10 +5075,10 @@
         <v>299</v>
       </c>
       <c r="C29" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="D29" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -5106,7 +5092,7 @@
         <v>104</v>
       </c>
       <c r="D30" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -5120,7 +5106,7 @@
         <v>104</v>
       </c>
       <c r="D31" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -5131,10 +5117,10 @@
         <v>277</v>
       </c>
       <c r="C32" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="D32" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -5148,7 +5134,7 @@
         <v>104</v>
       </c>
       <c r="D33" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -5162,7 +5148,7 @@
         <v>104</v>
       </c>
       <c r="D34" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -5176,7 +5162,7 @@
         <v>216</v>
       </c>
       <c r="D35" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -5190,7 +5176,7 @@
         <v>341</v>
       </c>
       <c r="D36" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -5204,7 +5190,7 @@
         <v>104</v>
       </c>
       <c r="D37" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -5218,7 +5204,7 @@
         <v>104</v>
       </c>
       <c r="D38" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -5232,7 +5218,7 @@
         <v>104</v>
       </c>
       <c r="D39" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -5240,13 +5226,13 @@
         <v>330</v>
       </c>
       <c r="B40" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="C40" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="D40" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -5260,7 +5246,7 @@
         <v>104</v>
       </c>
       <c r="D41" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -5268,13 +5254,13 @@
         <v>22</v>
       </c>
       <c r="B42" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="C42" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="D42" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -5288,7 +5274,7 @@
         <v>104</v>
       </c>
       <c r="D43" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -5296,13 +5282,13 @@
         <v>264</v>
       </c>
       <c r="B44" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C44" t="s">
         <v>104</v>
       </c>
       <c r="D44" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -5316,7 +5302,7 @@
         <v>104</v>
       </c>
       <c r="D45" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -5324,13 +5310,13 @@
         <v>328</v>
       </c>
       <c r="B46" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C46" t="s">
         <v>104</v>
       </c>
       <c r="D46" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -5344,7 +5330,7 @@
         <v>305</v>
       </c>
       <c r="D47" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -5358,7 +5344,7 @@
         <v>219</v>
       </c>
       <c r="D48" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -5372,7 +5358,7 @@
         <v>191</v>
       </c>
       <c r="D49" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -5386,7 +5372,7 @@
         <v>104</v>
       </c>
       <c r="D50" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -5400,7 +5386,7 @@
         <v>104</v>
       </c>
       <c r="D51" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -5414,7 +5400,7 @@
         <v>104</v>
       </c>
       <c r="D52" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -5422,13 +5408,13 @@
         <v>350</v>
       </c>
       <c r="B53" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="C53" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="D53" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -5442,7 +5428,7 @@
         <v>104</v>
       </c>
       <c r="D54" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -5456,7 +5442,7 @@
         <v>104</v>
       </c>
       <c r="D55" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -5498,7 +5484,7 @@
         <v>256</v>
       </c>
       <c r="D58" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -5512,7 +5498,7 @@
         <v>273</v>
       </c>
       <c r="D59" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -5526,7 +5512,7 @@
         <v>104</v>
       </c>
       <c r="D60" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -5540,7 +5526,7 @@
         <v>104</v>
       </c>
       <c r="D61" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -5554,7 +5540,7 @@
         <v>104</v>
       </c>
       <c r="D62" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -5568,7 +5554,7 @@
         <v>104</v>
       </c>
       <c r="D63" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -5582,7 +5568,7 @@
         <v>104</v>
       </c>
       <c r="D64" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -5596,7 +5582,7 @@
         <v>104</v>
       </c>
       <c r="D65" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -5610,7 +5596,7 @@
         <v>104</v>
       </c>
       <c r="D66" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -5624,7 +5610,7 @@
         <v>104</v>
       </c>
       <c r="D67" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -5632,13 +5618,13 @@
         <v>322</v>
       </c>
       <c r="B68" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="C68" t="s">
         <v>104</v>
       </c>
       <c r="D68" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -5652,7 +5638,7 @@
         <v>104</v>
       </c>
       <c r="D69" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -5666,7 +5652,7 @@
         <v>104</v>
       </c>
       <c r="D70" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -5680,7 +5666,7 @@
         <v>104</v>
       </c>
       <c r="D71" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -5688,13 +5674,13 @@
         <v>347</v>
       </c>
       <c r="B72" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C72" t="s">
         <v>104</v>
       </c>
       <c r="D72" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -5708,7 +5694,7 @@
         <v>104</v>
       </c>
       <c r="D73" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -5722,7 +5708,7 @@
         <v>104</v>
       </c>
       <c r="D74" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -5736,7 +5722,7 @@
         <v>104</v>
       </c>
       <c r="D75" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -5750,7 +5736,7 @@
         <v>104</v>
       </c>
       <c r="D76" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -5764,7 +5750,7 @@
         <v>104</v>
       </c>
       <c r="D77" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -5778,7 +5764,7 @@
         <v>104</v>
       </c>
       <c r="D78" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -5792,7 +5778,7 @@
         <v>104</v>
       </c>
       <c r="D79" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -5806,7 +5792,7 @@
         <v>104</v>
       </c>
       <c r="D80" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -5820,7 +5806,7 @@
         <v>104</v>
       </c>
       <c r="D81" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -5834,7 +5820,7 @@
         <v>104</v>
       </c>
       <c r="D82" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -5848,7 +5834,7 @@
         <v>104</v>
       </c>
       <c r="D83" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -5862,7 +5848,7 @@
         <v>104</v>
       </c>
       <c r="D84" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -5876,7 +5862,7 @@
         <v>104</v>
       </c>
       <c r="D85" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -5890,7 +5876,7 @@
         <v>104</v>
       </c>
       <c r="D86" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -5904,7 +5890,7 @@
         <v>104</v>
       </c>
       <c r="D87" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -5918,7 +5904,7 @@
         <v>104</v>
       </c>
       <c r="D88" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -5932,7 +5918,7 @@
         <v>104</v>
       </c>
       <c r="D89" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -5946,7 +5932,7 @@
         <v>104</v>
       </c>
       <c r="D90" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -5960,7 +5946,7 @@
         <v>104</v>
       </c>
       <c r="D91" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -5974,7 +5960,7 @@
         <v>104</v>
       </c>
       <c r="D92" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -5988,7 +5974,7 @@
         <v>104</v>
       </c>
       <c r="D93" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -6002,7 +5988,7 @@
         <v>104</v>
       </c>
       <c r="D94" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -6016,7 +6002,7 @@
         <v>104</v>
       </c>
       <c r="D95" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -6030,7 +6016,7 @@
         <v>104</v>
       </c>
       <c r="D96" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -6044,7 +6030,7 @@
         <v>104</v>
       </c>
       <c r="D97" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -6058,7 +6044,7 @@
         <v>104</v>
       </c>
       <c r="D98" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -6072,7 +6058,7 @@
         <v>104</v>
       </c>
       <c r="D99" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -6080,13 +6066,13 @@
         <v>163</v>
       </c>
       <c r="B100" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="C100" t="s">
         <v>104</v>
       </c>
       <c r="D100" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -6100,7 +6086,7 @@
         <v>104</v>
       </c>
       <c r="D101" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -6108,13 +6094,13 @@
         <v>288</v>
       </c>
       <c r="B102" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="C102" t="s">
         <v>104</v>
       </c>
       <c r="D102" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -6128,7 +6114,7 @@
         <v>104</v>
       </c>
       <c r="D103" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -6136,13 +6122,13 @@
         <v>169</v>
       </c>
       <c r="B104" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="C104" t="s">
         <v>104</v>
       </c>
       <c r="D104" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -6156,7 +6142,7 @@
         <v>104</v>
       </c>
       <c r="D105" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -6170,7 +6156,7 @@
         <v>104</v>
       </c>
       <c r="D106" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -6184,7 +6170,7 @@
         <v>104</v>
       </c>
       <c r="D107" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -6198,7 +6184,7 @@
         <v>104</v>
       </c>
       <c r="D108" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -6212,7 +6198,7 @@
         <v>104</v>
       </c>
       <c r="D109" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -6226,7 +6212,7 @@
         <v>104</v>
       </c>
       <c r="D110" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -6240,7 +6226,7 @@
         <v>104</v>
       </c>
       <c r="D111" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -6254,7 +6240,7 @@
         <v>104</v>
       </c>
       <c r="D112" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -6268,7 +6254,7 @@
         <v>104</v>
       </c>
       <c r="D113" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -6282,7 +6268,7 @@
         <v>104</v>
       </c>
       <c r="D114" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -6296,7 +6282,7 @@
         <v>104</v>
       </c>
       <c r="D115" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -6310,7 +6296,7 @@
         <v>104</v>
       </c>
       <c r="D116" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -6324,7 +6310,7 @@
         <v>104</v>
       </c>
       <c r="D117" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -6338,7 +6324,7 @@
         <v>104</v>
       </c>
       <c r="D118" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -6352,7 +6338,7 @@
         <v>104</v>
       </c>
       <c r="D119" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -6374,13 +6360,13 @@
         <v>274</v>
       </c>
       <c r="B121" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="C121" t="s">
         <v>104</v>
       </c>
       <c r="D121" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -6394,7 +6380,7 @@
         <v>104</v>
       </c>
       <c r="D122" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -6408,7 +6394,7 @@
         <v>104</v>
       </c>
       <c r="D123" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -6422,7 +6408,7 @@
         <v>104</v>
       </c>
       <c r="D124" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -6436,7 +6422,7 @@
         <v>104</v>
       </c>
       <c r="D125" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -6450,7 +6436,7 @@
         <v>104</v>
       </c>
       <c r="D126" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -6464,7 +6450,7 @@
         <v>104</v>
       </c>
       <c r="D127" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -6492,7 +6478,7 @@
         <v>104</v>
       </c>
       <c r="D129" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -6506,7 +6492,7 @@
         <v>104</v>
       </c>
       <c r="D130" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -6514,7 +6500,7 @@
         <v>342</v>
       </c>
       <c r="B131" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="C131" t="s">
         <v>104</v>
@@ -6542,7 +6528,7 @@
         <v>213</v>
       </c>
       <c r="B133" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="C133" t="s">
         <v>104</v>
@@ -6562,7 +6548,7 @@
         <v>104</v>
       </c>
       <c r="D134" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -6576,7 +6562,7 @@
         <v>104</v>
       </c>
       <c r="D135" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -6584,13 +6570,13 @@
         <v>351</v>
       </c>
       <c r="B136" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C136" t="s">
         <v>104</v>
       </c>
       <c r="D136" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -6618,7 +6604,7 @@
         <v>104</v>
       </c>
       <c r="D138" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -6632,7 +6618,7 @@
         <v>104</v>
       </c>
       <c r="D139" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -6646,7 +6632,7 @@
         <v>104</v>
       </c>
       <c r="D140" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -6660,7 +6646,7 @@
         <v>104</v>
       </c>
       <c r="D141" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -6674,7 +6660,7 @@
         <v>104</v>
       </c>
       <c r="D142" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -6688,7 +6674,7 @@
         <v>104</v>
       </c>
       <c r="D143" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -6730,7 +6716,7 @@
         <v>104</v>
       </c>
       <c r="D146" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -6744,7 +6730,7 @@
         <v>104</v>
       </c>
       <c r="D147" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -6758,7 +6744,7 @@
         <v>104</v>
       </c>
       <c r="D148" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -6766,13 +6752,13 @@
         <v>196</v>
       </c>
       <c r="B149" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="C149" t="s">
         <v>104</v>
       </c>
       <c r="D149" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -6786,7 +6772,7 @@
         <v>104</v>
       </c>
       <c r="D150" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -6800,7 +6786,7 @@
         <v>104</v>
       </c>
       <c r="D151" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -6814,7 +6800,7 @@
         <v>104</v>
       </c>
       <c r="D152" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -6842,7 +6828,7 @@
         <v>104</v>
       </c>
       <c r="D154" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -6856,12 +6842,12 @@
         <v>104</v>
       </c>
       <c r="D155" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="156" spans="1:4">
       <c r="A156" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="B156" t="s">
         <v>348</v>
@@ -6870,7 +6856,7 @@
         <v>104</v>
       </c>
       <c r="D156" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
     </row>
   </sheetData>
@@ -6886,21 +6872,21 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" t="s">
-        <v>28</v>
+        <v>768</v>
       </c>
       <c r="B1" t="s">
-        <v>29</v>
+        <v>769</v>
       </c>
       <c r="C1" t="s">
-        <v>36</v>
+        <v>770</v>
       </c>
       <c r="D1" t="s">
-        <v>103</v>
+        <v>771</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="B2" t="s">
         <v>348</v>
@@ -6909,7 +6895,7 @@
         <v>348</v>
       </c>
       <c r="D2" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
     </row>
   </sheetData>
@@ -6925,16 +6911,16 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" t="s">
-        <v>28</v>
+        <v>768</v>
       </c>
       <c r="B1" t="s">
-        <v>29</v>
+        <v>769</v>
       </c>
       <c r="C1" t="s">
-        <v>36</v>
+        <v>770</v>
       </c>
       <c r="D1" t="s">
-        <v>103</v>
+        <v>771</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -6962,7 +6948,7 @@
         <v>104</v>
       </c>
       <c r="D3" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -6976,7 +6962,7 @@
         <v>104</v>
       </c>
       <c r="D4" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -6990,7 +6976,7 @@
         <v>104</v>
       </c>
       <c r="D5" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -6998,13 +6984,13 @@
         <v>185</v>
       </c>
       <c r="B6" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="C6" t="s">
         <v>104</v>
       </c>
       <c r="D6" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -7032,7 +7018,7 @@
         <v>104</v>
       </c>
       <c r="D8" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -7060,7 +7046,7 @@
         <v>104</v>
       </c>
       <c r="D10" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -7074,7 +7060,7 @@
         <v>104</v>
       </c>
       <c r="D11" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -7088,7 +7074,7 @@
         <v>104</v>
       </c>
       <c r="D12" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -7102,7 +7088,7 @@
         <v>104</v>
       </c>
       <c r="D13" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -7116,7 +7102,7 @@
         <v>104</v>
       </c>
       <c r="D14" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -7124,13 +7110,13 @@
         <v>330</v>
       </c>
       <c r="B15" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="C15" t="s">
         <v>104</v>
       </c>
       <c r="D15" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -7138,13 +7124,13 @@
         <v>22</v>
       </c>
       <c r="B16" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="C16" t="s">
         <v>104</v>
       </c>
       <c r="D16" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -7158,7 +7144,7 @@
         <v>104</v>
       </c>
       <c r="D17" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -7172,7 +7158,7 @@
         <v>104</v>
       </c>
       <c r="D18" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -7186,7 +7172,7 @@
         <v>104</v>
       </c>
       <c r="D19" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -7200,7 +7186,7 @@
         <v>104</v>
       </c>
       <c r="D20" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -7208,13 +7194,13 @@
         <v>350</v>
       </c>
       <c r="B21" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="C21" t="s">
         <v>104</v>
       </c>
       <c r="D21" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -7242,7 +7228,7 @@
         <v>104</v>
       </c>
       <c r="D23" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -7256,7 +7242,7 @@
         <v>104</v>
       </c>
       <c r="D24" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -7270,7 +7256,7 @@
         <v>104</v>
       </c>
       <c r="D25" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -7278,13 +7264,13 @@
         <v>322</v>
       </c>
       <c r="B26" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="C26" t="s">
         <v>104</v>
       </c>
       <c r="D26" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -7298,7 +7284,7 @@
         <v>104</v>
       </c>
       <c r="D27" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -7312,12 +7298,12 @@
         <v>104</v>
       </c>
       <c r="D28" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
     </row>
     <row r="29" spans="1:4">
       <c r="A29" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="B29" t="s">
         <v>348</v>
@@ -7326,7 +7312,7 @@
         <v>104</v>
       </c>
       <c r="D29" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -7340,7 +7326,7 @@
         <v>104</v>
       </c>
       <c r="D30" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -7368,7 +7354,7 @@
         <v>104</v>
       </c>
       <c r="D32" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -7382,7 +7368,7 @@
         <v>104</v>
       </c>
       <c r="D33" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -7396,7 +7382,7 @@
         <v>104</v>
       </c>
       <c r="D34" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -7410,7 +7396,7 @@
         <v>104</v>
       </c>
       <c r="D35" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -7424,7 +7410,7 @@
         <v>104</v>
       </c>
       <c r="D36" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -7438,7 +7424,7 @@
         <v>104</v>
       </c>
       <c r="D37" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -7446,13 +7432,13 @@
         <v>288</v>
       </c>
       <c r="B38" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="C38" t="s">
         <v>104</v>
       </c>
       <c r="D38" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -7480,7 +7466,7 @@
         <v>104</v>
       </c>
       <c r="D40" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -7494,7 +7480,7 @@
         <v>104</v>
       </c>
       <c r="D41" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -7502,7 +7488,7 @@
         <v>213</v>
       </c>
       <c r="B42" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="C42" t="s">
         <v>104</v>
@@ -7522,7 +7508,7 @@
         <v>104</v>
       </c>
       <c r="D43" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -7536,7 +7522,7 @@
         <v>104</v>
       </c>
       <c r="D44" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -7550,7 +7536,7 @@
         <v>104</v>
       </c>
       <c r="D45" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
     </row>
   </sheetData>
@@ -7692,20 +7678,20 @@
       <c r="R3" s="52"/>
       <c r="T3" s="16"/>
       <c r="V3" s="54" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="4" spans="1:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B4" s="17"/>
-      <c r="D4" s="60"/>
-      <c r="E4" s="60" t="s">
-        <v>501</v>
-      </c>
-      <c r="F4" s="60" t="s">
-        <v>503</v>
-      </c>
-      <c r="G4" s="60"/>
-      <c r="H4" s="60"/>
+      <c r="D4" s="58"/>
+      <c r="E4" s="58" t="s">
+        <v>500</v>
+      </c>
+      <c r="F4" s="58" t="s">
+        <v>502</v>
+      </c>
+      <c r="G4" s="58"/>
+      <c r="H4" s="58"/>
       <c r="I4" s="18"/>
       <c r="J4" s="18"/>
       <c r="K4" s="18"/>
@@ -7723,19 +7709,19 @@
       <c r="B5" s="20">
         <v>1</v>
       </c>
-      <c r="D5" s="57" t="s">
+      <c r="D5" s="41" t="s">
         <v>358</v>
       </c>
-      <c r="E5" s="57" t="s">
+      <c r="E5" s="41" t="s">
         <v>312</v>
       </c>
-      <c r="F5" s="57" t="s">
+      <c r="F5" s="41" t="s">
         <v>352</v>
       </c>
-      <c r="G5" s="57" t="s">
+      <c r="G5" s="41" t="s">
         <v>359</v>
       </c>
-      <c r="H5" s="57" t="str">
+      <c r="H5" s="41" t="str">
         <f>CHAR(10)</f>
         <v xml:space="preserve">
 </v>
@@ -7758,10 +7744,10 @@
       <c r="C6" s="23"/>
       <c r="D6" s="24"/>
       <c r="E6" s="24" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="F6" s="24" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="G6" s="24"/>
       <c r="H6" s="24"/>
@@ -7786,11 +7772,11 @@
       <c r="F7" s="52"/>
       <c r="G7" s="52"/>
       <c r="H7" s="52" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="I7" s="52"/>
       <c r="J7" s="52" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="K7" s="52"/>
       <c r="L7" s="52" t="s">
@@ -7807,34 +7793,34 @@
     </row>
     <row r="8" spans="1:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B8" s="17"/>
-      <c r="D8" s="60" t="s">
-        <v>505</v>
-      </c>
-      <c r="E8" s="60" t="s">
-        <v>507</v>
-      </c>
-      <c r="F8" s="60" t="s">
-        <v>505</v>
-      </c>
-      <c r="G8" s="60" t="s">
-        <v>509</v>
-      </c>
-      <c r="H8" s="60" t="s">
+      <c r="D8" s="58" t="s">
+        <v>504</v>
+      </c>
+      <c r="E8" s="58" t="s">
+        <v>506</v>
+      </c>
+      <c r="F8" s="58" t="s">
+        <v>504</v>
+      </c>
+      <c r="G8" s="58" t="s">
+        <v>508</v>
+      </c>
+      <c r="H8" s="58" t="s">
+        <v>656</v>
+      </c>
+      <c r="I8" s="58" t="s">
+        <v>500</v>
+      </c>
+      <c r="J8" s="58" t="s">
         <v>657</v>
       </c>
-      <c r="I8" s="60" t="s">
-        <v>501</v>
-      </c>
-      <c r="J8" s="60" t="s">
-        <v>658</v>
-      </c>
-      <c r="K8" s="60" t="s">
-        <v>503</v>
-      </c>
-      <c r="L8" s="60" t="s">
+      <c r="K8" s="58" t="s">
+        <v>502</v>
+      </c>
+      <c r="L8" s="58" t="s">
         <v>124</v>
       </c>
-      <c r="M8" s="60"/>
+      <c r="M8" s="58"/>
       <c r="N8" s="18"/>
       <c r="O8" s="18"/>
       <c r="P8" s="18"/>
@@ -7848,34 +7834,34 @@
         <f>B5+1</f>
         <v>2</v>
       </c>
-      <c r="D9" s="57" t="s">
+      <c r="D9" s="41" t="s">
         <v>287</v>
       </c>
-      <c r="E9" s="57" t="s">
+      <c r="E9" s="41" t="s">
         <v>251</v>
       </c>
-      <c r="F9" s="57" t="s">
+      <c r="F9" s="41" t="s">
         <v>287</v>
       </c>
-      <c r="G9" s="57" t="s">
+      <c r="G9" s="41" t="s">
         <v>326</v>
       </c>
-      <c r="H9" s="57" t="s">
+      <c r="H9" s="41" t="s">
         <v>230</v>
       </c>
-      <c r="I9" s="57" t="s">
+      <c r="I9" s="41" t="s">
         <v>312</v>
       </c>
-      <c r="J9" s="57" t="s">
+      <c r="J9" s="41" t="s">
         <v>56</v>
       </c>
-      <c r="K9" s="57" t="s">
+      <c r="K9" s="41" t="s">
         <v>352</v>
       </c>
-      <c r="L9" s="57" t="s">
+      <c r="L9" s="41" t="s">
         <v>48</v>
       </c>
-      <c r="M9" s="57" t="str">
+      <c r="M9" s="41" t="str">
         <f>CHAR(10)</f>
         <v xml:space="preserve">
 </v>
@@ -7892,31 +7878,31 @@
     <row r="10" spans="1:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B10" s="22"/>
       <c r="D10" s="24" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="E10" s="24" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="F10" s="24" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="G10" s="24" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="H10" s="24" t="s">
+        <v>683</v>
+      </c>
+      <c r="I10" s="24" t="s">
+        <v>501</v>
+      </c>
+      <c r="J10" s="24" t="s">
         <v>684</v>
       </c>
-      <c r="I10" s="24" t="s">
-        <v>502</v>
-      </c>
-      <c r="J10" s="24" t="s">
-        <v>685</v>
-      </c>
       <c r="K10" s="24" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="L10" s="24" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="M10" s="24"/>
       <c r="N10" s="24"/>
@@ -7938,7 +7924,7 @@
       <c r="I11" s="52"/>
       <c r="J11" s="52"/>
       <c r="K11" s="52" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="L11" s="52"/>
       <c r="M11" s="52"/>
@@ -7951,34 +7937,34 @@
     </row>
     <row r="12" spans="1:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B12" s="17"/>
-      <c r="D12" s="60" t="s">
-        <v>511</v>
-      </c>
-      <c r="E12" s="60" t="s">
+      <c r="D12" s="58" t="s">
+        <v>510</v>
+      </c>
+      <c r="E12" s="58" t="s">
         <v>115</v>
       </c>
-      <c r="F12" s="60" t="s">
-        <v>514</v>
-      </c>
-      <c r="G12" s="60" t="s">
-        <v>516</v>
-      </c>
-      <c r="H12" s="60" t="s">
+      <c r="F12" s="58" t="s">
+        <v>513</v>
+      </c>
+      <c r="G12" s="58" t="s">
+        <v>515</v>
+      </c>
+      <c r="H12" s="58" t="s">
         <v>120</v>
       </c>
-      <c r="I12" s="60" t="s">
-        <v>509</v>
-      </c>
-      <c r="J12" s="60" t="s">
+      <c r="I12" s="58" t="s">
+        <v>508</v>
+      </c>
+      <c r="J12" s="58" t="s">
         <v>118</v>
       </c>
-      <c r="K12" s="60" t="s">
-        <v>659</v>
-      </c>
-      <c r="L12" s="60" t="s">
-        <v>511</v>
-      </c>
-      <c r="M12" s="60"/>
+      <c r="K12" s="58" t="s">
+        <v>658</v>
+      </c>
+      <c r="L12" s="58" t="s">
+        <v>510</v>
+      </c>
+      <c r="M12" s="58"/>
       <c r="N12" s="18"/>
       <c r="O12" s="18"/>
       <c r="P12" s="18"/>
@@ -7992,34 +7978,34 @@
         <f>B9+1</f>
         <v>3</v>
       </c>
-      <c r="D13" s="57" t="s">
-        <v>374</v>
-      </c>
-      <c r="E13" s="57" t="s">
+      <c r="D13" s="41" t="s">
+        <v>373</v>
+      </c>
+      <c r="E13" s="41" t="s">
         <v>64</v>
       </c>
-      <c r="F13" s="57" t="s">
+      <c r="F13" s="41" t="s">
         <v>21</v>
       </c>
-      <c r="G13" s="57" t="s">
+      <c r="G13" s="41" t="s">
         <v>192</v>
       </c>
-      <c r="H13" s="57" t="s">
+      <c r="H13" s="41" t="s">
         <v>190</v>
       </c>
-      <c r="I13" s="57" t="s">
+      <c r="I13" s="41" t="s">
         <v>326</v>
       </c>
-      <c r="J13" s="57" t="s">
+      <c r="J13" s="41" t="s">
         <v>53</v>
       </c>
-      <c r="K13" s="57" t="s">
+      <c r="K13" s="41" t="s">
         <v>286</v>
       </c>
-      <c r="L13" s="57" t="s">
+      <c r="L13" s="41" t="s">
         <v>284</v>
       </c>
-      <c r="M13" s="57" t="str">
+      <c r="M13" s="41" t="str">
         <f>CHAR(10)</f>
         <v xml:space="preserve">
 </v>
@@ -8035,31 +8021,31 @@
     <row r="14" spans="1:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B14" s="22"/>
       <c r="D14" s="24" t="s">
+        <v>511</v>
+      </c>
+      <c r="E14" s="24" t="s">
         <v>512</v>
       </c>
-      <c r="E14" s="24" t="s">
-        <v>513</v>
-      </c>
       <c r="F14" s="24" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="G14" s="24" t="s">
+        <v>516</v>
+      </c>
+      <c r="H14" s="24" t="s">
         <v>517</v>
       </c>
-      <c r="H14" s="24" t="s">
+      <c r="I14" s="24" t="s">
+        <v>509</v>
+      </c>
+      <c r="J14" s="24" t="s">
         <v>518</v>
       </c>
-      <c r="I14" s="24" t="s">
-        <v>510</v>
-      </c>
-      <c r="J14" s="24" t="s">
-        <v>519</v>
-      </c>
       <c r="K14" s="24" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="L14" s="24" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="M14" s="24"/>
       <c r="N14" s="24"/>
@@ -8074,7 +8060,7 @@
       <c r="B15" s="12"/>
       <c r="C15" s="34"/>
       <c r="D15" s="52" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="E15" s="52"/>
       <c r="F15" s="52" t="s">
@@ -8083,14 +8069,14 @@
       <c r="G15" s="52"/>
       <c r="H15" s="52"/>
       <c r="I15" s="52" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="J15" s="52"/>
       <c r="K15" s="52"/>
       <c r="L15" s="52"/>
       <c r="M15" s="52"/>
       <c r="N15" s="52" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="O15" s="52"/>
       <c r="P15" s="52"/>
@@ -8100,38 +8086,38 @@
     </row>
     <row r="16" spans="1:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B16" s="17"/>
-      <c r="D16" s="60" t="s">
-        <v>746</v>
-      </c>
-      <c r="E16" s="60" t="s">
+      <c r="D16" s="58" t="s">
+        <v>745</v>
+      </c>
+      <c r="E16" s="58" t="s">
         <v>141</v>
       </c>
-      <c r="F16" s="60" t="s">
+      <c r="F16" s="58" t="s">
         <v>123</v>
       </c>
-      <c r="G16" s="60" t="s">
-        <v>522</v>
-      </c>
-      <c r="H16" s="60" t="s">
-        <v>524</v>
-      </c>
-      <c r="I16" s="60" t="s">
+      <c r="G16" s="58" t="s">
+        <v>521</v>
+      </c>
+      <c r="H16" s="58" t="s">
+        <v>523</v>
+      </c>
+      <c r="I16" s="58" t="s">
+        <v>659</v>
+      </c>
+      <c r="J16" s="58"/>
+      <c r="K16" s="58" t="s">
+        <v>525</v>
+      </c>
+      <c r="L16" s="58" t="s">
+        <v>527</v>
+      </c>
+      <c r="M16" s="58" t="s">
+        <v>525</v>
+      </c>
+      <c r="N16" s="58" t="s">
         <v>660</v>
       </c>
-      <c r="J16" s="60"/>
-      <c r="K16" s="60" t="s">
-        <v>526</v>
-      </c>
-      <c r="L16" s="60" t="s">
-        <v>528</v>
-      </c>
-      <c r="M16" s="60" t="s">
-        <v>526</v>
-      </c>
-      <c r="N16" s="60" t="s">
-        <v>661</v>
-      </c>
-      <c r="O16" s="60"/>
+      <c r="O16" s="58"/>
       <c r="P16" s="18"/>
       <c r="Q16" s="18"/>
       <c r="R16" s="18"/>
@@ -8143,40 +8129,40 @@
         <f>B13+1</f>
         <v>4</v>
       </c>
-      <c r="D17" s="57" t="s">
+      <c r="D17" s="41" t="s">
         <v>185</v>
       </c>
-      <c r="E17" s="57" t="s">
+      <c r="E17" s="41" t="s">
         <v>66</v>
       </c>
-      <c r="F17" s="57" t="s">
+      <c r="F17" s="41" t="s">
         <v>47</v>
       </c>
-      <c r="G17" s="57" t="s">
+      <c r="G17" s="41" t="s">
         <v>306</v>
       </c>
-      <c r="H17" s="57" t="s">
+      <c r="H17" s="41" t="s">
         <v>229</v>
       </c>
-      <c r="I17" s="57" t="s">
+      <c r="I17" s="41" t="s">
         <v>270</v>
       </c>
-      <c r="J17" s="57" t="s">
-        <v>375</v>
-      </c>
-      <c r="K17" s="57" t="s">
+      <c r="J17" s="41" t="s">
+        <v>374</v>
+      </c>
+      <c r="K17" s="41" t="s">
         <v>162</v>
       </c>
-      <c r="L17" s="57" t="s">
+      <c r="L17" s="41" t="s">
         <v>203</v>
       </c>
-      <c r="M17" s="57" t="s">
+      <c r="M17" s="41" t="s">
         <v>162</v>
       </c>
-      <c r="N17" s="57" t="s">
+      <c r="N17" s="41" t="s">
         <v>166</v>
       </c>
-      <c r="O17" s="57" t="str">
+      <c r="O17" s="41" t="str">
         <f>CHAR(10)</f>
         <v xml:space="preserve">
 </v>
@@ -8190,35 +8176,35 @@
     <row r="18" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B18" s="22"/>
       <c r="D18" s="24" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="E18" s="24" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="F18" s="24" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="G18" s="24" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H18" s="24" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="I18" s="24" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="J18" s="24"/>
       <c r="K18" s="24" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="L18" s="24" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="M18" s="24" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="N18" s="24" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="O18" s="24"/>
       <c r="P18" s="24"/>
@@ -8231,7 +8217,7 @@
       <c r="B19" s="12"/>
       <c r="C19" s="34"/>
       <c r="D19" s="52" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="E19" s="52"/>
       <c r="F19" s="52" t="s">
@@ -8241,17 +8227,17 @@
       <c r="H19" s="52"/>
       <c r="I19" s="52"/>
       <c r="J19" s="52" t="s">
+        <v>661</v>
+      </c>
+      <c r="K19" s="52" t="s">
         <v>662</v>
-      </c>
-      <c r="K19" s="52" t="s">
-        <v>663</v>
       </c>
       <c r="L19" s="52"/>
       <c r="M19" s="52" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="N19" s="52" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="O19" s="52"/>
       <c r="P19" s="52"/>
@@ -8261,43 +8247,43 @@
     </row>
     <row r="20" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B20" s="17"/>
-      <c r="D20" s="60" t="s">
-        <v>748</v>
-      </c>
-      <c r="E20" s="60" t="s">
+      <c r="D20" s="58" t="s">
+        <v>747</v>
+      </c>
+      <c r="E20" s="58" t="s">
         <v>136</v>
       </c>
-      <c r="F20" s="60" t="s">
+      <c r="F20" s="58" t="s">
         <v>363</v>
       </c>
-      <c r="G20" s="60" t="s">
+      <c r="G20" s="58" t="s">
         <v>121</v>
       </c>
-      <c r="H20" s="60" t="s">
-        <v>533</v>
-      </c>
-      <c r="I20" s="60" t="s">
-        <v>505</v>
-      </c>
-      <c r="J20" s="60" t="s">
+      <c r="H20" s="58" t="s">
+        <v>532</v>
+      </c>
+      <c r="I20" s="58" t="s">
+        <v>504</v>
+      </c>
+      <c r="J20" s="58" t="s">
+        <v>661</v>
+      </c>
+      <c r="K20" s="58" t="s">
         <v>662</v>
       </c>
-      <c r="K20" s="60" t="s">
+      <c r="L20" s="58" t="s">
+        <v>534</v>
+      </c>
+      <c r="M20" s="58" t="s">
+        <v>762</v>
+      </c>
+      <c r="N20" s="58" t="s">
         <v>663</v>
       </c>
-      <c r="L20" s="60" t="s">
-        <v>535</v>
-      </c>
-      <c r="M20" s="60" t="s">
-        <v>763</v>
-      </c>
-      <c r="N20" s="60" t="s">
-        <v>664</v>
-      </c>
-      <c r="O20" s="60" t="s">
-        <v>537</v>
-      </c>
-      <c r="P20" s="60"/>
+      <c r="O20" s="58" t="s">
+        <v>536</v>
+      </c>
+      <c r="P20" s="58"/>
       <c r="Q20" s="18"/>
       <c r="R20" s="18"/>
       <c r="S20" s="19"/>
@@ -8308,43 +8294,43 @@
         <f>B17+1</f>
         <v>5</v>
       </c>
-      <c r="D21" s="57" t="s">
+      <c r="D21" s="41" t="s">
         <v>298</v>
       </c>
-      <c r="E21" s="57" t="s">
+      <c r="E21" s="41" t="s">
         <v>269</v>
       </c>
-      <c r="F21" s="57" t="s">
+      <c r="F21" s="41" t="s">
         <v>19</v>
       </c>
-      <c r="G21" s="57" t="s">
+      <c r="G21" s="41" t="s">
         <v>255</v>
       </c>
-      <c r="H21" s="57" t="s">
+      <c r="H21" s="41" t="s">
         <v>232</v>
       </c>
-      <c r="I21" s="57" t="s">
+      <c r="I21" s="41" t="s">
         <v>287</v>
       </c>
-      <c r="J21" s="57" t="s">
+      <c r="J21" s="41" t="s">
         <v>240</v>
       </c>
-      <c r="K21" s="57" t="s">
+      <c r="K21" s="41" t="s">
         <v>344</v>
       </c>
-      <c r="L21" s="57" t="s">
+      <c r="L21" s="41" t="s">
         <v>302</v>
       </c>
-      <c r="M21" s="57" t="s">
+      <c r="M21" s="41" t="s">
         <v>241</v>
       </c>
-      <c r="N21" s="57" t="s">
+      <c r="N21" s="41" t="s">
         <v>330</v>
       </c>
-      <c r="O21" s="57" t="s">
+      <c r="O21" s="41" t="s">
         <v>225</v>
       </c>
-      <c r="P21" s="57" t="str">
+      <c r="P21" s="41" t="str">
         <f>CHAR(10)</f>
         <v xml:space="preserve">
 </v>
@@ -8357,40 +8343,40 @@
     <row r="22" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B22" s="22"/>
       <c r="D22" s="24" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="E22" s="24" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="F22" s="24" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="G22" s="24" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H22" s="24" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="I22" s="24" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="J22" s="24" t="s">
+        <v>688</v>
+      </c>
+      <c r="K22" s="24" t="s">
         <v>689</v>
       </c>
-      <c r="K22" s="24" t="s">
-        <v>690</v>
-      </c>
       <c r="L22" s="24" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="M22" s="24" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="N22" s="24" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="O22" s="24" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="P22" s="24"/>
       <c r="Q22" s="24"/>
@@ -8402,30 +8388,30 @@
       <c r="B23" s="12"/>
       <c r="C23" s="34"/>
       <c r="D23" s="52" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="E23" s="52"/>
       <c r="F23" s="52"/>
       <c r="G23" s="52"/>
       <c r="H23" s="52" t="s">
+        <v>664</v>
+      </c>
+      <c r="I23" s="52" t="s">
         <v>665</v>
-      </c>
-      <c r="I23" s="52" t="s">
-        <v>666</v>
       </c>
       <c r="J23" s="52"/>
       <c r="K23" s="52" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="L23" s="52"/>
       <c r="M23" s="52" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="N23" s="52" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="O23" s="52" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="P23" s="52"/>
       <c r="Q23" s="52"/>
@@ -8434,41 +8420,41 @@
     </row>
     <row r="24" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B24" s="17"/>
-      <c r="D24" s="60" t="s">
-        <v>667</v>
-      </c>
-      <c r="E24" s="60" t="s">
-        <v>540</v>
-      </c>
-      <c r="F24" s="60" t="s">
-        <v>542</v>
-      </c>
-      <c r="G24" s="60" t="s">
-        <v>544</v>
-      </c>
-      <c r="H24" s="60" t="s">
+      <c r="D24" s="58" t="s">
+        <v>666</v>
+      </c>
+      <c r="E24" s="58" t="s">
+        <v>539</v>
+      </c>
+      <c r="F24" s="58" t="s">
+        <v>541</v>
+      </c>
+      <c r="G24" s="58" t="s">
+        <v>543</v>
+      </c>
+      <c r="H24" s="58" t="s">
+        <v>664</v>
+      </c>
+      <c r="I24" s="58" t="s">
         <v>665</v>
       </c>
-      <c r="I24" s="60" t="s">
+      <c r="J24" s="58"/>
+      <c r="K24" s="58" t="s">
         <v>666</v>
       </c>
-      <c r="J24" s="60"/>
-      <c r="K24" s="60" t="s">
-        <v>667</v>
-      </c>
-      <c r="L24" s="60" t="s">
-        <v>540</v>
-      </c>
-      <c r="M24" s="60" t="s">
-        <v>669</v>
-      </c>
-      <c r="N24" s="60" t="s">
-        <v>748</v>
-      </c>
-      <c r="O24" s="60" t="s">
-        <v>735</v>
-      </c>
-      <c r="P24" s="60"/>
+      <c r="L24" s="58" t="s">
+        <v>539</v>
+      </c>
+      <c r="M24" s="58" t="s">
+        <v>668</v>
+      </c>
+      <c r="N24" s="58" t="s">
+        <v>747</v>
+      </c>
+      <c r="O24" s="58" t="s">
+        <v>734</v>
+      </c>
+      <c r="P24" s="58"/>
       <c r="Q24" s="18"/>
       <c r="R24" s="18"/>
       <c r="S24" s="19"/>
@@ -8479,43 +8465,43 @@
         <f>B21+1</f>
         <v>6</v>
       </c>
-      <c r="D25" s="57" t="s">
+      <c r="D25" s="41" t="s">
         <v>22</v>
       </c>
-      <c r="E25" s="57" t="s">
+      <c r="E25" s="41" t="s">
         <v>264</v>
       </c>
-      <c r="F25" s="57" t="s">
+      <c r="F25" s="41" t="s">
         <v>325</v>
       </c>
-      <c r="G25" s="57" t="s">
+      <c r="G25" s="41" t="s">
         <v>328</v>
       </c>
-      <c r="H25" s="57" t="s">
+      <c r="H25" s="41" t="s">
         <v>304</v>
       </c>
-      <c r="I25" s="57" t="s">
+      <c r="I25" s="41" t="s">
         <v>189</v>
       </c>
-      <c r="J25" s="57" t="s">
-        <v>375</v>
-      </c>
-      <c r="K25" s="57" t="s">
+      <c r="J25" s="41" t="s">
+        <v>374</v>
+      </c>
+      <c r="K25" s="41" t="s">
         <v>22</v>
       </c>
-      <c r="L25" s="57" t="s">
+      <c r="L25" s="41" t="s">
         <v>264</v>
       </c>
-      <c r="M25" s="57" t="s">
+      <c r="M25" s="41" t="s">
         <v>161</v>
       </c>
-      <c r="N25" s="57" t="s">
+      <c r="N25" s="41" t="s">
         <v>298</v>
       </c>
-      <c r="O25" s="57" t="s">
+      <c r="O25" s="41" t="s">
         <v>50</v>
       </c>
-      <c r="P25" s="57" t="str">
+      <c r="P25" s="41" t="str">
         <f>CHAR(10)</f>
         <v xml:space="preserve">
 </v>
@@ -8528,38 +8514,38 @@
     <row r="26" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B26" s="22"/>
       <c r="D26" s="24" t="s">
+        <v>693</v>
+      </c>
+      <c r="E26" s="24" t="s">
+        <v>540</v>
+      </c>
+      <c r="F26" s="24" t="s">
+        <v>542</v>
+      </c>
+      <c r="G26" s="24" t="s">
+        <v>544</v>
+      </c>
+      <c r="H26" s="24" t="s">
         <v>694</v>
       </c>
-      <c r="E26" s="24" t="s">
-        <v>541</v>
-      </c>
-      <c r="F26" s="24" t="s">
-        <v>543</v>
-      </c>
-      <c r="G26" s="24" t="s">
-        <v>545</v>
-      </c>
-      <c r="H26" s="24" t="s">
+      <c r="I26" s="24" t="s">
         <v>695</v>
-      </c>
-      <c r="I26" s="24" t="s">
-        <v>696</v>
       </c>
       <c r="J26" s="24"/>
       <c r="K26" s="24" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="L26" s="24" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="M26" s="24" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="N26" s="24" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="O26" s="24" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="P26" s="24"/>
       <c r="Q26" s="24"/>
@@ -8574,7 +8560,7 @@
       <c r="E27" s="52"/>
       <c r="F27" s="52"/>
       <c r="G27" s="52" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="H27" s="52"/>
       <c r="I27" s="52"/>
@@ -8586,14 +8572,14 @@
       <c r="M27" s="52"/>
       <c r="N27" s="52"/>
       <c r="O27" s="52" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="P27" s="52"/>
       <c r="Q27" s="52" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="R27" s="52" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="U27" s="35" t="str">
         <f t="shared" ref="U27:U32" si="1" xml:space="preserve"> MID($N$26,4,1)</f>
@@ -8603,46 +8589,46 @@
     </row>
     <row r="28" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B28" s="17"/>
-      <c r="D28" s="60" t="s">
+      <c r="D28" s="58" t="s">
         <v>113</v>
       </c>
-      <c r="E28" s="60" t="s">
-        <v>547</v>
-      </c>
-      <c r="F28" s="60"/>
-      <c r="G28" s="60" t="s">
+      <c r="E28" s="58" t="s">
+        <v>546</v>
+      </c>
+      <c r="F28" s="58"/>
+      <c r="G28" s="58" t="s">
+        <v>669</v>
+      </c>
+      <c r="H28" s="58" t="s">
+        <v>527</v>
+      </c>
+      <c r="I28" s="58" t="s">
+        <v>548</v>
+      </c>
+      <c r="J28" s="58" t="s">
+        <v>521</v>
+      </c>
+      <c r="K28" s="58" t="s">
+        <v>550</v>
+      </c>
+      <c r="L28" s="58" t="s">
+        <v>131</v>
+      </c>
+      <c r="M28" s="58"/>
+      <c r="N28" s="58" t="s">
+        <v>554</v>
+      </c>
+      <c r="O28" s="58" t="s">
         <v>670</v>
       </c>
-      <c r="H28" s="60" t="s">
-        <v>528</v>
-      </c>
-      <c r="I28" s="60" t="s">
-        <v>549</v>
-      </c>
-      <c r="J28" s="60" t="s">
-        <v>522</v>
-      </c>
-      <c r="K28" s="60" t="s">
-        <v>551</v>
-      </c>
-      <c r="L28" s="60" t="s">
-        <v>131</v>
-      </c>
-      <c r="M28" s="60"/>
-      <c r="N28" s="60" t="s">
-        <v>555</v>
-      </c>
-      <c r="O28" s="60" t="s">
+      <c r="P28" s="58" t="s">
+        <v>136</v>
+      </c>
+      <c r="Q28" s="58" t="s">
+        <v>363</v>
+      </c>
+      <c r="R28" s="58" t="s">
         <v>671</v>
-      </c>
-      <c r="P28" s="60" t="s">
-        <v>136</v>
-      </c>
-      <c r="Q28" s="60" t="s">
-        <v>363</v>
-      </c>
-      <c r="R28" s="60" t="s">
-        <v>672</v>
       </c>
       <c r="S28" s="19"/>
       <c r="U28" s="35" t="str">
@@ -8656,49 +8642,49 @@
         <f>B25+1</f>
         <v>7</v>
       </c>
-      <c r="D29" s="57" t="s">
+      <c r="D29" s="41" t="s">
         <v>37</v>
       </c>
-      <c r="E29" s="57" t="s">
+      <c r="E29" s="41" t="s">
         <v>247</v>
       </c>
-      <c r="F29" s="57" t="s">
-        <v>375</v>
-      </c>
-      <c r="G29" s="57" t="s">
+      <c r="F29" s="41" t="s">
+        <v>374</v>
+      </c>
+      <c r="G29" s="41" t="s">
         <v>350</v>
       </c>
-      <c r="H29" s="57" t="s">
+      <c r="H29" s="41" t="s">
         <v>203</v>
       </c>
-      <c r="I29" s="57" t="s">
+      <c r="I29" s="41" t="s">
         <v>209</v>
       </c>
-      <c r="J29" s="57" t="s">
+      <c r="J29" s="41" t="s">
         <v>306</v>
       </c>
-      <c r="K29" s="57" t="s">
+      <c r="K29" s="41" t="s">
         <v>207</v>
       </c>
-      <c r="L29" s="57" t="s">
+      <c r="L29" s="41" t="s">
         <v>234</v>
       </c>
-      <c r="M29" s="57" t="s">
-        <v>375</v>
-      </c>
-      <c r="N29" s="57" t="s">
+      <c r="M29" s="41" t="s">
+        <v>374</v>
+      </c>
+      <c r="N29" s="41" t="s">
         <v>211</v>
       </c>
-      <c r="O29" s="57" t="s">
+      <c r="O29" s="41" t="s">
         <v>44</v>
       </c>
-      <c r="P29" s="57" t="s">
+      <c r="P29" s="41" t="s">
         <v>269</v>
       </c>
-      <c r="Q29" s="57" t="s">
+      <c r="Q29" s="41" t="s">
         <v>19</v>
       </c>
-      <c r="R29" s="57" t="s">
+      <c r="R29" s="41" t="s">
         <v>292</v>
       </c>
       <c r="S29" s="21"/>
@@ -8711,45 +8697,45 @@
     <row r="30" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B30" s="22"/>
       <c r="D30" s="24" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="E30" s="24" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="F30" s="24"/>
       <c r="G30" s="24" t="s">
+        <v>698</v>
+      </c>
+      <c r="H30" s="24" t="s">
+        <v>528</v>
+      </c>
+      <c r="I30" s="24" t="s">
+        <v>549</v>
+      </c>
+      <c r="J30" s="24" t="s">
+        <v>522</v>
+      </c>
+      <c r="K30" s="24" t="s">
+        <v>551</v>
+      </c>
+      <c r="L30" s="24" t="s">
         <v>699</v>
-      </c>
-      <c r="H30" s="24" t="s">
-        <v>529</v>
-      </c>
-      <c r="I30" s="24" t="s">
-        <v>550</v>
-      </c>
-      <c r="J30" s="24" t="s">
-        <v>523</v>
-      </c>
-      <c r="K30" s="24" t="s">
-        <v>552</v>
-      </c>
-      <c r="L30" s="24" t="s">
-        <v>700</v>
       </c>
       <c r="M30" s="24"/>
       <c r="N30" s="24" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="O30" s="24" t="s">
+        <v>700</v>
+      </c>
+      <c r="P30" s="24" t="s">
+        <v>529</v>
+      </c>
+      <c r="Q30" s="24" t="s">
+        <v>651</v>
+      </c>
+      <c r="R30" s="24" t="s">
         <v>701</v>
-      </c>
-      <c r="P30" s="24" t="s">
-        <v>530</v>
-      </c>
-      <c r="Q30" s="24" t="s">
-        <v>652</v>
-      </c>
-      <c r="R30" s="24" t="s">
-        <v>702</v>
       </c>
       <c r="S30" s="31"/>
       <c r="U30" s="35" t="str">
@@ -8811,7 +8797,7 @@
         <f>B29+1</f>
         <v>8</v>
       </c>
-      <c r="D33" s="57" t="str">
+      <c r="D33" s="41" t="str">
         <f>CHAR(10)</f>
         <v xml:space="preserve">
 </v>
@@ -8857,14 +8843,14 @@
       <c r="B35" s="12"/>
       <c r="C35" s="34"/>
       <c r="D35" s="52" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="E35" s="52"/>
       <c r="F35" s="52"/>
       <c r="G35" s="52"/>
       <c r="H35" s="52"/>
       <c r="I35" s="52" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="J35" s="52"/>
       <c r="K35" s="52"/>
@@ -8882,25 +8868,25 @@
     <row r="36" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B36" s="17"/>
       <c r="D36" s="18" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="E36" s="18" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="F36" s="18" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="G36" s="18" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="H36" s="18" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="I36" s="18" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="J36" s="18" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="K36" s="18" t="s">
         <v>122</v>
@@ -8922,34 +8908,34 @@
         <f>B33+1</f>
         <v>9</v>
       </c>
-      <c r="D37" s="57" t="s">
+      <c r="D37" s="41" t="s">
         <v>292</v>
       </c>
-      <c r="E37" s="57" t="s">
+      <c r="E37" s="41" t="s">
         <v>326</v>
       </c>
-      <c r="F37" s="57" t="s">
-        <v>374</v>
-      </c>
-      <c r="G37" s="57" t="s">
+      <c r="F37" s="41" t="s">
+        <v>373</v>
+      </c>
+      <c r="G37" s="41" t="s">
         <v>287</v>
       </c>
-      <c r="H37" s="57" t="s">
+      <c r="H37" s="41" t="s">
         <v>354</v>
       </c>
-      <c r="I37" s="57" t="s">
+      <c r="I37" s="41" t="s">
         <v>22</v>
       </c>
-      <c r="J37" s="57" t="s">
+      <c r="J37" s="41" t="s">
         <v>221</v>
       </c>
-      <c r="K37" s="57" t="s">
+      <c r="K37" s="41" t="s">
         <v>45</v>
       </c>
-      <c r="L37" s="57" t="s">
+      <c r="L37" s="41" t="s">
         <v>63</v>
       </c>
-      <c r="M37" s="57" t="str">
+      <c r="M37" s="41" t="str">
         <f>CHAR(10)</f>
         <v xml:space="preserve">
 </v>
@@ -8965,31 +8951,31 @@
     <row r="38" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B38" s="22"/>
       <c r="D38" s="24" t="s">
+        <v>701</v>
+      </c>
+      <c r="E38" s="24" t="s">
+        <v>509</v>
+      </c>
+      <c r="F38" s="24" t="s">
+        <v>511</v>
+      </c>
+      <c r="G38" s="24" t="s">
+        <v>505</v>
+      </c>
+      <c r="H38" s="24" t="s">
+        <v>557</v>
+      </c>
+      <c r="I38" s="24" t="s">
+        <v>693</v>
+      </c>
+      <c r="J38" s="24" t="s">
+        <v>559</v>
+      </c>
+      <c r="K38" s="24" t="s">
+        <v>560</v>
+      </c>
+      <c r="L38" s="24" t="s">
         <v>702</v>
-      </c>
-      <c r="E38" s="24" t="s">
-        <v>510</v>
-      </c>
-      <c r="F38" s="24" t="s">
-        <v>512</v>
-      </c>
-      <c r="G38" s="24" t="s">
-        <v>506</v>
-      </c>
-      <c r="H38" s="24" t="s">
-        <v>558</v>
-      </c>
-      <c r="I38" s="24" t="s">
-        <v>694</v>
-      </c>
-      <c r="J38" s="24" t="s">
-        <v>560</v>
-      </c>
-      <c r="K38" s="24" t="s">
-        <v>561</v>
-      </c>
-      <c r="L38" s="24" t="s">
-        <v>703</v>
       </c>
       <c r="M38" s="24"/>
       <c r="N38" s="24"/>
@@ -9005,18 +8991,18 @@
       <c r="C39" s="34"/>
       <c r="D39" s="52"/>
       <c r="E39" s="52" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F39" s="52"/>
       <c r="G39" s="52"/>
       <c r="H39" s="52"/>
       <c r="I39" s="52" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="J39" s="52"/>
       <c r="K39" s="52"/>
       <c r="L39" s="52" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="M39" s="52"/>
       <c r="N39" s="52"/>
@@ -9029,31 +9015,31 @@
     <row r="40" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B40" s="17"/>
       <c r="D40" s="18" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="E40" s="18" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="F40" s="18" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="G40" s="18" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="H40" s="18" t="s">
         <v>142</v>
       </c>
       <c r="I40" s="18" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="J40" s="18" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="K40" s="18" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="L40" s="18" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="M40" s="18"/>
       <c r="N40" s="18"/>
@@ -9069,34 +9055,34 @@
         <f>B37+1</f>
         <v>10</v>
       </c>
-      <c r="D41" s="57" t="s">
+      <c r="D41" s="41" t="s">
         <v>247</v>
       </c>
-      <c r="E41" s="57" t="s">
+      <c r="E41" s="41" t="s">
         <v>22</v>
       </c>
-      <c r="F41" s="57" t="s">
+      <c r="F41" s="41" t="s">
         <v>267</v>
       </c>
-      <c r="G41" s="57" t="s">
+      <c r="G41" s="41" t="s">
         <v>333</v>
       </c>
-      <c r="H41" s="57" t="s">
+      <c r="H41" s="41" t="s">
         <v>23</v>
       </c>
-      <c r="I41" s="57" t="s">
+      <c r="I41" s="41" t="s">
         <v>322</v>
       </c>
-      <c r="J41" s="57" t="s">
+      <c r="J41" s="41" t="s">
         <v>287</v>
       </c>
-      <c r="K41" s="57" t="s">
+      <c r="K41" s="41" t="s">
         <v>306</v>
       </c>
-      <c r="L41" s="57" t="s">
+      <c r="L41" s="41" t="s">
         <v>193</v>
       </c>
-      <c r="M41" s="57" t="str">
+      <c r="M41" s="41" t="str">
         <f>CHAR(10)</f>
         <v xml:space="preserve">
 </v>
@@ -9112,31 +9098,31 @@
     <row r="42" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B42" s="22"/>
       <c r="D42" s="24" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="E42" s="24" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="F42" s="24" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="G42" s="24" t="s">
+        <v>564</v>
+      </c>
+      <c r="H42" s="24" t="s">
         <v>565</v>
       </c>
-      <c r="H42" s="24" t="s">
-        <v>566</v>
-      </c>
       <c r="I42" s="24" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="J42" s="24" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="K42" s="24" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="L42" s="24" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="M42" s="24"/>
       <c r="N42" s="24"/>
@@ -9151,24 +9137,24 @@
       <c r="B43" s="12"/>
       <c r="C43" s="34"/>
       <c r="D43" s="52" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="E43" s="52"/>
       <c r="F43" s="52" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="G43" s="52"/>
       <c r="H43" s="52"/>
       <c r="I43" s="52"/>
       <c r="J43" s="52"/>
       <c r="K43" s="52" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="L43" s="52" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="M43" s="52" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="N43" s="52"/>
       <c r="O43" s="52"/>
@@ -9180,35 +9166,35 @@
     <row r="44" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B44" s="17"/>
       <c r="D44" s="18" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="E44" s="18" t="s">
         <v>116</v>
       </c>
       <c r="F44" s="18" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="G44" s="18" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="H44" s="18" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="I44" s="18" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="J44" s="18"/>
       <c r="K44" s="18" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="L44" s="18" t="s">
         <v>124</v>
       </c>
       <c r="M44" s="18" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="N44" s="18" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="O44" s="18"/>
       <c r="P44" s="18"/>
@@ -9222,40 +9208,40 @@
         <f>B41+1</f>
         <v>11</v>
       </c>
-      <c r="D45" s="57" t="s">
+      <c r="D45" s="41" t="s">
         <v>55</v>
       </c>
-      <c r="E45" s="57" t="s">
+      <c r="E45" s="41" t="s">
         <v>22</v>
       </c>
-      <c r="F45" s="58" t="s">
-        <v>732</v>
-      </c>
-      <c r="G45" s="57" t="s">
+      <c r="F45" s="57" t="s">
+        <v>731</v>
+      </c>
+      <c r="G45" s="41" t="s">
         <v>347</v>
       </c>
-      <c r="H45" s="57" t="s">
+      <c r="H45" s="41" t="s">
         <v>238</v>
       </c>
-      <c r="I45" s="57" t="s">
+      <c r="I45" s="41" t="s">
         <v>62</v>
       </c>
-      <c r="J45" s="57" t="s">
-        <v>375</v>
-      </c>
-      <c r="K45" s="57" t="s">
+      <c r="J45" s="41" t="s">
+        <v>374</v>
+      </c>
+      <c r="K45" s="41" t="s">
         <v>307</v>
       </c>
-      <c r="L45" s="57" t="s">
+      <c r="L45" s="41" t="s">
         <v>48</v>
       </c>
-      <c r="M45" s="57" t="s">
+      <c r="M45" s="41" t="s">
         <v>307</v>
       </c>
-      <c r="N45" s="57" t="s">
+      <c r="N45" s="41" t="s">
         <v>357</v>
       </c>
-      <c r="O45" s="57" t="str">
+      <c r="O45" s="41" t="str">
         <f>CHAR(10)</f>
         <v xml:space="preserve">
 </v>
@@ -9269,35 +9255,35 @@
     <row r="46" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B46" s="22"/>
       <c r="D46" s="24" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="E46" s="24" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="F46" s="24" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="G46" s="24" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H46" s="24" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="I46" s="24" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="J46" s="24"/>
       <c r="K46" s="24" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="L46" s="24" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="M46" s="24" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="N46" s="24" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="O46" s="24"/>
       <c r="P46" s="24"/>
@@ -9313,20 +9299,20 @@
         <v>129</v>
       </c>
       <c r="E47" s="52" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="F47" s="52" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="G47" s="52" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="H47" s="52"/>
       <c r="I47" s="52" t="s">
+        <v>674</v>
+      </c>
+      <c r="J47" s="52" t="s">
         <v>675</v>
-      </c>
-      <c r="J47" s="52" t="s">
-        <v>676</v>
       </c>
       <c r="K47" s="52"/>
       <c r="L47" s="52"/>
@@ -9344,37 +9330,37 @@
         <v>129</v>
       </c>
       <c r="E48" s="18" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="F48" s="18" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="G48" s="18" t="s">
+        <v>673</v>
+      </c>
+      <c r="H48" s="18" t="s">
+        <v>532</v>
+      </c>
+      <c r="I48" s="18" t="s">
         <v>674</v>
       </c>
-      <c r="H48" s="18" t="s">
-        <v>533</v>
-      </c>
-      <c r="I48" s="18" t="s">
+      <c r="J48" s="18" t="s">
         <v>675</v>
       </c>
-      <c r="J48" s="18" t="s">
-        <v>676</v>
-      </c>
       <c r="K48" s="18" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="L48" s="18" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="M48" s="18" t="s">
         <v>140</v>
       </c>
       <c r="N48" s="18" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="O48" s="18" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="P48" s="18"/>
       <c r="Q48" s="18"/>
@@ -9387,43 +9373,43 @@
         <f>B45+1</f>
         <v>12</v>
       </c>
-      <c r="D49" s="57" t="s">
+      <c r="D49" s="41" t="s">
         <v>226</v>
       </c>
-      <c r="E49" s="57" t="s">
+      <c r="E49" s="41" t="s">
         <v>228</v>
       </c>
-      <c r="F49" s="57" t="s">
+      <c r="F49" s="41" t="s">
         <v>44</v>
       </c>
-      <c r="G49" s="57" t="s">
+      <c r="G49" s="41" t="s">
         <v>237</v>
       </c>
-      <c r="H49" s="57" t="s">
+      <c r="H49" s="41" t="s">
         <v>232</v>
       </c>
-      <c r="I49" s="57" t="s">
+      <c r="I49" s="41" t="s">
         <v>300</v>
       </c>
-      <c r="J49" s="57" t="s">
+      <c r="J49" s="41" t="s">
         <v>25</v>
       </c>
-      <c r="K49" s="57" t="s">
+      <c r="K49" s="41" t="s">
         <v>306</v>
       </c>
-      <c r="L49" s="57" t="s">
+      <c r="L49" s="41" t="s">
         <v>290</v>
       </c>
-      <c r="M49" s="57" t="s">
+      <c r="M49" s="41" t="s">
         <v>220</v>
       </c>
-      <c r="N49" s="57" t="s">
+      <c r="N49" s="41" t="s">
         <v>203</v>
       </c>
-      <c r="O49" s="57" t="s">
+      <c r="O49" s="41" t="s">
         <v>339</v>
       </c>
-      <c r="P49" s="57" t="str">
+      <c r="P49" s="41" t="str">
         <f>CHAR(10)</f>
         <v xml:space="preserve">
 </v>
@@ -9436,40 +9422,40 @@
     <row r="50" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B50" s="22"/>
       <c r="D50" s="24" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="E50" s="24" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="F50" s="24" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="G50" s="24" t="s">
+        <v>706</v>
+      </c>
+      <c r="H50" s="24" t="s">
+        <v>533</v>
+      </c>
+      <c r="I50" s="24" t="s">
         <v>707</v>
       </c>
-      <c r="H50" s="24" t="s">
-        <v>534</v>
-      </c>
-      <c r="I50" s="24" t="s">
+      <c r="J50" s="24" t="s">
         <v>708</v>
       </c>
-      <c r="J50" s="24" t="s">
-        <v>709</v>
-      </c>
       <c r="K50" s="24" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="L50" s="24" t="s">
+        <v>577</v>
+      </c>
+      <c r="M50" s="24" t="s">
         <v>578</v>
       </c>
-      <c r="M50" s="24" t="s">
-        <v>579</v>
-      </c>
       <c r="N50" s="24" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="O50" s="24" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="P50" s="24"/>
       <c r="Q50" s="24"/>
@@ -9481,7 +9467,7 @@
       <c r="B51" s="12"/>
       <c r="C51" s="34"/>
       <c r="D51" s="52" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="E51" s="52"/>
       <c r="F51" s="52"/>
@@ -9492,7 +9478,7 @@
       <c r="K51" s="52"/>
       <c r="L51" s="52"/>
       <c r="M51" s="52" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="N51" s="52" t="s">
         <v>137</v>
@@ -9506,32 +9492,32 @@
     <row r="52" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B52" s="17"/>
       <c r="D52" s="18" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="E52" s="18" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="F52" s="18" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="G52" s="18" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H52" s="18" t="s">
         <v>135</v>
       </c>
       <c r="I52" s="18"/>
       <c r="J52" s="18" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="K52" s="18" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="L52" s="18" t="s">
         <v>134</v>
       </c>
       <c r="M52" s="18" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="N52" s="18" t="s">
         <v>137</v>
@@ -9548,40 +9534,40 @@
         <f>B49+1</f>
         <v>13</v>
       </c>
-      <c r="D53" s="57" t="s">
+      <c r="D53" s="41" t="s">
         <v>170</v>
       </c>
-      <c r="E53" s="57" t="s">
+      <c r="E53" s="41" t="s">
         <v>293</v>
       </c>
-      <c r="F53" s="57" t="s">
+      <c r="F53" s="41" t="s">
         <v>306</v>
       </c>
-      <c r="G53" s="57" t="s">
+      <c r="G53" s="41" t="s">
         <v>217</v>
       </c>
-      <c r="H53" s="57" t="s">
+      <c r="H53" s="41" t="s">
         <v>58</v>
       </c>
-      <c r="I53" s="57" t="s">
-        <v>375</v>
-      </c>
-      <c r="J53" s="57" t="s">
+      <c r="I53" s="41" t="s">
+        <v>374</v>
+      </c>
+      <c r="J53" s="41" t="s">
         <v>253</v>
       </c>
-      <c r="K53" s="57" t="s">
+      <c r="K53" s="41" t="s">
         <v>217</v>
       </c>
-      <c r="L53" s="57" t="s">
+      <c r="L53" s="41" t="s">
         <v>334</v>
       </c>
-      <c r="M53" s="57" t="s">
+      <c r="M53" s="41" t="s">
         <v>322</v>
       </c>
-      <c r="N53" s="57" t="s">
+      <c r="N53" s="41" t="s">
         <v>63</v>
       </c>
-      <c r="O53" s="57" t="str">
+      <c r="O53" s="41" t="str">
         <f>CHAR(10)</f>
         <v xml:space="preserve">
 </v>
@@ -9595,35 +9581,35 @@
     <row r="54" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B54" s="22"/>
       <c r="D54" s="24" t="s">
+        <v>709</v>
+      </c>
+      <c r="E54" s="24" t="s">
+        <v>582</v>
+      </c>
+      <c r="F54" s="24" t="s">
+        <v>522</v>
+      </c>
+      <c r="G54" s="24" t="s">
+        <v>584</v>
+      </c>
+      <c r="H54" s="24" t="s">
         <v>710</v>
-      </c>
-      <c r="E54" s="24" t="s">
-        <v>583</v>
-      </c>
-      <c r="F54" s="24" t="s">
-        <v>523</v>
-      </c>
-      <c r="G54" s="24" t="s">
-        <v>585</v>
-      </c>
-      <c r="H54" s="24" t="s">
-        <v>711</v>
       </c>
       <c r="I54" s="24"/>
       <c r="J54" s="24" t="s">
+        <v>586</v>
+      </c>
+      <c r="K54" s="24" t="s">
+        <v>584</v>
+      </c>
+      <c r="L54" s="24" t="s">
         <v>587</v>
       </c>
-      <c r="K54" s="24" t="s">
-        <v>585</v>
-      </c>
-      <c r="L54" s="24" t="s">
-        <v>588</v>
-      </c>
       <c r="M54" s="24" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="N54" s="24" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="O54" s="24"/>
       <c r="P54" s="24"/>
@@ -9636,24 +9622,24 @@
       <c r="B55" s="12"/>
       <c r="C55" s="34"/>
       <c r="D55" s="52" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="E55" s="52" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F55" s="52"/>
       <c r="G55" s="52" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="H55" s="52" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="I55" s="52"/>
       <c r="J55" s="52"/>
       <c r="K55" s="52"/>
       <c r="L55" s="52"/>
       <c r="M55" s="52" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="N55" s="52"/>
       <c r="O55" s="52"/>
@@ -9665,41 +9651,41 @@
     <row r="56" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B56" s="17"/>
       <c r="D56" s="18" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="E56" s="18" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="F56" s="18" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="G56" s="18" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="H56" s="18" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="I56" s="18" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="J56" s="18" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="K56" s="18" t="s">
         <v>132</v>
       </c>
       <c r="L56" s="18"/>
       <c r="M56" s="18" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="N56" s="18" t="s">
         <v>142</v>
       </c>
       <c r="O56" s="18" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="P56" s="18" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="Q56" s="18"/>
       <c r="R56" s="18"/>
@@ -9711,46 +9697,46 @@
         <f>B53+1</f>
         <v>14</v>
       </c>
-      <c r="D57" s="57" t="s">
+      <c r="D57" s="41" t="s">
         <v>50</v>
       </c>
-      <c r="E57" s="57" t="s">
+      <c r="E57" s="41" t="s">
         <v>344</v>
       </c>
-      <c r="F57" s="57" t="s">
+      <c r="F57" s="41" t="s">
         <v>287</v>
       </c>
-      <c r="G57" s="57" t="s">
+      <c r="G57" s="41" t="s">
         <v>50</v>
       </c>
-      <c r="H57" s="57" t="s">
+      <c r="H57" s="41" t="s">
         <v>344</v>
       </c>
-      <c r="I57" s="57" t="s">
+      <c r="I57" s="41" t="s">
         <v>306</v>
       </c>
-      <c r="J57" s="57" t="s">
+      <c r="J57" s="41" t="s">
         <v>338</v>
       </c>
-      <c r="K57" s="57" t="s">
+      <c r="K57" s="41" t="s">
         <v>57</v>
       </c>
-      <c r="L57" s="57" t="s">
-        <v>375</v>
-      </c>
-      <c r="M57" s="57" t="s">
+      <c r="L57" s="41" t="s">
+        <v>374</v>
+      </c>
+      <c r="M57" s="41" t="s">
         <v>239</v>
       </c>
-      <c r="N57" s="57" t="s">
+      <c r="N57" s="41" t="s">
         <v>23</v>
       </c>
-      <c r="O57" s="57" t="s">
+      <c r="O57" s="41" t="s">
         <v>332</v>
       </c>
-      <c r="P57" s="57" t="s">
+      <c r="P57" s="41" t="s">
         <v>163</v>
       </c>
-      <c r="Q57" s="57" t="str">
+      <c r="Q57" s="41" t="str">
         <f>CHAR(10)</f>
         <v xml:space="preserve">
 </v>
@@ -9762,41 +9748,41 @@
     <row r="58" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B58" s="22"/>
       <c r="D58" s="24" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="E58" s="24" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="F58" s="24" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="G58" s="24" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="H58" s="24" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="I58" s="24" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="J58" s="24" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="K58" s="24" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="L58" s="24"/>
       <c r="M58" s="24" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="N58" s="24" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="O58" s="24" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="P58" s="24" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="Q58" s="24"/>
       <c r="R58" s="24"/>
@@ -9808,19 +9794,19 @@
       <c r="C59" s="34"/>
       <c r="D59" s="52"/>
       <c r="E59" s="52" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="F59" s="52"/>
       <c r="G59" s="52"/>
       <c r="H59" s="52"/>
       <c r="I59" s="52"/>
       <c r="J59" s="52" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="K59" s="52"/>
       <c r="L59" s="52"/>
       <c r="M59" s="52" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="N59" s="52"/>
       <c r="O59" s="52"/>
@@ -9835,38 +9821,38 @@
         <v>125</v>
       </c>
       <c r="E60" s="18" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="F60" s="18" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="G60" s="18" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H60" s="18" t="s">
         <v>132</v>
       </c>
       <c r="I60" s="18"/>
       <c r="J60" s="18" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="K60" s="18" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="L60" s="18" t="s">
         <v>134</v>
       </c>
       <c r="M60" s="18" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="N60" s="18" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="O60" s="18" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="P60" s="18" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="Q60" s="18"/>
       <c r="R60" s="18"/>
@@ -9878,46 +9864,46 @@
         <f>B57+1</f>
         <v>15</v>
       </c>
-      <c r="D61" s="57" t="s">
+      <c r="D61" s="41" t="s">
         <v>49</v>
       </c>
-      <c r="E61" s="57" t="s">
+      <c r="E61" s="41" t="s">
         <v>288</v>
       </c>
-      <c r="F61" s="57" t="s">
+      <c r="F61" s="41" t="s">
         <v>203</v>
       </c>
-      <c r="G61" s="57" t="s">
+      <c r="G61" s="41" t="s">
         <v>306</v>
       </c>
-      <c r="H61" s="57" t="s">
+      <c r="H61" s="41" t="s">
         <v>57</v>
       </c>
-      <c r="I61" s="57" t="s">
-        <v>375</v>
-      </c>
-      <c r="J61" s="57" t="s">
+      <c r="I61" s="41" t="s">
+        <v>374</v>
+      </c>
+      <c r="J61" s="41" t="s">
         <v>288</v>
       </c>
-      <c r="K61" s="57" t="s">
+      <c r="K61" s="41" t="s">
         <v>203</v>
       </c>
-      <c r="L61" s="57" t="s">
+      <c r="L61" s="41" t="s">
         <v>303</v>
       </c>
-      <c r="M61" s="57" t="s">
+      <c r="M61" s="41" t="s">
         <v>344</v>
       </c>
-      <c r="N61" s="57" t="s">
+      <c r="N61" s="41" t="s">
         <v>306</v>
       </c>
-      <c r="O61" s="57" t="s">
+      <c r="O61" s="41" t="s">
         <v>169</v>
       </c>
-      <c r="P61" s="57" t="s">
+      <c r="P61" s="41" t="s">
         <v>249</v>
       </c>
-      <c r="Q61" s="57" t="str">
+      <c r="Q61" s="41" t="str">
         <f>CHAR(10)</f>
         <v xml:space="preserve">
 </v>
@@ -9929,41 +9915,41 @@
     <row r="62" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B62" s="22"/>
       <c r="D62" s="24" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="E62" s="24" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="F62" s="24" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="G62" s="24" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H62" s="24" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="I62" s="24"/>
       <c r="J62" s="24" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="K62" s="24" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="L62" s="24" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="M62" s="24" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="N62" s="24" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="O62" s="24" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="P62" s="24" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="Q62" s="24"/>
       <c r="R62" s="24"/>
@@ -9975,7 +9961,7 @@
       <c r="C63" s="34"/>
       <c r="D63" s="52"/>
       <c r="E63" s="52" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F63" s="52"/>
       <c r="G63" s="52"/>
@@ -9998,25 +9984,25 @@
         <v>138</v>
       </c>
       <c r="E64" s="18" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="F64" s="18" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="G64" s="18" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="H64" s="18" t="s">
         <v>129</v>
       </c>
       <c r="I64" s="18" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="J64" s="18" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="K64" s="18" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="L64" s="18"/>
       <c r="M64" s="18"/>
@@ -10033,31 +10019,31 @@
         <f>B61+1</f>
         <v>16</v>
       </c>
-      <c r="D65" s="57" t="s">
+      <c r="D65" s="41" t="s">
         <v>24</v>
       </c>
-      <c r="E65" s="57" t="s">
+      <c r="E65" s="41" t="s">
         <v>298</v>
       </c>
-      <c r="F65" s="57" t="s">
+      <c r="F65" s="41" t="s">
         <v>321</v>
       </c>
-      <c r="G65" s="57" t="s">
+      <c r="G65" s="41" t="s">
         <v>349</v>
       </c>
-      <c r="H65" s="57" t="s">
+      <c r="H65" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="I65" s="57" t="s">
+      <c r="I65" s="41" t="s">
         <v>252</v>
       </c>
-      <c r="J65" s="57" t="s">
+      <c r="J65" s="41" t="s">
         <v>171</v>
       </c>
-      <c r="K65" s="57" t="s">
+      <c r="K65" s="41" t="s">
         <v>225</v>
       </c>
-      <c r="L65" s="57" t="str">
+      <c r="L65" s="41" t="str">
         <f>CHAR(10)</f>
         <v xml:space="preserve">
 </v>
@@ -10074,28 +10060,28 @@
     <row r="66" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B66" s="22"/>
       <c r="D66" s="24" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="E66" s="24" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="F66" s="24" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="G66" s="24" t="s">
+        <v>603</v>
+      </c>
+      <c r="H66" s="24" t="s">
         <v>604</v>
       </c>
-      <c r="H66" s="24" t="s">
-        <v>605</v>
-      </c>
       <c r="I66" s="24" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="J66" s="24" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="K66" s="24" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="L66" s="24"/>
       <c r="M66" s="24"/>
@@ -10112,20 +10098,20 @@
       <c r="C67" s="34"/>
       <c r="D67" s="52"/>
       <c r="E67" s="52" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F67" s="52"/>
       <c r="G67" s="52"/>
       <c r="H67" s="52"/>
       <c r="I67" s="52"/>
       <c r="J67" s="52" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="K67" s="52"/>
       <c r="L67" s="52"/>
       <c r="M67" s="52"/>
       <c r="N67" s="52" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="O67" s="52"/>
       <c r="P67" s="52"/>
@@ -10139,20 +10125,20 @@
         <v>125</v>
       </c>
       <c r="E68" s="18" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="F68" s="18" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="G68" s="18" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H68" s="18" t="s">
         <v>132</v>
       </c>
       <c r="I68" s="18"/>
       <c r="J68" s="18" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="K68" s="18" t="s">
         <v>118</v>
@@ -10164,7 +10150,7 @@
         <v>127</v>
       </c>
       <c r="N68" s="18" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="O68" s="18"/>
       <c r="P68" s="18"/>
@@ -10178,40 +10164,40 @@
         <f>B65+1</f>
         <v>17</v>
       </c>
-      <c r="D69" s="57" t="s">
+      <c r="D69" s="41" t="s">
         <v>49</v>
       </c>
-      <c r="E69" s="57" t="s">
+      <c r="E69" s="41" t="s">
         <v>288</v>
       </c>
-      <c r="F69" s="57" t="s">
+      <c r="F69" s="41" t="s">
         <v>203</v>
       </c>
-      <c r="G69" s="57" t="s">
+      <c r="G69" s="41" t="s">
         <v>306</v>
       </c>
-      <c r="H69" s="57" t="s">
+      <c r="H69" s="41" t="s">
         <v>57</v>
       </c>
-      <c r="I69" s="57" t="s">
-        <v>375</v>
-      </c>
-      <c r="J69" s="57" t="s">
+      <c r="I69" s="41" t="s">
+        <v>374</v>
+      </c>
+      <c r="J69" s="41" t="s">
         <v>288</v>
       </c>
-      <c r="K69" s="57" t="s">
+      <c r="K69" s="41" t="s">
         <v>53</v>
       </c>
-      <c r="L69" s="57" t="s">
+      <c r="L69" s="41" t="s">
         <v>43</v>
       </c>
-      <c r="M69" s="57" t="s">
-        <v>734</v>
-      </c>
-      <c r="N69" s="57" t="s">
+      <c r="M69" s="41" t="s">
+        <v>733</v>
+      </c>
+      <c r="N69" s="41" t="s">
         <v>270</v>
       </c>
-      <c r="O69" s="57" t="str">
+      <c r="O69" s="41" t="str">
         <f>CHAR(10)</f>
         <v xml:space="preserve">
 </v>
@@ -10225,35 +10211,35 @@
     <row r="70" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B70" s="22"/>
       <c r="D70" s="24" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="E70" s="24" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="F70" s="24" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="G70" s="24" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H70" s="24" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="I70" s="24"/>
       <c r="J70" s="24" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="K70" s="24" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="L70" s="24" t="s">
+        <v>609</v>
+      </c>
+      <c r="M70" s="24" t="s">
         <v>610</v>
       </c>
-      <c r="M70" s="24" t="s">
-        <v>611</v>
-      </c>
       <c r="N70" s="24" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="O70" s="24"/>
       <c r="P70" s="24"/>
@@ -10273,7 +10259,7 @@
       <c r="G71" s="52"/>
       <c r="H71" s="52"/>
       <c r="I71" s="52" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="J71" s="52"/>
       <c r="K71" s="52"/>
@@ -10292,28 +10278,28 @@
         <v>133</v>
       </c>
       <c r="E72" s="18" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="F72" s="18" t="s">
         <v>142</v>
       </c>
       <c r="G72" s="18" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="H72" s="18" t="s">
         <v>362</v>
       </c>
       <c r="I72" s="18" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="J72" s="18" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="K72" s="18" t="s">
         <v>116</v>
       </c>
       <c r="L72" s="18" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="M72" s="18"/>
       <c r="N72" s="18"/>
@@ -10329,34 +10315,34 @@
         <f>B69+1</f>
         <v>18</v>
       </c>
-      <c r="D73" s="57" t="s">
+      <c r="D73" s="41" t="s">
         <v>228</v>
       </c>
-      <c r="E73" s="57" t="s">
+      <c r="E73" s="41" t="s">
         <v>314</v>
       </c>
-      <c r="F73" s="57" t="s">
+      <c r="F73" s="41" t="s">
         <v>23</v>
       </c>
-      <c r="G73" s="57" t="s">
+      <c r="G73" s="41" t="s">
         <v>209</v>
       </c>
-      <c r="H73" s="57" t="s">
+      <c r="H73" s="41" t="s">
         <v>18</v>
       </c>
-      <c r="I73" s="57" t="s">
-        <v>681</v>
-      </c>
-      <c r="J73" s="57" t="s">
+      <c r="I73" s="41" t="s">
+        <v>680</v>
+      </c>
+      <c r="J73" s="41" t="s">
         <v>306</v>
       </c>
-      <c r="K73" s="57" t="s">
+      <c r="K73" s="41" t="s">
         <v>22</v>
       </c>
-      <c r="L73" s="57" t="s">
+      <c r="L73" s="41" t="s">
         <v>309</v>
       </c>
-      <c r="M73" s="57" t="str">
+      <c r="M73" s="41" t="str">
         <f>CHAR(10)</f>
         <v xml:space="preserve">
 </v>
@@ -10372,31 +10358,31 @@
     <row r="74" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B74" s="22"/>
       <c r="D74" s="24" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="E74" s="24" t="s">
+        <v>612</v>
+      </c>
+      <c r="F74" s="24" t="s">
+        <v>565</v>
+      </c>
+      <c r="G74" s="24" t="s">
+        <v>549</v>
+      </c>
+      <c r="H74" s="24" t="s">
         <v>613</v>
       </c>
-      <c r="F74" s="24" t="s">
-        <v>566</v>
-      </c>
-      <c r="G74" s="24" t="s">
-        <v>550</v>
-      </c>
-      <c r="H74" s="24" t="s">
-        <v>614</v>
-      </c>
       <c r="I74" s="24" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="J74" s="24" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="K74" s="24" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="L74" s="24" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="M74" s="24"/>
       <c r="N74" s="24"/>
@@ -10411,19 +10397,19 @@
       <c r="B75" s="12"/>
       <c r="C75" s="34"/>
       <c r="D75" s="52" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="E75" s="52"/>
       <c r="F75" s="52"/>
       <c r="G75" s="52"/>
       <c r="H75" s="52"/>
       <c r="I75" s="52" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="J75" s="52"/>
       <c r="K75" s="52"/>
       <c r="L75" s="52" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="M75" s="52"/>
       <c r="N75" s="52"/>
@@ -10436,25 +10422,25 @@
     <row r="76" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B76" s="17"/>
       <c r="D76" s="18" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="E76" s="18" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="F76" s="18" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="G76" s="18" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="H76" s="18" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="I76" s="18" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="J76" s="18" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="K76" s="18" t="s">
         <v>122</v>
@@ -10476,34 +10462,34 @@
         <f>B73+1</f>
         <v>19</v>
       </c>
-      <c r="D77" s="57" t="s">
+      <c r="D77" s="41" t="s">
         <v>292</v>
       </c>
-      <c r="E77" s="57" t="s">
+      <c r="E77" s="41" t="s">
         <v>326</v>
       </c>
-      <c r="F77" s="57" t="s">
-        <v>374</v>
-      </c>
-      <c r="G77" s="57" t="s">
+      <c r="F77" s="41" t="s">
+        <v>373</v>
+      </c>
+      <c r="G77" s="41" t="s">
         <v>287</v>
       </c>
-      <c r="H77" s="57" t="s">
+      <c r="H77" s="41" t="s">
         <v>354</v>
       </c>
-      <c r="I77" s="57" t="s">
+      <c r="I77" s="41" t="s">
         <v>22</v>
       </c>
-      <c r="J77" s="57" t="s">
+      <c r="J77" s="41" t="s">
         <v>221</v>
       </c>
-      <c r="K77" s="57" t="s">
+      <c r="K77" s="41" t="s">
         <v>45</v>
       </c>
-      <c r="L77" s="57" t="s">
+      <c r="L77" s="41" t="s">
         <v>63</v>
       </c>
-      <c r="M77" s="57" t="str">
+      <c r="M77" s="41" t="str">
         <f>CHAR(10)</f>
         <v xml:space="preserve">
 </v>
@@ -10519,31 +10505,31 @@
     <row r="78" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B78" s="22"/>
       <c r="D78" s="24" t="s">
+        <v>701</v>
+      </c>
+      <c r="E78" s="24" t="s">
+        <v>509</v>
+      </c>
+      <c r="F78" s="24" t="s">
+        <v>511</v>
+      </c>
+      <c r="G78" s="24" t="s">
+        <v>505</v>
+      </c>
+      <c r="H78" s="24" t="s">
+        <v>557</v>
+      </c>
+      <c r="I78" s="24" t="s">
+        <v>693</v>
+      </c>
+      <c r="J78" s="24" t="s">
+        <v>559</v>
+      </c>
+      <c r="K78" s="24" t="s">
+        <v>560</v>
+      </c>
+      <c r="L78" s="24" t="s">
         <v>702</v>
-      </c>
-      <c r="E78" s="24" t="s">
-        <v>510</v>
-      </c>
-      <c r="F78" s="24" t="s">
-        <v>512</v>
-      </c>
-      <c r="G78" s="24" t="s">
-        <v>506</v>
-      </c>
-      <c r="H78" s="24" t="s">
-        <v>558</v>
-      </c>
-      <c r="I78" s="24" t="s">
-        <v>694</v>
-      </c>
-      <c r="J78" s="24" t="s">
-        <v>560</v>
-      </c>
-      <c r="K78" s="24" t="s">
-        <v>561</v>
-      </c>
-      <c r="L78" s="24" t="s">
-        <v>703</v>
       </c>
       <c r="M78" s="24"/>
       <c r="N78" s="24"/>
@@ -10559,18 +10545,18 @@
       <c r="C79" s="34"/>
       <c r="D79" s="52"/>
       <c r="E79" s="52" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F79" s="52"/>
       <c r="G79" s="52"/>
       <c r="H79" s="52"/>
       <c r="I79" s="52" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="J79" s="52"/>
       <c r="K79" s="52"/>
       <c r="L79" s="52" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="M79" s="52"/>
       <c r="N79" s="52"/>
@@ -10583,31 +10569,31 @@
     <row r="80" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B80" s="17"/>
       <c r="D80" s="18" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="E80" s="18" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="F80" s="18" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="G80" s="18" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="H80" s="18" t="s">
         <v>142</v>
       </c>
       <c r="I80" s="18" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="J80" s="18" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="K80" s="18" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="L80" s="18" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="M80" s="18"/>
       <c r="N80" s="18"/>
@@ -10623,34 +10609,34 @@
         <f>B77+1</f>
         <v>20</v>
       </c>
-      <c r="D81" s="57" t="s">
+      <c r="D81" s="41" t="s">
         <v>247</v>
       </c>
-      <c r="E81" s="57" t="s">
+      <c r="E81" s="41" t="s">
         <v>22</v>
       </c>
-      <c r="F81" s="57" t="s">
+      <c r="F81" s="41" t="s">
         <v>267</v>
       </c>
-      <c r="G81" s="57" t="s">
+      <c r="G81" s="41" t="s">
         <v>333</v>
       </c>
-      <c r="H81" s="57" t="s">
+      <c r="H81" s="41" t="s">
         <v>23</v>
       </c>
-      <c r="I81" s="57" t="s">
+      <c r="I81" s="41" t="s">
         <v>322</v>
       </c>
-      <c r="J81" s="57" t="s">
+      <c r="J81" s="41" t="s">
         <v>287</v>
       </c>
-      <c r="K81" s="57" t="s">
+      <c r="K81" s="41" t="s">
         <v>306</v>
       </c>
-      <c r="L81" s="57" t="s">
+      <c r="L81" s="41" t="s">
         <v>193</v>
       </c>
-      <c r="M81" s="57" t="str">
+      <c r="M81" s="41" t="str">
         <f>CHAR(10)</f>
         <v xml:space="preserve">
 </v>
@@ -10666,31 +10652,31 @@
     <row r="82" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B82" s="22"/>
       <c r="D82" s="24" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="E82" s="24" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="F82" s="24" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="G82" s="24" t="s">
+        <v>564</v>
+      </c>
+      <c r="H82" s="24" t="s">
         <v>565</v>
       </c>
-      <c r="H82" s="24" t="s">
-        <v>566</v>
-      </c>
       <c r="I82" s="24" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="J82" s="24" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="K82" s="24" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="L82" s="24" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="M82" s="24"/>
       <c r="N82" s="24"/>
@@ -10705,26 +10691,26 @@
       <c r="B83" s="12"/>
       <c r="C83" s="34"/>
       <c r="D83" s="52" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="E83" s="52" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F83" s="52" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="G83" s="52"/>
       <c r="H83" s="52"/>
       <c r="I83" s="52"/>
       <c r="J83" s="52"/>
       <c r="K83" s="52" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="L83" s="52" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="M83" s="52" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="N83" s="52"/>
       <c r="O83" s="52"/>
@@ -10736,35 +10722,35 @@
     <row r="84" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B84" s="17"/>
       <c r="D84" s="18" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="E84" s="18" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="F84" s="18" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="G84" s="18" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="H84" s="18" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="I84" s="18" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="J84" s="18"/>
       <c r="K84" s="18" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="L84" s="18" t="s">
         <v>124</v>
       </c>
       <c r="M84" s="18" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="N84" s="18" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="O84" s="18"/>
       <c r="P84" s="18"/>
@@ -10778,40 +10764,40 @@
         <f>B81+1</f>
         <v>21</v>
       </c>
-      <c r="D85" s="57" t="s">
+      <c r="D85" s="41" t="s">
         <v>55</v>
       </c>
-      <c r="E85" s="57" t="s">
+      <c r="E85" s="41" t="s">
         <v>22</v>
       </c>
-      <c r="F85" s="58" t="s">
-        <v>732</v>
-      </c>
-      <c r="G85" s="57" t="s">
+      <c r="F85" s="57" t="s">
+        <v>731</v>
+      </c>
+      <c r="G85" s="41" t="s">
         <v>347</v>
       </c>
-      <c r="H85" s="57" t="s">
+      <c r="H85" s="41" t="s">
         <v>238</v>
       </c>
-      <c r="I85" s="57" t="s">
+      <c r="I85" s="41" t="s">
         <v>62</v>
       </c>
-      <c r="J85" s="57" t="s">
-        <v>375</v>
-      </c>
-      <c r="K85" s="57" t="s">
+      <c r="J85" s="41" t="s">
+        <v>374</v>
+      </c>
+      <c r="K85" s="41" t="s">
         <v>307</v>
       </c>
-      <c r="L85" s="57" t="s">
+      <c r="L85" s="41" t="s">
         <v>48</v>
       </c>
-      <c r="M85" s="57" t="s">
+      <c r="M85" s="41" t="s">
         <v>307</v>
       </c>
-      <c r="N85" s="57" t="s">
+      <c r="N85" s="41" t="s">
         <v>357</v>
       </c>
-      <c r="O85" s="57" t="str">
+      <c r="O85" s="41" t="str">
         <f>CHAR(10)</f>
         <v xml:space="preserve">
 </v>
@@ -10829,35 +10815,35 @@
     <row r="86" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B86" s="22"/>
       <c r="D86" s="24" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="E86" s="24" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="F86" s="24" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="G86" s="24" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H86" s="24" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="I86" s="24" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="J86" s="24"/>
       <c r="K86" s="24" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="L86" s="24" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="M86" s="24" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="N86" s="24" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="O86" s="24"/>
       <c r="P86" s="24"/>
@@ -10873,14 +10859,14 @@
       <c r="E87" s="52"/>
       <c r="F87" s="52"/>
       <c r="G87" s="52" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="H87" s="52"/>
       <c r="I87" s="52" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="J87" s="52" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="K87" s="52"/>
       <c r="L87" s="52"/>
@@ -10898,37 +10884,37 @@
         <v>129</v>
       </c>
       <c r="E88" s="18" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="F88" s="18" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="G88" s="18" t="s">
+        <v>673</v>
+      </c>
+      <c r="H88" s="18" t="s">
+        <v>532</v>
+      </c>
+      <c r="I88" s="18" t="s">
         <v>674</v>
       </c>
-      <c r="H88" s="18" t="s">
-        <v>533</v>
-      </c>
-      <c r="I88" s="18" t="s">
+      <c r="J88" s="18" t="s">
         <v>675</v>
       </c>
-      <c r="J88" s="18" t="s">
-        <v>676</v>
-      </c>
       <c r="K88" s="18" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="L88" s="18" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="M88" s="18" t="s">
         <v>140</v>
       </c>
       <c r="N88" s="18" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="O88" s="18" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="P88" s="18"/>
       <c r="Q88" s="18"/>
@@ -10941,43 +10927,43 @@
         <f>B85+1</f>
         <v>22</v>
       </c>
-      <c r="D89" s="57" t="s">
+      <c r="D89" s="41" t="s">
         <v>226</v>
       </c>
-      <c r="E89" s="57" t="s">
+      <c r="E89" s="41" t="s">
         <v>228</v>
       </c>
-      <c r="F89" s="57" t="s">
+      <c r="F89" s="41" t="s">
         <v>44</v>
       </c>
-      <c r="G89" s="57" t="s">
+      <c r="G89" s="41" t="s">
         <v>237</v>
       </c>
-      <c r="H89" s="57" t="s">
+      <c r="H89" s="41" t="s">
         <v>232</v>
       </c>
-      <c r="I89" s="57" t="s">
+      <c r="I89" s="41" t="s">
         <v>300</v>
       </c>
-      <c r="J89" s="57" t="s">
+      <c r="J89" s="41" t="s">
         <v>25</v>
       </c>
-      <c r="K89" s="57" t="s">
+      <c r="K89" s="41" t="s">
         <v>306</v>
       </c>
-      <c r="L89" s="57" t="s">
+      <c r="L89" s="41" t="s">
         <v>290</v>
       </c>
-      <c r="M89" s="57" t="s">
+      <c r="M89" s="41" t="s">
         <v>220</v>
       </c>
-      <c r="N89" s="57" t="s">
+      <c r="N89" s="41" t="s">
         <v>203</v>
       </c>
-      <c r="O89" s="57" t="s">
+      <c r="O89" s="41" t="s">
         <v>339</v>
       </c>
-      <c r="P89" s="57" t="str">
+      <c r="P89" s="41" t="str">
         <f>CHAR(10)</f>
         <v xml:space="preserve">
 </v>
@@ -10990,40 +10976,40 @@
     <row r="90" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B90" s="22"/>
       <c r="D90" s="24" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="E90" s="24" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="F90" s="24" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="G90" s="24" t="s">
+        <v>706</v>
+      </c>
+      <c r="H90" s="24" t="s">
+        <v>533</v>
+      </c>
+      <c r="I90" s="24" t="s">
         <v>707</v>
       </c>
-      <c r="H90" s="24" t="s">
-        <v>534</v>
-      </c>
-      <c r="I90" s="24" t="s">
+      <c r="J90" s="24" t="s">
         <v>708</v>
       </c>
-      <c r="J90" s="24" t="s">
-        <v>709</v>
-      </c>
       <c r="K90" s="24" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="L90" s="24" t="s">
+        <v>577</v>
+      </c>
+      <c r="M90" s="24" t="s">
         <v>578</v>
       </c>
-      <c r="M90" s="24" t="s">
-        <v>579</v>
-      </c>
       <c r="N90" s="24" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="O90" s="24" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="P90" s="24"/>
       <c r="Q90" s="24"/>
@@ -11044,10 +11030,10 @@
       <c r="K91" s="52"/>
       <c r="L91" s="52"/>
       <c r="M91" s="52" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="N91" s="52" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="O91" s="52"/>
       <c r="P91" s="52"/>
@@ -11058,32 +11044,32 @@
     <row r="92" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B92" s="17"/>
       <c r="D92" s="18" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="E92" s="18" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="F92" s="18" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="G92" s="18" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H92" s="18" t="s">
         <v>135</v>
       </c>
       <c r="I92" s="18"/>
       <c r="J92" s="18" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="K92" s="18" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="L92" s="18" t="s">
         <v>134</v>
       </c>
       <c r="M92" s="18" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="N92" s="18" t="s">
         <v>137</v>
@@ -11100,40 +11086,40 @@
         <f>B89+1</f>
         <v>23</v>
       </c>
-      <c r="D93" s="57" t="s">
+      <c r="D93" s="41" t="s">
         <v>170</v>
       </c>
-      <c r="E93" s="57" t="s">
+      <c r="E93" s="41" t="s">
         <v>293</v>
       </c>
-      <c r="F93" s="57" t="s">
+      <c r="F93" s="41" t="s">
         <v>306</v>
       </c>
-      <c r="G93" s="57" t="s">
+      <c r="G93" s="41" t="s">
         <v>217</v>
       </c>
-      <c r="H93" s="57" t="s">
+      <c r="H93" s="41" t="s">
         <v>58</v>
       </c>
-      <c r="I93" s="57" t="s">
-        <v>375</v>
-      </c>
-      <c r="J93" s="57" t="s">
+      <c r="I93" s="41" t="s">
+        <v>374</v>
+      </c>
+      <c r="J93" s="41" t="s">
         <v>253</v>
       </c>
-      <c r="K93" s="57" t="s">
+      <c r="K93" s="41" t="s">
         <v>217</v>
       </c>
-      <c r="L93" s="57" t="s">
+      <c r="L93" s="41" t="s">
         <v>334</v>
       </c>
-      <c r="M93" s="57" t="s">
+      <c r="M93" s="41" t="s">
         <v>322</v>
       </c>
-      <c r="N93" s="57" t="s">
+      <c r="N93" s="41" t="s">
         <v>63</v>
       </c>
-      <c r="O93" s="57" t="str">
+      <c r="O93" s="41" t="str">
         <f>CHAR(10)</f>
         <v xml:space="preserve">
 </v>
@@ -11147,35 +11133,35 @@
     <row r="94" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B94" s="22"/>
       <c r="D94" s="24" t="s">
+        <v>709</v>
+      </c>
+      <c r="E94" s="24" t="s">
+        <v>582</v>
+      </c>
+      <c r="F94" s="24" t="s">
+        <v>522</v>
+      </c>
+      <c r="G94" s="24" t="s">
+        <v>584</v>
+      </c>
+      <c r="H94" s="24" t="s">
         <v>710</v>
-      </c>
-      <c r="E94" s="24" t="s">
-        <v>583</v>
-      </c>
-      <c r="F94" s="24" t="s">
-        <v>523</v>
-      </c>
-      <c r="G94" s="24" t="s">
-        <v>585</v>
-      </c>
-      <c r="H94" s="24" t="s">
-        <v>711</v>
       </c>
       <c r="I94" s="24"/>
       <c r="J94" s="24" t="s">
+        <v>586</v>
+      </c>
+      <c r="K94" s="24" t="s">
+        <v>584</v>
+      </c>
+      <c r="L94" s="24" t="s">
         <v>587</v>
       </c>
-      <c r="K94" s="24" t="s">
-        <v>585</v>
-      </c>
-      <c r="L94" s="24" t="s">
-        <v>588</v>
-      </c>
       <c r="M94" s="24" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="N94" s="24" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="O94" s="24"/>
       <c r="P94" s="24"/>
@@ -11188,24 +11174,24 @@
       <c r="B95" s="12"/>
       <c r="C95" s="34"/>
       <c r="D95" s="52" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="E95" s="52" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F95" s="52"/>
       <c r="G95" s="52" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="H95" s="52" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="I95" s="52"/>
       <c r="J95" s="52"/>
       <c r="K95" s="52"/>
       <c r="L95" s="52"/>
       <c r="M95" s="52" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="N95" s="52"/>
       <c r="O95" s="52"/>
@@ -11217,41 +11203,41 @@
     <row r="96" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B96" s="17"/>
       <c r="D96" s="18" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="E96" s="18" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="F96" s="18" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="G96" s="18" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="H96" s="18" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="I96" s="18" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="J96" s="18" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="K96" s="18" t="s">
         <v>132</v>
       </c>
       <c r="L96" s="18"/>
       <c r="M96" s="18" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="N96" s="18" t="s">
         <v>142</v>
       </c>
       <c r="O96" s="18" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="P96" s="18" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="Q96" s="18"/>
       <c r="R96" s="18"/>
@@ -11263,46 +11249,46 @@
         <f>B93+1</f>
         <v>24</v>
       </c>
-      <c r="D97" s="57" t="s">
+      <c r="D97" s="41" t="s">
         <v>50</v>
       </c>
-      <c r="E97" s="57" t="s">
+      <c r="E97" s="41" t="s">
         <v>344</v>
       </c>
-      <c r="F97" s="57" t="s">
+      <c r="F97" s="41" t="s">
         <v>287</v>
       </c>
-      <c r="G97" s="57" t="s">
+      <c r="G97" s="41" t="s">
         <v>50</v>
       </c>
-      <c r="H97" s="57" t="s">
+      <c r="H97" s="41" t="s">
         <v>344</v>
       </c>
-      <c r="I97" s="57" t="s">
+      <c r="I97" s="41" t="s">
         <v>306</v>
       </c>
-      <c r="J97" s="57" t="s">
+      <c r="J97" s="41" t="s">
         <v>338</v>
       </c>
-      <c r="K97" s="57" t="s">
+      <c r="K97" s="41" t="s">
         <v>57</v>
       </c>
-      <c r="L97" s="57" t="s">
-        <v>375</v>
-      </c>
-      <c r="M97" s="57" t="s">
+      <c r="L97" s="41" t="s">
+        <v>374</v>
+      </c>
+      <c r="M97" s="41" t="s">
         <v>239</v>
       </c>
-      <c r="N97" s="57" t="s">
+      <c r="N97" s="41" t="s">
         <v>23</v>
       </c>
-      <c r="O97" s="57" t="s">
+      <c r="O97" s="41" t="s">
         <v>332</v>
       </c>
-      <c r="P97" s="57" t="s">
+      <c r="P97" s="41" t="s">
         <v>163</v>
       </c>
-      <c r="Q97" s="57" t="str">
+      <c r="Q97" s="41" t="str">
         <f>CHAR(10)</f>
         <v xml:space="preserve">
 </v>
@@ -11314,41 +11300,41 @@
     <row r="98" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B98" s="22"/>
       <c r="D98" s="24" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="E98" s="24" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="F98" s="24" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="G98" s="24" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="H98" s="24" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="I98" s="24" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="J98" s="24" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="K98" s="24" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="L98" s="24"/>
       <c r="M98" s="24" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="N98" s="24" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="O98" s="24" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="P98" s="24" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="Q98" s="24"/>
       <c r="R98" s="24"/>
@@ -11360,19 +11346,19 @@
       <c r="C99" s="34"/>
       <c r="D99" s="52"/>
       <c r="E99" s="52" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F99" s="52"/>
       <c r="G99" s="52"/>
       <c r="H99" s="52"/>
       <c r="I99" s="52"/>
       <c r="J99" s="52" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="K99" s="52"/>
       <c r="L99" s="52"/>
       <c r="M99" s="52" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="N99" s="52"/>
       <c r="O99" s="52"/>
@@ -11387,38 +11373,38 @@
         <v>125</v>
       </c>
       <c r="E100" s="18" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="F100" s="18" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="G100" s="18" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H100" s="18" t="s">
         <v>132</v>
       </c>
       <c r="I100" s="18"/>
       <c r="J100" s="18" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="K100" s="18" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="L100" s="18" t="s">
         <v>134</v>
       </c>
       <c r="M100" s="18" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="N100" s="18" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="O100" s="18" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="P100" s="18" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="Q100" s="18"/>
       <c r="R100" s="18"/>
@@ -11430,46 +11416,46 @@
         <f>B97+1</f>
         <v>25</v>
       </c>
-      <c r="D101" s="57" t="s">
+      <c r="D101" s="41" t="s">
         <v>49</v>
       </c>
-      <c r="E101" s="57" t="s">
+      <c r="E101" s="41" t="s">
         <v>288</v>
       </c>
-      <c r="F101" s="57" t="s">
+      <c r="F101" s="41" t="s">
         <v>203</v>
       </c>
-      <c r="G101" s="57" t="s">
+      <c r="G101" s="41" t="s">
         <v>306</v>
       </c>
-      <c r="H101" s="57" t="s">
+      <c r="H101" s="41" t="s">
         <v>57</v>
       </c>
-      <c r="I101" s="57" t="s">
-        <v>375</v>
-      </c>
-      <c r="J101" s="57" t="s">
+      <c r="I101" s="41" t="s">
+        <v>374</v>
+      </c>
+      <c r="J101" s="41" t="s">
         <v>288</v>
       </c>
-      <c r="K101" s="57" t="s">
+      <c r="K101" s="41" t="s">
         <v>203</v>
       </c>
-      <c r="L101" s="57" t="s">
+      <c r="L101" s="41" t="s">
         <v>303</v>
       </c>
-      <c r="M101" s="57" t="s">
+      <c r="M101" s="41" t="s">
         <v>344</v>
       </c>
-      <c r="N101" s="57" t="s">
+      <c r="N101" s="41" t="s">
         <v>306</v>
       </c>
-      <c r="O101" s="57" t="s">
+      <c r="O101" s="41" t="s">
         <v>169</v>
       </c>
-      <c r="P101" s="57" t="s">
+      <c r="P101" s="41" t="s">
         <v>249</v>
       </c>
-      <c r="Q101" s="57" t="str">
+      <c r="Q101" s="41" t="str">
         <f>CHAR(10)</f>
         <v xml:space="preserve">
 </v>
@@ -11481,41 +11467,41 @@
     <row r="102" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B102" s="22"/>
       <c r="D102" s="24" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="E102" s="24" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="F102" s="24" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="G102" s="24" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H102" s="24" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="I102" s="24"/>
       <c r="J102" s="24" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="K102" s="24" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="L102" s="24" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="M102" s="24" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="N102" s="24" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="O102" s="24" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="P102" s="24" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="Q102" s="24"/>
       <c r="R102" s="24"/>
@@ -11527,7 +11513,7 @@
       <c r="C103" s="34"/>
       <c r="D103" s="52"/>
       <c r="E103" s="52" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F103" s="52"/>
       <c r="G103" s="52"/>
@@ -11550,25 +11536,25 @@
         <v>138</v>
       </c>
       <c r="E104" s="18" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="F104" s="18" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="G104" s="18" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="H104" s="18" t="s">
         <v>129</v>
       </c>
       <c r="I104" s="18" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="J104" s="18" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="K104" s="18" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="L104" s="18"/>
       <c r="M104" s="18"/>
@@ -11585,31 +11571,31 @@
         <f>B101+1</f>
         <v>26</v>
       </c>
-      <c r="D105" s="57" t="s">
+      <c r="D105" s="41" t="s">
         <v>24</v>
       </c>
-      <c r="E105" s="57" t="s">
+      <c r="E105" s="41" t="s">
         <v>298</v>
       </c>
-      <c r="F105" s="57" t="s">
+      <c r="F105" s="41" t="s">
         <v>321</v>
       </c>
-      <c r="G105" s="59" t="s">
+      <c r="G105" s="42" t="s">
         <v>349</v>
       </c>
-      <c r="H105" s="57" t="s">
+      <c r="H105" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="I105" s="57" t="s">
+      <c r="I105" s="41" t="s">
         <v>252</v>
       </c>
-      <c r="J105" s="57" t="s">
+      <c r="J105" s="41" t="s">
         <v>171</v>
       </c>
-      <c r="K105" s="57" t="s">
+      <c r="K105" s="41" t="s">
         <v>225</v>
       </c>
-      <c r="L105" s="57" t="str">
+      <c r="L105" s="41" t="str">
         <f>CHAR(10)</f>
         <v xml:space="preserve">
 </v>
@@ -11626,28 +11612,28 @@
     <row r="106" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B106" s="22"/>
       <c r="D106" s="24" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="E106" s="24" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="F106" s="24" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="G106" s="24" t="s">
+        <v>603</v>
+      </c>
+      <c r="H106" s="24" t="s">
         <v>604</v>
       </c>
-      <c r="H106" s="24" t="s">
-        <v>605</v>
-      </c>
       <c r="I106" s="24" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="J106" s="24" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="K106" s="24" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="L106" s="24"/>
       <c r="M106" s="24"/>
@@ -11673,7 +11659,7 @@
       <c r="L107" s="52"/>
       <c r="M107" s="52"/>
       <c r="N107" s="52" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="O107" s="52"/>
       <c r="P107" s="52"/>
@@ -11687,20 +11673,20 @@
         <v>125</v>
       </c>
       <c r="E108" s="18" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="F108" s="18" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="G108" s="18" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H108" s="18" t="s">
         <v>132</v>
       </c>
       <c r="I108" s="18"/>
       <c r="J108" s="18" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="K108" s="18" t="s">
         <v>118</v>
@@ -11712,7 +11698,7 @@
         <v>127</v>
       </c>
       <c r="N108" s="18" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="O108" s="18"/>
       <c r="P108" s="18"/>
@@ -11726,40 +11712,40 @@
         <f>B105+1</f>
         <v>27</v>
       </c>
-      <c r="D109" s="57" t="s">
+      <c r="D109" s="41" t="s">
         <v>49</v>
       </c>
-      <c r="E109" s="57" t="s">
+      <c r="E109" s="41" t="s">
         <v>288</v>
       </c>
-      <c r="F109" s="57" t="s">
+      <c r="F109" s="41" t="s">
         <v>203</v>
       </c>
-      <c r="G109" s="57" t="s">
+      <c r="G109" s="41" t="s">
         <v>306</v>
       </c>
-      <c r="H109" s="57" t="s">
+      <c r="H109" s="41" t="s">
         <v>57</v>
       </c>
-      <c r="I109" s="57" t="s">
-        <v>375</v>
-      </c>
-      <c r="J109" s="57" t="s">
+      <c r="I109" s="41" t="s">
+        <v>374</v>
+      </c>
+      <c r="J109" s="41" t="s">
         <v>288</v>
       </c>
-      <c r="K109" s="57" t="s">
+      <c r="K109" s="41" t="s">
         <v>53</v>
       </c>
-      <c r="L109" s="57" t="s">
+      <c r="L109" s="41" t="s">
         <v>43</v>
       </c>
-      <c r="M109" s="57" t="s">
-        <v>734</v>
-      </c>
-      <c r="N109" s="57" t="s">
+      <c r="M109" s="41" t="s">
+        <v>733</v>
+      </c>
+      <c r="N109" s="41" t="s">
         <v>270</v>
       </c>
-      <c r="O109" s="57" t="str">
+      <c r="O109" s="41" t="str">
         <f>CHAR(10)</f>
         <v xml:space="preserve">
 </v>
@@ -11773,35 +11759,35 @@
     <row r="110" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B110" s="22"/>
       <c r="D110" s="24" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="E110" s="24" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="F110" s="24" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="G110" s="24" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H110" s="24" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="I110" s="24"/>
       <c r="J110" s="24" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="K110" s="24" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="L110" s="24" t="s">
+        <v>609</v>
+      </c>
+      <c r="M110" s="24" t="s">
         <v>610</v>
       </c>
-      <c r="M110" s="24" t="s">
-        <v>611</v>
-      </c>
       <c r="N110" s="24" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="O110" s="24"/>
       <c r="P110" s="24"/>
@@ -11821,7 +11807,7 @@
       <c r="G111" s="52"/>
       <c r="H111" s="52"/>
       <c r="I111" s="52" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="J111" s="52"/>
       <c r="K111" s="52"/>
@@ -11846,22 +11832,22 @@
         <v>142</v>
       </c>
       <c r="G112" s="18" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="H112" s="18" t="s">
         <v>362</v>
       </c>
       <c r="I112" s="18" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="J112" s="18" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="K112" s="18" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="L112" s="18" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="M112" s="18"/>
       <c r="N112" s="18"/>
@@ -11877,34 +11863,34 @@
         <f>B109+1</f>
         <v>28</v>
       </c>
-      <c r="D113" s="57" t="s">
+      <c r="D113" s="41" t="s">
         <v>272</v>
       </c>
-      <c r="E113" s="57" t="s">
+      <c r="E113" s="41" t="s">
         <v>41</v>
       </c>
-      <c r="F113" s="57" t="s">
+      <c r="F113" s="41" t="s">
         <v>23</v>
       </c>
-      <c r="G113" s="57" t="s">
+      <c r="G113" s="41" t="s">
         <v>209</v>
       </c>
-      <c r="H113" s="57" t="s">
+      <c r="H113" s="41" t="s">
         <v>18</v>
       </c>
-      <c r="I113" s="57" t="s">
-        <v>681</v>
-      </c>
-      <c r="J113" s="57" t="s">
+      <c r="I113" s="41" t="s">
+        <v>680</v>
+      </c>
+      <c r="J113" s="41" t="s">
         <v>306</v>
       </c>
-      <c r="K113" s="57" t="s">
+      <c r="K113" s="41" t="s">
         <v>302</v>
       </c>
-      <c r="L113" s="57" t="s">
+      <c r="L113" s="41" t="s">
         <v>309</v>
       </c>
-      <c r="M113" s="57" t="str">
+      <c r="M113" s="41" t="str">
         <f>CHAR(10)</f>
         <v xml:space="preserve">
 </v>
@@ -11920,31 +11906,31 @@
     <row r="114" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B114" s="22"/>
       <c r="D114" s="24" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="E114" s="24" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="F114" s="24" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="G114" s="24" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="H114" s="24" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="I114" s="24" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="J114" s="24" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="K114" s="24" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="L114" s="24" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="M114" s="24"/>
       <c r="N114" s="24"/>
@@ -11969,7 +11955,7 @@
       <c r="L115" s="52"/>
       <c r="M115" s="52"/>
       <c r="N115" s="52" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="O115" s="52"/>
       <c r="P115" s="52"/>
@@ -11983,38 +11969,38 @@
         <v>125</v>
       </c>
       <c r="E116" s="18" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="F116" s="18" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="G116" s="18" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H116" s="18" t="s">
         <v>132</v>
       </c>
       <c r="I116" s="18"/>
       <c r="J116" s="18" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="K116" s="18" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="L116" s="18" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="M116" s="18" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="N116" s="18" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="O116" s="18" t="s">
         <v>139</v>
       </c>
       <c r="P116" s="18" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="Q116" s="18"/>
       <c r="R116" s="18"/>
@@ -12026,46 +12012,46 @@
         <f>B113+1</f>
         <v>29</v>
       </c>
-      <c r="D117" s="57" t="s">
+      <c r="D117" s="41" t="s">
         <v>49</v>
       </c>
-      <c r="E117" s="57" t="s">
+      <c r="E117" s="41" t="s">
         <v>288</v>
       </c>
-      <c r="F117" s="59" t="s">
+      <c r="F117" s="42" t="s">
         <v>203</v>
       </c>
-      <c r="G117" s="59" t="s">
+      <c r="G117" s="42" t="s">
         <v>306</v>
       </c>
-      <c r="H117" s="57" t="s">
+      <c r="H117" s="41" t="s">
         <v>57</v>
       </c>
-      <c r="I117" s="57" t="s">
-        <v>375</v>
-      </c>
-      <c r="J117" s="57" t="s">
+      <c r="I117" s="41" t="s">
+        <v>374</v>
+      </c>
+      <c r="J117" s="41" t="s">
         <v>274</v>
       </c>
-      <c r="K117" s="57" t="s">
+      <c r="K117" s="41" t="s">
         <v>331</v>
       </c>
-      <c r="L117" s="57" t="s">
+      <c r="L117" s="41" t="s">
         <v>222</v>
       </c>
-      <c r="M117" s="57" t="s">
+      <c r="M117" s="41" t="s">
         <v>168</v>
       </c>
-      <c r="N117" s="57" t="s">
+      <c r="N117" s="41" t="s">
         <v>298</v>
       </c>
-      <c r="O117" s="57" t="s">
+      <c r="O117" s="41" t="s">
         <v>65</v>
       </c>
-      <c r="P117" s="57" t="s">
+      <c r="P117" s="41" t="s">
         <v>200</v>
       </c>
-      <c r="Q117" s="57" t="str">
+      <c r="Q117" s="41" t="str">
         <f>CHAR(10)</f>
         <v xml:space="preserve">
 </v>
@@ -12077,41 +12063,41 @@
     <row r="118" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B118" s="22"/>
       <c r="D118" s="24" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="E118" s="24" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="F118" s="24" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="G118" s="24" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H118" s="24" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="I118" s="24"/>
       <c r="J118" s="24" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="K118" s="24" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="L118" s="24" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="M118" s="24" t="s">
+        <v>621</v>
+      </c>
+      <c r="N118" s="24" t="s">
+        <v>748</v>
+      </c>
+      <c r="O118" s="24" t="s">
         <v>622</v>
       </c>
-      <c r="N118" s="24" t="s">
-        <v>749</v>
-      </c>
-      <c r="O118" s="24" t="s">
-        <v>623</v>
-      </c>
       <c r="P118" s="24" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="Q118" s="24"/>
       <c r="R118" s="24"/>
@@ -12123,19 +12109,19 @@
       <c r="C119" s="34"/>
       <c r="D119" s="52"/>
       <c r="E119" s="52" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="F119" s="52"/>
       <c r="G119" s="52" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="H119" s="52" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="I119" s="52"/>
       <c r="J119" s="52"/>
       <c r="K119" s="52" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="L119" s="52"/>
       <c r="M119" s="52"/>
@@ -12149,28 +12135,28 @@
     <row r="120" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B120" s="17"/>
       <c r="D120" s="18" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="E120" s="18" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="F120" s="18" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="G120" s="18" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="H120" s="18" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="I120" s="18" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="J120" s="18" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="K120" s="18" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="L120" s="18"/>
       <c r="M120" s="18"/>
@@ -12187,31 +12173,31 @@
         <f>B117+1</f>
         <v>30</v>
       </c>
-      <c r="D121" s="57" t="s">
+      <c r="D121" s="41" t="s">
         <v>265</v>
       </c>
-      <c r="E121" s="57" t="s">
+      <c r="E121" s="41" t="s">
         <v>38</v>
       </c>
-      <c r="F121" s="57" t="s">
+      <c r="F121" s="41" t="s">
         <v>214</v>
       </c>
-      <c r="G121" s="59" t="s">
+      <c r="G121" s="42" t="s">
         <v>25</v>
       </c>
-      <c r="H121" s="57" t="s">
+      <c r="H121" s="41" t="s">
         <v>55</v>
       </c>
-      <c r="I121" s="57" t="s">
+      <c r="I121" s="41" t="s">
         <v>342</v>
       </c>
-      <c r="J121" s="57" t="s">
+      <c r="J121" s="41" t="s">
         <v>301</v>
       </c>
-      <c r="K121" s="57" t="s">
+      <c r="K121" s="41" t="s">
         <v>213</v>
       </c>
-      <c r="L121" s="57" t="str">
+      <c r="L121" s="41" t="str">
         <f>CHAR(10)</f>
         <v xml:space="preserve">
 </v>
@@ -12228,28 +12214,28 @@
     <row r="122" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B122" s="22"/>
       <c r="D122" s="24" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="E122" s="24" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="F122" s="24" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="G122" s="24" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="H122" s="24" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="I122" s="24" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="J122" s="24" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="K122" s="24" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="L122" s="24"/>
       <c r="M122" s="24"/>
@@ -12275,7 +12261,7 @@
       <c r="L123" s="52"/>
       <c r="M123" s="52"/>
       <c r="N123" s="52" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="O123" s="52"/>
       <c r="P123" s="52"/>
@@ -12289,13 +12275,13 @@
         <v>125</v>
       </c>
       <c r="E124" s="18" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="F124" s="18" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="G124" s="18" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H124" s="18" t="s">
         <v>132</v>
@@ -12305,16 +12291,16 @@
         <v>142</v>
       </c>
       <c r="K124" s="18" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="L124" s="18" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="M124" s="18" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="N124" s="18" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="O124" s="18"/>
       <c r="P124" s="18"/>
@@ -12328,40 +12314,40 @@
         <f>B121+1</f>
         <v>31</v>
       </c>
-      <c r="D125" s="57" t="s">
+      <c r="D125" s="41" t="s">
         <v>49</v>
       </c>
-      <c r="E125" s="57" t="s">
+      <c r="E125" s="41" t="s">
         <v>288</v>
       </c>
-      <c r="F125" s="57" t="s">
+      <c r="F125" s="41" t="s">
         <v>203</v>
       </c>
-      <c r="G125" s="59" t="s">
+      <c r="G125" s="42" t="s">
         <v>306</v>
       </c>
-      <c r="H125" s="57" t="s">
+      <c r="H125" s="41" t="s">
         <v>57</v>
       </c>
-      <c r="I125" s="57" t="s">
-        <v>375</v>
-      </c>
-      <c r="J125" s="57" t="s">
+      <c r="I125" s="41" t="s">
+        <v>374</v>
+      </c>
+      <c r="J125" s="41" t="s">
         <v>23</v>
       </c>
-      <c r="K125" s="57" t="s">
+      <c r="K125" s="41" t="s">
         <v>209</v>
       </c>
-      <c r="L125" s="57" t="s">
+      <c r="L125" s="41" t="s">
         <v>306</v>
       </c>
-      <c r="M125" s="57" t="s">
+      <c r="M125" s="41" t="s">
         <v>343</v>
       </c>
-      <c r="N125" s="57" t="s">
+      <c r="N125" s="41" t="s">
         <v>205</v>
       </c>
-      <c r="O125" s="57" t="str">
+      <c r="O125" s="41" t="str">
         <f>CHAR(10)</f>
         <v xml:space="preserve">
 </v>
@@ -12375,35 +12361,35 @@
     <row r="126" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B126" s="22"/>
       <c r="D126" s="24" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="E126" s="24" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="F126" s="24" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="G126" s="24" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H126" s="24" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="I126" s="24"/>
       <c r="J126" s="24" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="K126" s="24" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="L126" s="24" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="M126" s="24" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="N126" s="24" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="O126" s="24"/>
       <c r="P126" s="24"/>
@@ -12419,7 +12405,7 @@
       <c r="E127" s="14"/>
       <c r="F127" s="14"/>
       <c r="G127" s="14" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="H127" s="14"/>
       <c r="I127" s="14" t="s">
@@ -12428,7 +12414,7 @@
       <c r="J127" s="14"/>
       <c r="K127" s="14"/>
       <c r="L127" s="14" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="M127" s="14"/>
       <c r="N127" s="14"/>
@@ -12441,7 +12427,7 @@
     <row r="128" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B128" s="17"/>
       <c r="D128" s="18" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="E128" s="18" t="s">
         <v>142</v>
@@ -12450,22 +12436,22 @@
         <v>128</v>
       </c>
       <c r="G128" s="18" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="H128" s="18" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="I128" s="18" t="s">
         <v>126</v>
       </c>
       <c r="J128" s="18" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="K128" s="18" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="L128" s="18" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="M128" s="18"/>
       <c r="N128" s="18"/>
@@ -12481,34 +12467,34 @@
         <f>B125+1</f>
         <v>32</v>
       </c>
-      <c r="D129" s="57" t="s">
+      <c r="D129" s="41" t="s">
         <v>351</v>
       </c>
-      <c r="E129" s="57" t="s">
+      <c r="E129" s="41" t="s">
         <v>23</v>
       </c>
-      <c r="F129" s="57" t="s">
+      <c r="F129" s="41" t="s">
         <v>19</v>
       </c>
-      <c r="G129" s="57" t="s">
+      <c r="G129" s="41" t="s">
         <v>25</v>
       </c>
-      <c r="H129" s="57" t="s">
+      <c r="H129" s="41" t="s">
         <v>235</v>
       </c>
-      <c r="I129" s="57" t="s">
+      <c r="I129" s="41" t="s">
         <v>67</v>
       </c>
-      <c r="J129" s="57" t="s">
+      <c r="J129" s="41" t="s">
         <v>251</v>
       </c>
-      <c r="K129" s="57" t="s">
+      <c r="K129" s="41" t="s">
         <v>337</v>
       </c>
-      <c r="L129" s="57" t="s">
+      <c r="L129" s="41" t="s">
         <v>50</v>
       </c>
-      <c r="M129" s="57" t="str">
+      <c r="M129" s="41" t="str">
         <f>CHAR(10)</f>
         <v xml:space="preserve">
 </v>
@@ -12524,31 +12510,31 @@
     <row r="130" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B130" s="22"/>
       <c r="D130" s="24" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="E130" s="24" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="F130" s="24" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="G130" s="24" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="H130" s="24" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="I130" s="24" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="J130" s="24" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="K130" s="24" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="L130" s="24" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="M130" s="24"/>
       <c r="N130" s="24"/>
@@ -12585,16 +12571,16 @@
         <v>125</v>
       </c>
       <c r="E132" s="18" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="F132" s="18" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="G132" s="18" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H132" s="18" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="I132" s="18"/>
       <c r="J132" s="18" t="s">
@@ -12604,13 +12590,13 @@
         <v>114</v>
       </c>
       <c r="L132" s="18" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="M132" s="18" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="N132" s="18" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="O132" s="18"/>
       <c r="P132" s="18"/>
@@ -12624,40 +12610,40 @@
         <f>B129+1</f>
         <v>33</v>
       </c>
-      <c r="D133" s="57" t="s">
+      <c r="D133" s="41" t="s">
         <v>49</v>
       </c>
-      <c r="E133" s="57" t="s">
+      <c r="E133" s="41" t="s">
         <v>288</v>
       </c>
-      <c r="F133" s="57" t="s">
+      <c r="F133" s="41" t="s">
         <v>203</v>
       </c>
-      <c r="G133" s="59" t="s">
+      <c r="G133" s="42" t="s">
         <v>306</v>
       </c>
-      <c r="H133" s="57" t="s">
+      <c r="H133" s="41" t="s">
         <v>311</v>
       </c>
-      <c r="I133" s="57" t="s">
-        <v>375</v>
-      </c>
-      <c r="J133" s="57" t="s">
+      <c r="I133" s="41" t="s">
+        <v>374</v>
+      </c>
+      <c r="J133" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="K133" s="57" t="s">
+      <c r="K133" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="L133" s="57" t="s">
+      <c r="L133" s="41" t="s">
         <v>39</v>
       </c>
-      <c r="M133" s="57" t="s">
+      <c r="M133" s="41" t="s">
         <v>212</v>
       </c>
-      <c r="N133" s="57" t="s">
+      <c r="N133" s="41" t="s">
         <v>165</v>
       </c>
-      <c r="O133" s="57" t="str">
+      <c r="O133" s="41" t="str">
         <f>CHAR(10)</f>
         <v xml:space="preserve">
 </v>
@@ -12671,35 +12657,35 @@
     <row r="134" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B134" s="22"/>
       <c r="D134" s="24" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="E134" s="24" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="F134" s="24" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="G134" s="24" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H134" s="24" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="I134" s="24"/>
       <c r="J134" s="24" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="K134" s="24" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="L134" s="24" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="M134" s="24" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="N134" s="24" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="O134" s="24"/>
       <c r="P134" s="24"/>
@@ -12734,28 +12720,28 @@
         <v>130</v>
       </c>
       <c r="E136" s="18" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="F136" s="18" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="G136" s="18" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="H136" s="18" t="s">
         <v>363</v>
       </c>
       <c r="I136" s="18" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="J136" s="18" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="K136" s="18" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="L136" s="18" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="M136" s="18"/>
       <c r="N136" s="18"/>
@@ -12771,34 +12757,34 @@
         <f>B133+1</f>
         <v>34</v>
       </c>
-      <c r="D137" s="57" t="s">
+      <c r="D137" s="41" t="s">
         <v>167</v>
       </c>
-      <c r="E137" s="57" t="s">
+      <c r="E137" s="41" t="s">
         <v>345</v>
       </c>
-      <c r="F137" s="57" t="s">
+      <c r="F137" s="41" t="s">
         <v>196</v>
       </c>
-      <c r="G137" s="57" t="s">
+      <c r="G137" s="41" t="s">
         <v>333</v>
       </c>
-      <c r="H137" s="57" t="s">
+      <c r="H137" s="41" t="s">
         <v>346</v>
       </c>
-      <c r="I137" s="57" t="s">
+      <c r="I137" s="41" t="s">
         <v>164</v>
       </c>
-      <c r="J137" s="57" t="s">
+      <c r="J137" s="41" t="s">
         <v>183</v>
       </c>
-      <c r="K137" s="57" t="s">
+      <c r="K137" s="41" t="s">
         <v>261</v>
       </c>
-      <c r="L137" s="57" t="s">
+      <c r="L137" s="41" t="s">
         <v>352</v>
       </c>
-      <c r="M137" s="57" t="str">
+      <c r="M137" s="41" t="str">
         <f>CHAR(10)</f>
         <v xml:space="preserve">
 </v>
@@ -12814,31 +12800,31 @@
     <row r="138" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B138" s="22"/>
       <c r="D138" s="24" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E138" s="24" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="F138" s="24" t="s">
+        <v>650</v>
+      </c>
+      <c r="G138" s="24" t="s">
+        <v>564</v>
+      </c>
+      <c r="H138" s="24" t="s">
         <v>651</v>
       </c>
-      <c r="G138" s="24" t="s">
-        <v>565</v>
-      </c>
-      <c r="H138" s="24" t="s">
-        <v>652</v>
-      </c>
       <c r="I138" s="24" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="J138" s="24" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="K138" s="24" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="L138" s="24" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="M138" s="24"/>
       <c r="N138" s="24"/>
@@ -12894,7 +12880,7 @@
         <f>B137+1</f>
         <v>35</v>
       </c>
-      <c r="D141" s="57" t="s">
+      <c r="D141" s="41" t="s">
         <v>26</v>
       </c>
       <c r="E141" s="41"/>
@@ -19676,291 +19662,283 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="D3:R3 D43:R43">
-    <cfRule type="expression" dxfId="71" priority="15">
+    <cfRule type="expression" dxfId="69" priority="15">
       <formula>顯示注音輸入</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="70" priority="16">
+    <cfRule type="expression" dxfId="68" priority="16">
       <formula>"'= TRUE(顯示注音輸入)"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D7:R7 D11:R11 D15:R15 D19:R19 D23:N23 D27:R27 D31:R31 D35:R35 D47:R47 D51:R51 E55:F55 D59:R59 D63:R63 D67:R67 D71:H71 D75:R75 D79:R79 P83:R83 D87:R87 D91:R91 P23:R23 H55:R55 D39:R39 J71:R71">
-    <cfRule type="expression" dxfId="69" priority="13">
+  <conditionalFormatting sqref="D7:R7 D11:R11 D15:R15 D19:R19 D27:R27 D31:R31 D35:R35 D39:R39 D47:R47 D51:R51 D59:R59 D63:R63 D67:R67 D75:R75 D79:R79 D87:R87 D91:R91">
+    <cfRule type="expression" dxfId="67" priority="13">
       <formula>顯示注音輸入</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="68" priority="14">
+    <cfRule type="expression" dxfId="66" priority="14">
+      <formula>"'= TRUE(顯示注音輸入)"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D23:R23">
+    <cfRule type="expression" dxfId="65" priority="7">
+      <formula>顯示注音輸入</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="64" priority="8">
+      <formula>"'= TRUE(顯示注音輸入)"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D55:R55">
+    <cfRule type="expression" dxfId="63" priority="3">
+      <formula>顯示注音輸入</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="62" priority="4">
+      <formula>"'= TRUE(顯示注音輸入)"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D71:R71">
+    <cfRule type="expression" dxfId="61" priority="1">
+      <formula>顯示注音輸入</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="60" priority="2">
+      <formula>"'= TRUE(顯示注音輸入)"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D83:R83">
+    <cfRule type="expression" dxfId="59" priority="9">
+      <formula>顯示注音輸入</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="58" priority="10">
       <formula>"'= TRUE(顯示注音輸入)"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D95:R95">
-    <cfRule type="expression" dxfId="67" priority="31">
+    <cfRule type="expression" dxfId="57" priority="31">
       <formula>顯示注音輸入</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="66" priority="32">
+    <cfRule type="expression" dxfId="56" priority="32">
       <formula>"'= TRUE(顯示注音輸入)"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D99:R99">
-    <cfRule type="expression" dxfId="65" priority="29">
+    <cfRule type="expression" dxfId="55" priority="29">
       <formula>顯示注音輸入</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="64" priority="30">
+    <cfRule type="expression" dxfId="54" priority="30">
       <formula>"'= TRUE(顯示注音輸入)"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D103:R103">
-    <cfRule type="expression" dxfId="63" priority="27">
+    <cfRule type="expression" dxfId="53" priority="28">
+      <formula>"'= TRUE(顯示注音輸入)"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="52" priority="27">
       <formula>顯示注音輸入</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="62" priority="28">
-      <formula>"'= TRUE(顯示注音輸入)"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D107:R107">
-    <cfRule type="expression" dxfId="61" priority="25">
+    <cfRule type="expression" dxfId="51" priority="26">
+      <formula>"'= TRUE(顯示注音輸入)"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="50" priority="25">
       <formula>顯示注音輸入</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="60" priority="26">
-      <formula>"'= TRUE(顯示注音輸入)"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D111:R111">
-    <cfRule type="expression" dxfId="59" priority="23">
+    <cfRule type="expression" dxfId="49" priority="24">
+      <formula>"'= TRUE(顯示注音輸入)"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="48" priority="23">
       <formula>顯示注音輸入</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="58" priority="24">
-      <formula>"'= TRUE(顯示注音輸入)"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D115:R115">
-    <cfRule type="expression" dxfId="57" priority="21">
+    <cfRule type="expression" dxfId="47" priority="21">
       <formula>顯示注音輸入</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="56" priority="22">
+    <cfRule type="expression" dxfId="46" priority="22">
       <formula>"'= TRUE(顯示注音輸入)"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D119:R119">
-    <cfRule type="expression" dxfId="55" priority="19">
+    <cfRule type="expression" dxfId="45" priority="20">
+      <formula>"'= TRUE(顯示注音輸入)"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="44" priority="19">
       <formula>顯示注音輸入</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="54" priority="20">
-      <formula>"'= TRUE(顯示注音輸入)"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D123:R123">
-    <cfRule type="expression" dxfId="53" priority="11">
+    <cfRule type="expression" dxfId="43" priority="12">
+      <formula>"'= TRUE(顯示注音輸入)"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="42" priority="11">
       <formula>顯示注音輸入</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="52" priority="12">
-      <formula>"'= TRUE(顯示注音輸入)"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D127:R127 D131:R131 D135:R135 D139:R139 D143:R143 D147:R147 D151:R151 D155:R155 D159:R159 D163:R163">
-    <cfRule type="expression" dxfId="51" priority="161">
+    <cfRule type="expression" dxfId="41" priority="161">
       <formula>顯示注音輸入</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="50" priority="162">
+    <cfRule type="expression" dxfId="40" priority="162">
       <formula>"'= TRUE(顯示注音輸入)"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D167:R167 D171:R171 D175:R175 D179:R179 D183:R183 D187:R187 D191:R191 D195:R195 D199:R199">
-    <cfRule type="expression" dxfId="49" priority="159">
+    <cfRule type="expression" dxfId="39" priority="160">
+      <formula>"'= TRUE(顯示注音輸入)"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="38" priority="159">
       <formula>顯示注音輸入</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="48" priority="160">
-      <formula>"'= TRUE(顯示注音輸入)"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D203:R203">
-    <cfRule type="expression" dxfId="47" priority="157">
+    <cfRule type="expression" dxfId="37" priority="158">
+      <formula>"'= TRUE(顯示注音輸入)"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="36" priority="157">
       <formula>顯示注音輸入</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="46" priority="158">
-      <formula>"'= TRUE(顯示注音輸入)"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D207:R207 D211:R211 D215:R215 D219:R219 D223:R223 D227:R227 D231:R231 D235:R235 D239:R239">
-    <cfRule type="expression" dxfId="45" priority="155">
+    <cfRule type="expression" dxfId="35" priority="156">
+      <formula>"'= TRUE(顯示注音輸入)"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="34" priority="155">
       <formula>顯示注音輸入</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="44" priority="156">
-      <formula>"'= TRUE(顯示注音輸入)"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D243:R243">
-    <cfRule type="expression" dxfId="43" priority="111">
+    <cfRule type="expression" dxfId="33" priority="111">
       <formula>顯示注音輸入</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="42" priority="112">
+    <cfRule type="expression" dxfId="32" priority="112">
       <formula>"'= TRUE(顯示注音輸入)"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D247:R247 D251:R251 D255:R255 D259:R259 D263:R263 D267:R267 D271:R271 D275:R275 D279:R279">
-    <cfRule type="expression" dxfId="41" priority="109">
+    <cfRule type="expression" dxfId="31" priority="110">
+      <formula>"'= TRUE(顯示注音輸入)"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="30" priority="109">
       <formula>顯示注音輸入</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="40" priority="110">
-      <formula>"'= TRUE(顯示注音輸入)"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D283:R283">
-    <cfRule type="expression" dxfId="39" priority="107">
+    <cfRule type="expression" dxfId="29" priority="108">
+      <formula>"'= TRUE(顯示注音輸入)"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="28" priority="107">
       <formula>顯示注音輸入</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="38" priority="108">
-      <formula>"'= TRUE(顯示注音輸入)"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D287:R287">
-    <cfRule type="expression" dxfId="37" priority="105">
+    <cfRule type="expression" dxfId="27" priority="105">
       <formula>顯示注音輸入</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="36" priority="106">
+    <cfRule type="expression" dxfId="26" priority="106">
       <formula>"'= TRUE(顯示注音輸入)"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D291:R291 D295:R295 D299:R299 D303:R303 D307:R307 D311:R311 D315:R315 D319:R319 D323:R323">
-    <cfRule type="expression" dxfId="35" priority="103">
+    <cfRule type="expression" dxfId="25" priority="104">
+      <formula>"'= TRUE(顯示注音輸入)"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="24" priority="103">
       <formula>顯示注音輸入</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="34" priority="104">
-      <formula>"'= TRUE(顯示注音輸入)"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D327:R327">
-    <cfRule type="expression" dxfId="33" priority="101">
+    <cfRule type="expression" dxfId="23" priority="101">
       <formula>顯示注音輸入</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="32" priority="102">
+    <cfRule type="expression" dxfId="22" priority="102">
       <formula>"'= TRUE(顯示注音輸入)"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D331:R331">
-    <cfRule type="expression" dxfId="31" priority="99">
+    <cfRule type="expression" dxfId="21" priority="100">
+      <formula>"'= TRUE(顯示注音輸入)"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="20" priority="99">
       <formula>顯示注音輸入</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="30" priority="100">
-      <formula>"'= TRUE(顯示注音輸入)"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D335:R335 D339:R339 D343:R343 D347:R347 D351:R351 D355:R355 D359:R359 D363:R363 D367:R367">
-    <cfRule type="expression" dxfId="29" priority="97">
+    <cfRule type="expression" dxfId="19" priority="98">
+      <formula>"'= TRUE(顯示注音輸入)"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="18" priority="97">
       <formula>顯示注音輸入</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="28" priority="98">
-      <formula>"'= TRUE(顯示注音輸入)"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D371:R371">
-    <cfRule type="expression" dxfId="27" priority="95">
+    <cfRule type="expression" dxfId="17" priority="95">
       <formula>顯示注音輸入</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="26" priority="96">
+    <cfRule type="expression" dxfId="16" priority="96">
       <formula>"'= TRUE(顯示注音輸入)"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D375:R375">
-    <cfRule type="expression" dxfId="25" priority="93">
+    <cfRule type="expression" dxfId="15" priority="93">
       <formula>顯示注音輸入</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="24" priority="94">
+    <cfRule type="expression" dxfId="14" priority="94">
       <formula>"'= TRUE(顯示注音輸入)"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D379:R379 D383:R383 D387:R387 D391:R391 D395:R395 D399:R399 D403:R403 D407:R407 D411:R411">
-    <cfRule type="expression" dxfId="23" priority="91">
+    <cfRule type="expression" dxfId="13" priority="91">
       <formula>顯示注音輸入</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="22" priority="92">
+    <cfRule type="expression" dxfId="12" priority="92">
       <formula>"'= TRUE(顯示注音輸入)"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D415:R415">
-    <cfRule type="expression" dxfId="21" priority="89">
+    <cfRule type="expression" dxfId="11" priority="89">
       <formula>顯示注音輸入</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="20" priority="90">
+    <cfRule type="expression" dxfId="10" priority="90">
       <formula>"'= TRUE(顯示注音輸入)"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D419:R419">
-    <cfRule type="expression" dxfId="19" priority="87">
+    <cfRule type="expression" dxfId="9" priority="88">
+      <formula>"'= TRUE(顯示注音輸入)"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="8" priority="87">
       <formula>顯示注音輸入</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="18" priority="88">
-      <formula>"'= TRUE(顯示注音輸入)"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D423:R423 D427:R427 D431:R431 D435:R435 D439:R439 D443:R443 D447:R447 D451:R451 D455:R455">
-    <cfRule type="expression" dxfId="17" priority="85">
+    <cfRule type="expression" dxfId="7" priority="85">
       <formula>顯示注音輸入</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="16" priority="86">
+    <cfRule type="expression" dxfId="6" priority="86">
       <formula>"'= TRUE(顯示注音輸入)"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D459:R459">
-    <cfRule type="expression" dxfId="15" priority="81">
+    <cfRule type="expression" dxfId="5" priority="82">
+      <formula>"'= TRUE(顯示注音輸入)"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="4" priority="81">
       <formula>顯示注音輸入</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="14" priority="82">
-      <formula>"'= TRUE(顯示注音輸入)"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D463:R463 D467:R467 D471:R471 D475:R475">
-    <cfRule type="expression" dxfId="13" priority="79">
+    <cfRule type="expression" dxfId="3" priority="80">
+      <formula>"'= TRUE(顯示注音輸入)"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="2" priority="79">
       <formula>顯示注音輸入</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="12" priority="80">
-      <formula>"'= TRUE(顯示注音輸入)"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D479:R479">
-    <cfRule type="expression" dxfId="11" priority="77">
-      <formula>顯示注音輸入</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="10" priority="78">
+    <cfRule type="expression" dxfId="1" priority="78">
       <formula>"'= TRUE(顯示注音輸入)"</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D83:O83">
-    <cfRule type="expression" dxfId="9" priority="9">
+    <cfRule type="expression" dxfId="0" priority="77">
       <formula>顯示注音輸入</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="8" priority="10">
-      <formula>"'= TRUE(顯示注音輸入)"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="O23">
-    <cfRule type="expression" dxfId="7" priority="7">
-      <formula>顯示注音輸入</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="6" priority="8">
-      <formula>"'= TRUE(顯示注音輸入)"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D55">
-    <cfRule type="expression" dxfId="5" priority="5">
-      <formula>顯示注音輸入</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="4" priority="6">
-      <formula>"'= TRUE(顯示注音輸入)"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G55">
-    <cfRule type="expression" dxfId="3" priority="3">
-      <formula>顯示注音輸入</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="2" priority="4">
-      <formula>"'= TRUE(顯示注音輸入)"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I71">
-    <cfRule type="expression" dxfId="1" priority="1">
-      <formula>顯示注音輸入</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="0" priority="2">
-      <formula>"'= TRUE(顯示注音輸入)"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/output7/【河洛白話注音-閩拼調符】《秋離》.xlsx
+++ b/output7/【河洛白話注音-閩拼調符】《秋離》.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\work\Piau-Im\output7\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{014A3801-C3E3-480C-9C3E-AA8DEE415042}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{13BABD09-37E4-4B3B-89F2-4781A1DC66B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-15" windowWidth="29040" windowHeight="15720" tabRatio="689" activeTab="4" xr2:uid="{25A76161-EFED-4AC8-8EAA-A42737AE1909}"/>
+    <workbookView xWindow="105" yWindow="1950" windowWidth="28695" windowHeight="11295" tabRatio="689" activeTab="4" xr2:uid="{25A76161-EFED-4AC8-8EAA-A42737AE1909}"/>
   </bookViews>
   <sheets>
     <sheet name="env" sheetId="8" r:id="rId1"/>
@@ -1225,9 +1225,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>https://imgs.guwendianji.com/wp-content/uploads/2017/06/1-32.jpg</t>
-  </si>
-  <si>
     <t>方音符號</t>
   </si>
   <si>
@@ -2708,6 +2705,10 @@
   </si>
   <si>
     <t>【河洛白話注音-閩拼調符】《秋離》.xlsx</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ciu1-Li5.jpg</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -4496,7 +4497,7 @@
     </row>
     <row r="2" spans="2:11">
       <c r="B2" s="4" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C2" s="53">
         <v>1</v>
@@ -4513,7 +4514,7 @@
         <v>3</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
     </row>
     <row r="5" spans="2:11">
@@ -4521,7 +4522,7 @@
         <v>4</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
     </row>
     <row r="6" spans="2:11">
@@ -4529,7 +4530,7 @@
         <v>5</v>
       </c>
       <c r="C6" s="50" t="s">
-        <v>370</v>
+        <v>772</v>
       </c>
       <c r="D6" s="51"/>
       <c r="E6" s="51"/>
@@ -4585,7 +4586,7 @@
         <v>11</v>
       </c>
       <c r="C12" s="46" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
     </row>
     <row r="13" spans="2:11" ht="30">
@@ -4601,7 +4602,7 @@
         <v>13</v>
       </c>
       <c r="C14" s="46" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
     </row>
     <row r="15" spans="2:11" ht="30">
@@ -4625,7 +4626,7 @@
         <v>16</v>
       </c>
       <c r="C17" s="46" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="30">
@@ -4633,7 +4634,7 @@
         <v>17</v>
       </c>
       <c r="C18" s="46" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="19" spans="2:3" ht="30">
@@ -4677,16 +4678,16 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" t="s">
+        <v>767</v>
+      </c>
+      <c r="B1" t="s">
         <v>768</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>769</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>770</v>
-      </c>
-      <c r="D1" t="s">
-        <v>771</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -4694,13 +4695,13 @@
         <v>312</v>
       </c>
       <c r="B2" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C2" t="s">
         <v>104</v>
       </c>
       <c r="D2" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -4714,7 +4715,7 @@
         <v>104</v>
       </c>
       <c r="D3" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -4728,7 +4729,7 @@
         <v>104</v>
       </c>
       <c r="D4" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -4742,7 +4743,7 @@
         <v>104</v>
       </c>
       <c r="D5" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -4756,7 +4757,7 @@
         <v>104</v>
       </c>
       <c r="D6" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -4784,7 +4785,7 @@
         <v>263</v>
       </c>
       <c r="D8" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -4798,7 +4799,7 @@
         <v>79</v>
       </c>
       <c r="D9" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -4812,7 +4813,7 @@
         <v>104</v>
       </c>
       <c r="D10" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -4826,12 +4827,12 @@
         <v>104</v>
       </c>
       <c r="D11" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B12" t="s">
         <v>285</v>
@@ -4840,7 +4841,7 @@
         <v>104</v>
       </c>
       <c r="D12" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -4868,7 +4869,7 @@
         <v>104</v>
       </c>
       <c r="D14" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -4882,7 +4883,7 @@
         <v>104</v>
       </c>
       <c r="D15" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -4896,7 +4897,7 @@
         <v>104</v>
       </c>
       <c r="D16" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -4910,7 +4911,7 @@
         <v>104</v>
       </c>
       <c r="D17" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -4924,7 +4925,7 @@
         <v>181</v>
       </c>
       <c r="D18" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -4946,13 +4947,13 @@
         <v>185</v>
       </c>
       <c r="B20" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="C20" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="D20" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -4994,7 +4995,7 @@
         <v>104</v>
       </c>
       <c r="D23" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -5008,7 +5009,7 @@
         <v>104</v>
       </c>
       <c r="D24" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -5022,7 +5023,7 @@
         <v>271</v>
       </c>
       <c r="D25" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -5036,7 +5037,7 @@
         <v>104</v>
       </c>
       <c r="D26" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -5050,7 +5051,7 @@
         <v>104</v>
       </c>
       <c r="D27" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -5075,10 +5076,10 @@
         <v>299</v>
       </c>
       <c r="C29" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="D29" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -5092,7 +5093,7 @@
         <v>104</v>
       </c>
       <c r="D30" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -5106,7 +5107,7 @@
         <v>104</v>
       </c>
       <c r="D31" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -5117,10 +5118,10 @@
         <v>277</v>
       </c>
       <c r="C32" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="D32" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -5134,7 +5135,7 @@
         <v>104</v>
       </c>
       <c r="D33" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -5148,7 +5149,7 @@
         <v>104</v>
       </c>
       <c r="D34" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -5162,7 +5163,7 @@
         <v>216</v>
       </c>
       <c r="D35" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -5176,7 +5177,7 @@
         <v>341</v>
       </c>
       <c r="D36" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -5190,7 +5191,7 @@
         <v>104</v>
       </c>
       <c r="D37" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -5204,7 +5205,7 @@
         <v>104</v>
       </c>
       <c r="D38" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -5218,7 +5219,7 @@
         <v>104</v>
       </c>
       <c r="D39" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -5226,13 +5227,13 @@
         <v>330</v>
       </c>
       <c r="B40" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="C40" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="D40" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -5246,7 +5247,7 @@
         <v>104</v>
       </c>
       <c r="D41" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -5254,13 +5255,13 @@
         <v>22</v>
       </c>
       <c r="B42" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="C42" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="D42" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -5274,7 +5275,7 @@
         <v>104</v>
       </c>
       <c r="D43" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -5282,13 +5283,13 @@
         <v>264</v>
       </c>
       <c r="B44" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C44" t="s">
         <v>104</v>
       </c>
       <c r="D44" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -5302,7 +5303,7 @@
         <v>104</v>
       </c>
       <c r="D45" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -5310,13 +5311,13 @@
         <v>328</v>
       </c>
       <c r="B46" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C46" t="s">
         <v>104</v>
       </c>
       <c r="D46" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -5330,7 +5331,7 @@
         <v>305</v>
       </c>
       <c r="D47" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -5344,7 +5345,7 @@
         <v>219</v>
       </c>
       <c r="D48" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -5358,7 +5359,7 @@
         <v>191</v>
       </c>
       <c r="D49" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -5372,7 +5373,7 @@
         <v>104</v>
       </c>
       <c r="D50" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -5386,7 +5387,7 @@
         <v>104</v>
       </c>
       <c r="D51" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -5400,7 +5401,7 @@
         <v>104</v>
       </c>
       <c r="D52" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -5408,13 +5409,13 @@
         <v>350</v>
       </c>
       <c r="B53" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="C53" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="D53" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -5428,7 +5429,7 @@
         <v>104</v>
       </c>
       <c r="D54" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -5442,7 +5443,7 @@
         <v>104</v>
       </c>
       <c r="D55" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -5484,7 +5485,7 @@
         <v>256</v>
       </c>
       <c r="D58" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -5498,7 +5499,7 @@
         <v>273</v>
       </c>
       <c r="D59" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -5512,7 +5513,7 @@
         <v>104</v>
       </c>
       <c r="D60" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -5526,7 +5527,7 @@
         <v>104</v>
       </c>
       <c r="D61" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -5540,7 +5541,7 @@
         <v>104</v>
       </c>
       <c r="D62" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -5554,7 +5555,7 @@
         <v>104</v>
       </c>
       <c r="D63" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -5568,7 +5569,7 @@
         <v>104</v>
       </c>
       <c r="D64" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -5582,7 +5583,7 @@
         <v>104</v>
       </c>
       <c r="D65" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -5596,7 +5597,7 @@
         <v>104</v>
       </c>
       <c r="D66" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -5610,7 +5611,7 @@
         <v>104</v>
       </c>
       <c r="D67" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -5618,13 +5619,13 @@
         <v>322</v>
       </c>
       <c r="B68" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="C68" t="s">
         <v>104</v>
       </c>
       <c r="D68" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -5638,7 +5639,7 @@
         <v>104</v>
       </c>
       <c r="D69" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -5652,7 +5653,7 @@
         <v>104</v>
       </c>
       <c r="D70" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -5666,7 +5667,7 @@
         <v>104</v>
       </c>
       <c r="D71" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -5674,13 +5675,13 @@
         <v>347</v>
       </c>
       <c r="B72" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C72" t="s">
         <v>104</v>
       </c>
       <c r="D72" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -5694,7 +5695,7 @@
         <v>104</v>
       </c>
       <c r="D73" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -5708,7 +5709,7 @@
         <v>104</v>
       </c>
       <c r="D74" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -5722,7 +5723,7 @@
         <v>104</v>
       </c>
       <c r="D75" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -5736,7 +5737,7 @@
         <v>104</v>
       </c>
       <c r="D76" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -5750,7 +5751,7 @@
         <v>104</v>
       </c>
       <c r="D77" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -5764,7 +5765,7 @@
         <v>104</v>
       </c>
       <c r="D78" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -5778,7 +5779,7 @@
         <v>104</v>
       </c>
       <c r="D79" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -5792,7 +5793,7 @@
         <v>104</v>
       </c>
       <c r="D80" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -5806,7 +5807,7 @@
         <v>104</v>
       </c>
       <c r="D81" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -5820,7 +5821,7 @@
         <v>104</v>
       </c>
       <c r="D82" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -5834,7 +5835,7 @@
         <v>104</v>
       </c>
       <c r="D83" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -5848,7 +5849,7 @@
         <v>104</v>
       </c>
       <c r="D84" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -5862,7 +5863,7 @@
         <v>104</v>
       </c>
       <c r="D85" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -5876,7 +5877,7 @@
         <v>104</v>
       </c>
       <c r="D86" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -5890,7 +5891,7 @@
         <v>104</v>
       </c>
       <c r="D87" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -5904,7 +5905,7 @@
         <v>104</v>
       </c>
       <c r="D88" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -5918,7 +5919,7 @@
         <v>104</v>
       </c>
       <c r="D89" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -5932,7 +5933,7 @@
         <v>104</v>
       </c>
       <c r="D90" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -5946,7 +5947,7 @@
         <v>104</v>
       </c>
       <c r="D91" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -5960,7 +5961,7 @@
         <v>104</v>
       </c>
       <c r="D92" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -5974,7 +5975,7 @@
         <v>104</v>
       </c>
       <c r="D93" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -5988,7 +5989,7 @@
         <v>104</v>
       </c>
       <c r="D94" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -6002,7 +6003,7 @@
         <v>104</v>
       </c>
       <c r="D95" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -6016,7 +6017,7 @@
         <v>104</v>
       </c>
       <c r="D96" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -6030,7 +6031,7 @@
         <v>104</v>
       </c>
       <c r="D97" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -6044,7 +6045,7 @@
         <v>104</v>
       </c>
       <c r="D98" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -6058,7 +6059,7 @@
         <v>104</v>
       </c>
       <c r="D99" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -6066,13 +6067,13 @@
         <v>163</v>
       </c>
       <c r="B100" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C100" t="s">
         <v>104</v>
       </c>
       <c r="D100" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -6086,7 +6087,7 @@
         <v>104</v>
       </c>
       <c r="D101" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -6094,13 +6095,13 @@
         <v>288</v>
       </c>
       <c r="B102" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="C102" t="s">
         <v>104</v>
       </c>
       <c r="D102" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -6114,7 +6115,7 @@
         <v>104</v>
       </c>
       <c r="D103" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -6122,13 +6123,13 @@
         <v>169</v>
       </c>
       <c r="B104" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="C104" t="s">
         <v>104</v>
       </c>
       <c r="D104" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -6142,7 +6143,7 @@
         <v>104</v>
       </c>
       <c r="D105" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -6156,7 +6157,7 @@
         <v>104</v>
       </c>
       <c r="D106" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -6170,7 +6171,7 @@
         <v>104</v>
       </c>
       <c r="D107" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -6184,7 +6185,7 @@
         <v>104</v>
       </c>
       <c r="D108" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -6198,7 +6199,7 @@
         <v>104</v>
       </c>
       <c r="D109" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -6212,7 +6213,7 @@
         <v>104</v>
       </c>
       <c r="D110" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -6226,7 +6227,7 @@
         <v>104</v>
       </c>
       <c r="D111" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -6240,7 +6241,7 @@
         <v>104</v>
       </c>
       <c r="D112" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -6254,7 +6255,7 @@
         <v>104</v>
       </c>
       <c r="D113" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -6268,7 +6269,7 @@
         <v>104</v>
       </c>
       <c r="D114" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -6282,7 +6283,7 @@
         <v>104</v>
       </c>
       <c r="D115" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -6296,7 +6297,7 @@
         <v>104</v>
       </c>
       <c r="D116" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -6310,7 +6311,7 @@
         <v>104</v>
       </c>
       <c r="D117" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -6324,7 +6325,7 @@
         <v>104</v>
       </c>
       <c r="D118" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -6338,7 +6339,7 @@
         <v>104</v>
       </c>
       <c r="D119" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -6360,13 +6361,13 @@
         <v>274</v>
       </c>
       <c r="B121" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="C121" t="s">
         <v>104</v>
       </c>
       <c r="D121" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -6380,7 +6381,7 @@
         <v>104</v>
       </c>
       <c r="D122" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -6394,7 +6395,7 @@
         <v>104</v>
       </c>
       <c r="D123" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -6408,7 +6409,7 @@
         <v>104</v>
       </c>
       <c r="D124" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -6422,7 +6423,7 @@
         <v>104</v>
       </c>
       <c r="D125" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -6436,7 +6437,7 @@
         <v>104</v>
       </c>
       <c r="D126" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -6450,7 +6451,7 @@
         <v>104</v>
       </c>
       <c r="D127" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -6478,7 +6479,7 @@
         <v>104</v>
       </c>
       <c r="D129" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -6492,7 +6493,7 @@
         <v>104</v>
       </c>
       <c r="D130" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -6500,7 +6501,7 @@
         <v>342</v>
       </c>
       <c r="B131" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="C131" t="s">
         <v>104</v>
@@ -6528,7 +6529,7 @@
         <v>213</v>
       </c>
       <c r="B133" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="C133" t="s">
         <v>104</v>
@@ -6548,7 +6549,7 @@
         <v>104</v>
       </c>
       <c r="D134" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -6562,7 +6563,7 @@
         <v>104</v>
       </c>
       <c r="D135" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -6570,13 +6571,13 @@
         <v>351</v>
       </c>
       <c r="B136" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="C136" t="s">
         <v>104</v>
       </c>
       <c r="D136" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -6604,7 +6605,7 @@
         <v>104</v>
       </c>
       <c r="D138" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -6618,7 +6619,7 @@
         <v>104</v>
       </c>
       <c r="D139" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -6632,7 +6633,7 @@
         <v>104</v>
       </c>
       <c r="D140" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -6646,7 +6647,7 @@
         <v>104</v>
       </c>
       <c r="D141" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -6660,7 +6661,7 @@
         <v>104</v>
       </c>
       <c r="D142" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -6674,7 +6675,7 @@
         <v>104</v>
       </c>
       <c r="D143" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -6716,7 +6717,7 @@
         <v>104</v>
       </c>
       <c r="D146" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -6730,7 +6731,7 @@
         <v>104</v>
       </c>
       <c r="D147" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -6744,7 +6745,7 @@
         <v>104</v>
       </c>
       <c r="D148" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -6752,13 +6753,13 @@
         <v>196</v>
       </c>
       <c r="B149" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="C149" t="s">
         <v>104</v>
       </c>
       <c r="D149" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -6772,7 +6773,7 @@
         <v>104</v>
       </c>
       <c r="D150" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -6786,7 +6787,7 @@
         <v>104</v>
       </c>
       <c r="D151" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -6800,7 +6801,7 @@
         <v>104</v>
       </c>
       <c r="D152" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -6828,7 +6829,7 @@
         <v>104</v>
       </c>
       <c r="D154" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -6842,12 +6843,12 @@
         <v>104</v>
       </c>
       <c r="D155" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="156" spans="1:4">
       <c r="A156" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="B156" t="s">
         <v>348</v>
@@ -6856,7 +6857,7 @@
         <v>104</v>
       </c>
       <c r="D156" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
     </row>
   </sheetData>
@@ -6872,21 +6873,21 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" t="s">
+        <v>767</v>
+      </c>
+      <c r="B1" t="s">
         <v>768</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>769</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>770</v>
-      </c>
-      <c r="D1" t="s">
-        <v>771</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="B2" t="s">
         <v>348</v>
@@ -6895,7 +6896,7 @@
         <v>348</v>
       </c>
       <c r="D2" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
     </row>
   </sheetData>
@@ -6911,16 +6912,16 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" t="s">
+        <v>767</v>
+      </c>
+      <c r="B1" t="s">
         <v>768</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>769</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>770</v>
-      </c>
-      <c r="D1" t="s">
-        <v>771</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -6948,7 +6949,7 @@
         <v>104</v>
       </c>
       <c r="D3" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -6962,7 +6963,7 @@
         <v>104</v>
       </c>
       <c r="D4" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -6976,7 +6977,7 @@
         <v>104</v>
       </c>
       <c r="D5" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -6984,13 +6985,13 @@
         <v>185</v>
       </c>
       <c r="B6" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="C6" t="s">
         <v>104</v>
       </c>
       <c r="D6" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -7018,7 +7019,7 @@
         <v>104</v>
       </c>
       <c r="D8" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -7046,7 +7047,7 @@
         <v>104</v>
       </c>
       <c r="D10" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -7060,7 +7061,7 @@
         <v>104</v>
       </c>
       <c r="D11" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -7074,7 +7075,7 @@
         <v>104</v>
       </c>
       <c r="D12" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -7088,7 +7089,7 @@
         <v>104</v>
       </c>
       <c r="D13" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -7102,7 +7103,7 @@
         <v>104</v>
       </c>
       <c r="D14" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -7110,13 +7111,13 @@
         <v>330</v>
       </c>
       <c r="B15" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="C15" t="s">
         <v>104</v>
       </c>
       <c r="D15" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -7124,13 +7125,13 @@
         <v>22</v>
       </c>
       <c r="B16" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="C16" t="s">
         <v>104</v>
       </c>
       <c r="D16" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -7144,7 +7145,7 @@
         <v>104</v>
       </c>
       <c r="D17" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -7158,7 +7159,7 @@
         <v>104</v>
       </c>
       <c r="D18" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -7172,7 +7173,7 @@
         <v>104</v>
       </c>
       <c r="D19" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -7186,7 +7187,7 @@
         <v>104</v>
       </c>
       <c r="D20" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -7194,13 +7195,13 @@
         <v>350</v>
       </c>
       <c r="B21" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="C21" t="s">
         <v>104</v>
       </c>
       <c r="D21" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -7228,7 +7229,7 @@
         <v>104</v>
       </c>
       <c r="D23" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -7242,7 +7243,7 @@
         <v>104</v>
       </c>
       <c r="D24" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -7256,7 +7257,7 @@
         <v>104</v>
       </c>
       <c r="D25" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -7264,13 +7265,13 @@
         <v>322</v>
       </c>
       <c r="B26" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="C26" t="s">
         <v>104</v>
       </c>
       <c r="D26" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -7284,7 +7285,7 @@
         <v>104</v>
       </c>
       <c r="D27" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -7298,12 +7299,12 @@
         <v>104</v>
       </c>
       <c r="D28" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
     </row>
     <row r="29" spans="1:4">
       <c r="A29" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="B29" t="s">
         <v>348</v>
@@ -7312,7 +7313,7 @@
         <v>104</v>
       </c>
       <c r="D29" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -7326,7 +7327,7 @@
         <v>104</v>
       </c>
       <c r="D30" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -7354,7 +7355,7 @@
         <v>104</v>
       </c>
       <c r="D32" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -7368,7 +7369,7 @@
         <v>104</v>
       </c>
       <c r="D33" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -7382,7 +7383,7 @@
         <v>104</v>
       </c>
       <c r="D34" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -7396,7 +7397,7 @@
         <v>104</v>
       </c>
       <c r="D35" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -7410,7 +7411,7 @@
         <v>104</v>
       </c>
       <c r="D36" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -7424,7 +7425,7 @@
         <v>104</v>
       </c>
       <c r="D37" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -7432,13 +7433,13 @@
         <v>288</v>
       </c>
       <c r="B38" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="C38" t="s">
         <v>104</v>
       </c>
       <c r="D38" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -7466,7 +7467,7 @@
         <v>104</v>
       </c>
       <c r="D40" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -7480,7 +7481,7 @@
         <v>104</v>
       </c>
       <c r="D41" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -7488,7 +7489,7 @@
         <v>213</v>
       </c>
       <c r="B42" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="C42" t="s">
         <v>104</v>
@@ -7508,7 +7509,7 @@
         <v>104</v>
       </c>
       <c r="D43" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -7522,7 +7523,7 @@
         <v>104</v>
       </c>
       <c r="D44" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -7536,7 +7537,7 @@
         <v>104</v>
       </c>
       <c r="D45" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
     </row>
   </sheetData>
@@ -7678,17 +7679,17 @@
       <c r="R3" s="52"/>
       <c r="T3" s="16"/>
       <c r="V3" s="54" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="4" spans="1:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B4" s="17"/>
       <c r="D4" s="58"/>
       <c r="E4" s="58" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="F4" s="58" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="G4" s="58"/>
       <c r="H4" s="58"/>
@@ -7744,10 +7745,10 @@
       <c r="C6" s="23"/>
       <c r="D6" s="24"/>
       <c r="E6" s="24" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="F6" s="24" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="G6" s="24"/>
       <c r="H6" s="24"/>
@@ -7772,11 +7773,11 @@
       <c r="F7" s="52"/>
       <c r="G7" s="52"/>
       <c r="H7" s="52" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="I7" s="52"/>
       <c r="J7" s="52" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="K7" s="52"/>
       <c r="L7" s="52" t="s">
@@ -7794,28 +7795,28 @@
     <row r="8" spans="1:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B8" s="17"/>
       <c r="D8" s="58" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="E8" s="58" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="F8" s="58" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="G8" s="58" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H8" s="58" t="s">
+        <v>655</v>
+      </c>
+      <c r="I8" s="58" t="s">
+        <v>499</v>
+      </c>
+      <c r="J8" s="58" t="s">
         <v>656</v>
       </c>
-      <c r="I8" s="58" t="s">
-        <v>500</v>
-      </c>
-      <c r="J8" s="58" t="s">
-        <v>657</v>
-      </c>
       <c r="K8" s="58" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="L8" s="58" t="s">
         <v>124</v>
@@ -7878,31 +7879,31 @@
     <row r="10" spans="1:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B10" s="22"/>
       <c r="D10" s="24" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="E10" s="24" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="F10" s="24" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="G10" s="24" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="H10" s="24" t="s">
+        <v>682</v>
+      </c>
+      <c r="I10" s="24" t="s">
+        <v>500</v>
+      </c>
+      <c r="J10" s="24" t="s">
         <v>683</v>
       </c>
-      <c r="I10" s="24" t="s">
-        <v>501</v>
-      </c>
-      <c r="J10" s="24" t="s">
-        <v>684</v>
-      </c>
       <c r="K10" s="24" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="L10" s="24" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="M10" s="24"/>
       <c r="N10" s="24"/>
@@ -7924,7 +7925,7 @@
       <c r="I11" s="52"/>
       <c r="J11" s="52"/>
       <c r="K11" s="52" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="L11" s="52"/>
       <c r="M11" s="52"/>
@@ -7938,31 +7939,31 @@
     <row r="12" spans="1:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B12" s="17"/>
       <c r="D12" s="58" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="E12" s="58" t="s">
         <v>115</v>
       </c>
       <c r="F12" s="58" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="G12" s="58" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="H12" s="58" t="s">
         <v>120</v>
       </c>
       <c r="I12" s="58" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="J12" s="58" t="s">
         <v>118</v>
       </c>
       <c r="K12" s="58" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="L12" s="58" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="M12" s="58"/>
       <c r="N12" s="18"/>
@@ -7979,7 +7980,7 @@
         <v>3</v>
       </c>
       <c r="D13" s="41" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="E13" s="41" t="s">
         <v>64</v>
@@ -8021,31 +8022,31 @@
     <row r="14" spans="1:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B14" s="22"/>
       <c r="D14" s="24" t="s">
+        <v>510</v>
+      </c>
+      <c r="E14" s="24" t="s">
         <v>511</v>
       </c>
-      <c r="E14" s="24" t="s">
-        <v>512</v>
-      </c>
       <c r="F14" s="24" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="G14" s="24" t="s">
+        <v>515</v>
+      </c>
+      <c r="H14" s="24" t="s">
         <v>516</v>
       </c>
-      <c r="H14" s="24" t="s">
+      <c r="I14" s="24" t="s">
+        <v>508</v>
+      </c>
+      <c r="J14" s="24" t="s">
         <v>517</v>
       </c>
-      <c r="I14" s="24" t="s">
-        <v>509</v>
-      </c>
-      <c r="J14" s="24" t="s">
-        <v>518</v>
-      </c>
       <c r="K14" s="24" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="L14" s="24" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="M14" s="24"/>
       <c r="N14" s="24"/>
@@ -8060,7 +8061,7 @@
       <c r="B15" s="12"/>
       <c r="C15" s="34"/>
       <c r="D15" s="52" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="E15" s="52"/>
       <c r="F15" s="52" t="s">
@@ -8069,14 +8070,14 @@
       <c r="G15" s="52"/>
       <c r="H15" s="52"/>
       <c r="I15" s="52" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="J15" s="52"/>
       <c r="K15" s="52"/>
       <c r="L15" s="52"/>
       <c r="M15" s="52"/>
       <c r="N15" s="52" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="O15" s="52"/>
       <c r="P15" s="52"/>
@@ -8087,7 +8088,7 @@
     <row r="16" spans="1:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B16" s="17"/>
       <c r="D16" s="58" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="E16" s="58" t="s">
         <v>141</v>
@@ -8096,26 +8097,26 @@
         <v>123</v>
       </c>
       <c r="G16" s="58" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="H16" s="58" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="I16" s="58" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="J16" s="58"/>
       <c r="K16" s="58" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="L16" s="58" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="M16" s="58" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="N16" s="58" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="O16" s="58"/>
       <c r="P16" s="18"/>
@@ -8148,7 +8149,7 @@
         <v>270</v>
       </c>
       <c r="J17" s="41" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="K17" s="41" t="s">
         <v>162</v>
@@ -8176,35 +8177,35 @@
     <row r="18" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B18" s="22"/>
       <c r="D18" s="24" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="E18" s="24" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="F18" s="24" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="G18" s="24" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H18" s="24" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="I18" s="24" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="J18" s="24"/>
       <c r="K18" s="24" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="L18" s="24" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="M18" s="24" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="N18" s="24" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="O18" s="24"/>
       <c r="P18" s="24"/>
@@ -8217,7 +8218,7 @@
       <c r="B19" s="12"/>
       <c r="C19" s="34"/>
       <c r="D19" s="52" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="E19" s="52"/>
       <c r="F19" s="52" t="s">
@@ -8227,17 +8228,17 @@
       <c r="H19" s="52"/>
       <c r="I19" s="52"/>
       <c r="J19" s="52" t="s">
+        <v>660</v>
+      </c>
+      <c r="K19" s="52" t="s">
         <v>661</v>
-      </c>
-      <c r="K19" s="52" t="s">
-        <v>662</v>
       </c>
       <c r="L19" s="52"/>
       <c r="M19" s="52" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="N19" s="52" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="O19" s="52"/>
       <c r="P19" s="52"/>
@@ -8248,7 +8249,7 @@
     <row r="20" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B20" s="17"/>
       <c r="D20" s="58" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="E20" s="58" t="s">
         <v>136</v>
@@ -8260,28 +8261,28 @@
         <v>121</v>
       </c>
       <c r="H20" s="58" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="I20" s="58" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="J20" s="58" t="s">
+        <v>660</v>
+      </c>
+      <c r="K20" s="58" t="s">
         <v>661</v>
       </c>
-      <c r="K20" s="58" t="s">
+      <c r="L20" s="58" t="s">
+        <v>533</v>
+      </c>
+      <c r="M20" s="58" t="s">
+        <v>761</v>
+      </c>
+      <c r="N20" s="58" t="s">
         <v>662</v>
       </c>
-      <c r="L20" s="58" t="s">
-        <v>534</v>
-      </c>
-      <c r="M20" s="58" t="s">
-        <v>762</v>
-      </c>
-      <c r="N20" s="58" t="s">
-        <v>663</v>
-      </c>
       <c r="O20" s="58" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="P20" s="58"/>
       <c r="Q20" s="18"/>
@@ -8343,40 +8344,40 @@
     <row r="22" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B22" s="22"/>
       <c r="D22" s="24" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="E22" s="24" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="F22" s="24" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="G22" s="24" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="H22" s="24" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="I22" s="24" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="J22" s="24" t="s">
+        <v>687</v>
+      </c>
+      <c r="K22" s="24" t="s">
         <v>688</v>
       </c>
-      <c r="K22" s="24" t="s">
-        <v>689</v>
-      </c>
       <c r="L22" s="24" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="M22" s="24" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="N22" s="24" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="O22" s="24" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="P22" s="24"/>
       <c r="Q22" s="24"/>
@@ -8388,30 +8389,30 @@
       <c r="B23" s="12"/>
       <c r="C23" s="34"/>
       <c r="D23" s="52" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="E23" s="52"/>
       <c r="F23" s="52"/>
       <c r="G23" s="52"/>
       <c r="H23" s="52" t="s">
+        <v>663</v>
+      </c>
+      <c r="I23" s="52" t="s">
         <v>664</v>
-      </c>
-      <c r="I23" s="52" t="s">
-        <v>665</v>
       </c>
       <c r="J23" s="52"/>
       <c r="K23" s="52" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="L23" s="52"/>
       <c r="M23" s="52" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="N23" s="52" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="O23" s="52" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="P23" s="52"/>
       <c r="Q23" s="52"/>
@@ -8421,38 +8422,38 @@
     <row r="24" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B24" s="17"/>
       <c r="D24" s="58" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="E24" s="58" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="F24" s="58" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="G24" s="58" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="H24" s="58" t="s">
+        <v>663</v>
+      </c>
+      <c r="I24" s="58" t="s">
         <v>664</v>
-      </c>
-      <c r="I24" s="58" t="s">
-        <v>665</v>
       </c>
       <c r="J24" s="58"/>
       <c r="K24" s="58" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="L24" s="58" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="M24" s="58" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="N24" s="58" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="O24" s="58" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="P24" s="58"/>
       <c r="Q24" s="18"/>
@@ -8484,7 +8485,7 @@
         <v>189</v>
       </c>
       <c r="J25" s="41" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="K25" s="41" t="s">
         <v>22</v>
@@ -8514,38 +8515,38 @@
     <row r="26" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B26" s="22"/>
       <c r="D26" s="24" t="s">
+        <v>692</v>
+      </c>
+      <c r="E26" s="24" t="s">
+        <v>539</v>
+      </c>
+      <c r="F26" s="24" t="s">
+        <v>541</v>
+      </c>
+      <c r="G26" s="24" t="s">
+        <v>543</v>
+      </c>
+      <c r="H26" s="24" t="s">
         <v>693</v>
       </c>
-      <c r="E26" s="24" t="s">
-        <v>540</v>
-      </c>
-      <c r="F26" s="24" t="s">
-        <v>542</v>
-      </c>
-      <c r="G26" s="24" t="s">
-        <v>544</v>
-      </c>
-      <c r="H26" s="24" t="s">
+      <c r="I26" s="24" t="s">
         <v>694</v>
-      </c>
-      <c r="I26" s="24" t="s">
-        <v>695</v>
       </c>
       <c r="J26" s="24"/>
       <c r="K26" s="24" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="L26" s="24" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="M26" s="24" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="N26" s="24" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="O26" s="24" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="P26" s="24"/>
       <c r="Q26" s="24"/>
@@ -8560,7 +8561,7 @@
       <c r="E27" s="52"/>
       <c r="F27" s="52"/>
       <c r="G27" s="52" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="H27" s="52"/>
       <c r="I27" s="52"/>
@@ -8572,14 +8573,14 @@
       <c r="M27" s="52"/>
       <c r="N27" s="52"/>
       <c r="O27" s="52" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="P27" s="52"/>
       <c r="Q27" s="52" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="R27" s="52" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="U27" s="35" t="str">
         <f t="shared" ref="U27:U32" si="1" xml:space="preserve"> MID($N$26,4,1)</f>
@@ -8593,33 +8594,33 @@
         <v>113</v>
       </c>
       <c r="E28" s="58" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="F28" s="58"/>
       <c r="G28" s="58" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="H28" s="58" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="I28" s="58" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="J28" s="58" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="K28" s="58" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="L28" s="58" t="s">
         <v>131</v>
       </c>
       <c r="M28" s="58"/>
       <c r="N28" s="58" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="O28" s="58" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="P28" s="58" t="s">
         <v>136</v>
@@ -8628,7 +8629,7 @@
         <v>363</v>
       </c>
       <c r="R28" s="58" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="S28" s="19"/>
       <c r="U28" s="35" t="str">
@@ -8649,7 +8650,7 @@
         <v>247</v>
       </c>
       <c r="F29" s="41" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="G29" s="41" t="s">
         <v>350</v>
@@ -8670,7 +8671,7 @@
         <v>234</v>
       </c>
       <c r="M29" s="41" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="N29" s="41" t="s">
         <v>211</v>
@@ -8697,45 +8698,45 @@
     <row r="30" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B30" s="22"/>
       <c r="D30" s="24" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="E30" s="24" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="F30" s="24"/>
       <c r="G30" s="24" t="s">
+        <v>697</v>
+      </c>
+      <c r="H30" s="24" t="s">
+        <v>527</v>
+      </c>
+      <c r="I30" s="24" t="s">
+        <v>548</v>
+      </c>
+      <c r="J30" s="24" t="s">
+        <v>521</v>
+      </c>
+      <c r="K30" s="24" t="s">
+        <v>550</v>
+      </c>
+      <c r="L30" s="24" t="s">
         <v>698</v>
-      </c>
-      <c r="H30" s="24" t="s">
-        <v>528</v>
-      </c>
-      <c r="I30" s="24" t="s">
-        <v>549</v>
-      </c>
-      <c r="J30" s="24" t="s">
-        <v>522</v>
-      </c>
-      <c r="K30" s="24" t="s">
-        <v>551</v>
-      </c>
-      <c r="L30" s="24" t="s">
-        <v>699</v>
       </c>
       <c r="M30" s="24"/>
       <c r="N30" s="24" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="O30" s="24" t="s">
+        <v>699</v>
+      </c>
+      <c r="P30" s="24" t="s">
+        <v>528</v>
+      </c>
+      <c r="Q30" s="24" t="s">
+        <v>650</v>
+      </c>
+      <c r="R30" s="24" t="s">
         <v>700</v>
-      </c>
-      <c r="P30" s="24" t="s">
-        <v>529</v>
-      </c>
-      <c r="Q30" s="24" t="s">
-        <v>651</v>
-      </c>
-      <c r="R30" s="24" t="s">
-        <v>701</v>
       </c>
       <c r="S30" s="31"/>
       <c r="U30" s="35" t="str">
@@ -8843,14 +8844,14 @@
       <c r="B35" s="12"/>
       <c r="C35" s="34"/>
       <c r="D35" s="52" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="E35" s="52"/>
       <c r="F35" s="52"/>
       <c r="G35" s="52"/>
       <c r="H35" s="52"/>
       <c r="I35" s="52" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="J35" s="52"/>
       <c r="K35" s="52"/>
@@ -8868,25 +8869,25 @@
     <row r="36" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B36" s="17"/>
       <c r="D36" s="18" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="E36" s="18" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="F36" s="18" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="G36" s="18" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H36" s="18" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="I36" s="18" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="J36" s="18" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="K36" s="18" t="s">
         <v>122</v>
@@ -8915,7 +8916,7 @@
         <v>326</v>
       </c>
       <c r="F37" s="41" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="G37" s="41" t="s">
         <v>287</v>
@@ -8951,31 +8952,31 @@
     <row r="38" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B38" s="22"/>
       <c r="D38" s="24" t="s">
+        <v>700</v>
+      </c>
+      <c r="E38" s="24" t="s">
+        <v>508</v>
+      </c>
+      <c r="F38" s="24" t="s">
+        <v>510</v>
+      </c>
+      <c r="G38" s="24" t="s">
+        <v>504</v>
+      </c>
+      <c r="H38" s="24" t="s">
+        <v>556</v>
+      </c>
+      <c r="I38" s="24" t="s">
+        <v>692</v>
+      </c>
+      <c r="J38" s="24" t="s">
+        <v>558</v>
+      </c>
+      <c r="K38" s="24" t="s">
+        <v>559</v>
+      </c>
+      <c r="L38" s="24" t="s">
         <v>701</v>
-      </c>
-      <c r="E38" s="24" t="s">
-        <v>509</v>
-      </c>
-      <c r="F38" s="24" t="s">
-        <v>511</v>
-      </c>
-      <c r="G38" s="24" t="s">
-        <v>505</v>
-      </c>
-      <c r="H38" s="24" t="s">
-        <v>557</v>
-      </c>
-      <c r="I38" s="24" t="s">
-        <v>693</v>
-      </c>
-      <c r="J38" s="24" t="s">
-        <v>559</v>
-      </c>
-      <c r="K38" s="24" t="s">
-        <v>560</v>
-      </c>
-      <c r="L38" s="24" t="s">
-        <v>702</v>
       </c>
       <c r="M38" s="24"/>
       <c r="N38" s="24"/>
@@ -8991,18 +8992,18 @@
       <c r="C39" s="34"/>
       <c r="D39" s="52"/>
       <c r="E39" s="52" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="F39" s="52"/>
       <c r="G39" s="52"/>
       <c r="H39" s="52"/>
       <c r="I39" s="52" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="J39" s="52"/>
       <c r="K39" s="52"/>
       <c r="L39" s="52" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="M39" s="52"/>
       <c r="N39" s="52"/>
@@ -9015,31 +9016,31 @@
     <row r="40" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B40" s="17"/>
       <c r="D40" s="18" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="E40" s="18" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="F40" s="18" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="G40" s="18" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H40" s="18" t="s">
         <v>142</v>
       </c>
       <c r="I40" s="18" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="J40" s="18" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="K40" s="18" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="L40" s="18" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="M40" s="18"/>
       <c r="N40" s="18"/>
@@ -9098,31 +9099,31 @@
     <row r="42" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B42" s="22"/>
       <c r="D42" s="24" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="E42" s="24" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="F42" s="24" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="G42" s="24" t="s">
+        <v>563</v>
+      </c>
+      <c r="H42" s="24" t="s">
         <v>564</v>
       </c>
-      <c r="H42" s="24" t="s">
-        <v>565</v>
-      </c>
       <c r="I42" s="24" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="J42" s="24" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="K42" s="24" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="L42" s="24" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="M42" s="24"/>
       <c r="N42" s="24"/>
@@ -9137,24 +9138,24 @@
       <c r="B43" s="12"/>
       <c r="C43" s="34"/>
       <c r="D43" s="52" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="E43" s="52"/>
       <c r="F43" s="52" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="G43" s="52"/>
       <c r="H43" s="52"/>
       <c r="I43" s="52"/>
       <c r="J43" s="52"/>
       <c r="K43" s="52" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="L43" s="52" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="M43" s="52" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="N43" s="52"/>
       <c r="O43" s="52"/>
@@ -9166,35 +9167,35 @@
     <row r="44" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B44" s="17"/>
       <c r="D44" s="18" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="E44" s="18" t="s">
         <v>116</v>
       </c>
       <c r="F44" s="18" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="G44" s="18" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="H44" s="18" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="I44" s="18" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="J44" s="18"/>
       <c r="K44" s="18" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="L44" s="18" t="s">
         <v>124</v>
       </c>
       <c r="M44" s="18" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="N44" s="18" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="O44" s="18"/>
       <c r="P44" s="18"/>
@@ -9215,7 +9216,7 @@
         <v>22</v>
       </c>
       <c r="F45" s="57" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="G45" s="41" t="s">
         <v>347</v>
@@ -9227,7 +9228,7 @@
         <v>62</v>
       </c>
       <c r="J45" s="41" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="K45" s="41" t="s">
         <v>307</v>
@@ -9255,35 +9256,35 @@
     <row r="46" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B46" s="22"/>
       <c r="D46" s="24" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="E46" s="24" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="F46" s="24" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="G46" s="24" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="H46" s="24" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="I46" s="24" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="J46" s="24"/>
       <c r="K46" s="24" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="L46" s="24" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="M46" s="24" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="N46" s="24" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="O46" s="24"/>
       <c r="P46" s="24"/>
@@ -9299,20 +9300,20 @@
         <v>129</v>
       </c>
       <c r="E47" s="52" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="F47" s="52" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="G47" s="52" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="H47" s="52"/>
       <c r="I47" s="52" t="s">
+        <v>673</v>
+      </c>
+      <c r="J47" s="52" t="s">
         <v>674</v>
-      </c>
-      <c r="J47" s="52" t="s">
-        <v>675</v>
       </c>
       <c r="K47" s="52"/>
       <c r="L47" s="52"/>
@@ -9330,37 +9331,37 @@
         <v>129</v>
       </c>
       <c r="E48" s="18" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="F48" s="18" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="G48" s="18" t="s">
+        <v>672</v>
+      </c>
+      <c r="H48" s="18" t="s">
+        <v>531</v>
+      </c>
+      <c r="I48" s="18" t="s">
         <v>673</v>
       </c>
-      <c r="H48" s="18" t="s">
-        <v>532</v>
-      </c>
-      <c r="I48" s="18" t="s">
+      <c r="J48" s="18" t="s">
         <v>674</v>
       </c>
-      <c r="J48" s="18" t="s">
-        <v>675</v>
-      </c>
       <c r="K48" s="18" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="L48" s="18" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="M48" s="18" t="s">
         <v>140</v>
       </c>
       <c r="N48" s="18" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="O48" s="18" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="P48" s="18"/>
       <c r="Q48" s="18"/>
@@ -9422,40 +9423,40 @@
     <row r="50" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B50" s="22"/>
       <c r="D50" s="24" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="E50" s="24" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="F50" s="24" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="G50" s="24" t="s">
+        <v>705</v>
+      </c>
+      <c r="H50" s="24" t="s">
+        <v>532</v>
+      </c>
+      <c r="I50" s="24" t="s">
         <v>706</v>
       </c>
-      <c r="H50" s="24" t="s">
-        <v>533</v>
-      </c>
-      <c r="I50" s="24" t="s">
+      <c r="J50" s="24" t="s">
         <v>707</v>
       </c>
-      <c r="J50" s="24" t="s">
-        <v>708</v>
-      </c>
       <c r="K50" s="24" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="L50" s="24" t="s">
+        <v>576</v>
+      </c>
+      <c r="M50" s="24" t="s">
         <v>577</v>
       </c>
-      <c r="M50" s="24" t="s">
-        <v>578</v>
-      </c>
       <c r="N50" s="24" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="O50" s="24" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="P50" s="24"/>
       <c r="Q50" s="24"/>
@@ -9467,7 +9468,7 @@
       <c r="B51" s="12"/>
       <c r="C51" s="34"/>
       <c r="D51" s="52" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="E51" s="52"/>
       <c r="F51" s="52"/>
@@ -9478,7 +9479,7 @@
       <c r="K51" s="52"/>
       <c r="L51" s="52"/>
       <c r="M51" s="52" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="N51" s="52" t="s">
         <v>137</v>
@@ -9492,32 +9493,32 @@
     <row r="52" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B52" s="17"/>
       <c r="D52" s="18" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="E52" s="18" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="F52" s="18" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="G52" s="18" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="H52" s="18" t="s">
         <v>135</v>
       </c>
       <c r="I52" s="18"/>
       <c r="J52" s="18" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="K52" s="18" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="L52" s="18" t="s">
         <v>134</v>
       </c>
       <c r="M52" s="18" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="N52" s="18" t="s">
         <v>137</v>
@@ -9550,7 +9551,7 @@
         <v>58</v>
       </c>
       <c r="I53" s="41" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="J53" s="41" t="s">
         <v>253</v>
@@ -9581,35 +9582,35 @@
     <row r="54" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B54" s="22"/>
       <c r="D54" s="24" t="s">
+        <v>708</v>
+      </c>
+      <c r="E54" s="24" t="s">
+        <v>581</v>
+      </c>
+      <c r="F54" s="24" t="s">
+        <v>521</v>
+      </c>
+      <c r="G54" s="24" t="s">
+        <v>583</v>
+      </c>
+      <c r="H54" s="24" t="s">
         <v>709</v>
-      </c>
-      <c r="E54" s="24" t="s">
-        <v>582</v>
-      </c>
-      <c r="F54" s="24" t="s">
-        <v>522</v>
-      </c>
-      <c r="G54" s="24" t="s">
-        <v>584</v>
-      </c>
-      <c r="H54" s="24" t="s">
-        <v>710</v>
       </c>
       <c r="I54" s="24"/>
       <c r="J54" s="24" t="s">
+        <v>585</v>
+      </c>
+      <c r="K54" s="24" t="s">
+        <v>583</v>
+      </c>
+      <c r="L54" s="24" t="s">
         <v>586</v>
       </c>
-      <c r="K54" s="24" t="s">
-        <v>584</v>
-      </c>
-      <c r="L54" s="24" t="s">
-        <v>587</v>
-      </c>
       <c r="M54" s="24" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="N54" s="24" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="O54" s="24"/>
       <c r="P54" s="24"/>
@@ -9622,24 +9623,24 @@
       <c r="B55" s="12"/>
       <c r="C55" s="34"/>
       <c r="D55" s="52" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="E55" s="52" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="F55" s="52"/>
       <c r="G55" s="52" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="H55" s="52" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="I55" s="52"/>
       <c r="J55" s="52"/>
       <c r="K55" s="52"/>
       <c r="L55" s="52"/>
       <c r="M55" s="52" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="N55" s="52"/>
       <c r="O55" s="52"/>
@@ -9651,41 +9652,41 @@
     <row r="56" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B56" s="17"/>
       <c r="D56" s="18" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="E56" s="18" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="F56" s="18" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="G56" s="18" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="H56" s="18" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="I56" s="18" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="J56" s="18" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="K56" s="18" t="s">
         <v>132</v>
       </c>
       <c r="L56" s="18"/>
       <c r="M56" s="18" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="N56" s="18" t="s">
         <v>142</v>
       </c>
       <c r="O56" s="18" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="P56" s="18" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="Q56" s="18"/>
       <c r="R56" s="18"/>
@@ -9722,7 +9723,7 @@
         <v>57</v>
       </c>
       <c r="L57" s="41" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="M57" s="41" t="s">
         <v>239</v>
@@ -9748,41 +9749,41 @@
     <row r="58" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B58" s="22"/>
       <c r="D58" s="24" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="E58" s="24" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="F58" s="24" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="G58" s="24" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="H58" s="24" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="I58" s="24" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="J58" s="24" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="K58" s="24" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="L58" s="24"/>
       <c r="M58" s="24" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="N58" s="24" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="O58" s="24" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="P58" s="24" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="Q58" s="24"/>
       <c r="R58" s="24"/>
@@ -9794,19 +9795,19 @@
       <c r="C59" s="34"/>
       <c r="D59" s="52"/>
       <c r="E59" s="52" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="F59" s="52"/>
       <c r="G59" s="52"/>
       <c r="H59" s="52"/>
       <c r="I59" s="52"/>
       <c r="J59" s="52" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="K59" s="52"/>
       <c r="L59" s="52"/>
       <c r="M59" s="52" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="N59" s="52"/>
       <c r="O59" s="52"/>
@@ -9821,38 +9822,38 @@
         <v>125</v>
       </c>
       <c r="E60" s="18" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="F60" s="18" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="G60" s="18" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="H60" s="18" t="s">
         <v>132</v>
       </c>
       <c r="I60" s="18"/>
       <c r="J60" s="18" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="K60" s="18" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="L60" s="18" t="s">
         <v>134</v>
       </c>
       <c r="M60" s="18" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="N60" s="18" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="O60" s="18" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="P60" s="18" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="Q60" s="18"/>
       <c r="R60" s="18"/>
@@ -9880,7 +9881,7 @@
         <v>57</v>
       </c>
       <c r="I61" s="41" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="J61" s="41" t="s">
         <v>288</v>
@@ -9915,41 +9916,41 @@
     <row r="62" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B62" s="22"/>
       <c r="D62" s="24" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="E62" s="24" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="F62" s="24" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="G62" s="24" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H62" s="24" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="I62" s="24"/>
       <c r="J62" s="24" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="K62" s="24" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="L62" s="24" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="M62" s="24" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="N62" s="24" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="O62" s="24" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="P62" s="24" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="Q62" s="24"/>
       <c r="R62" s="24"/>
@@ -9961,7 +9962,7 @@
       <c r="C63" s="34"/>
       <c r="D63" s="52"/>
       <c r="E63" s="52" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="F63" s="52"/>
       <c r="G63" s="52"/>
@@ -9984,25 +9985,25 @@
         <v>138</v>
       </c>
       <c r="E64" s="18" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="F64" s="18" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="G64" s="18" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="H64" s="18" t="s">
         <v>129</v>
       </c>
       <c r="I64" s="18" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="J64" s="18" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="K64" s="18" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="L64" s="18"/>
       <c r="M64" s="18"/>
@@ -10060,28 +10061,28 @@
     <row r="66" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B66" s="22"/>
       <c r="D66" s="24" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="E66" s="24" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="F66" s="24" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="G66" s="24" t="s">
+        <v>602</v>
+      </c>
+      <c r="H66" s="24" t="s">
         <v>603</v>
       </c>
-      <c r="H66" s="24" t="s">
-        <v>604</v>
-      </c>
       <c r="I66" s="24" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="J66" s="24" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="K66" s="24" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="L66" s="24"/>
       <c r="M66" s="24"/>
@@ -10098,20 +10099,20 @@
       <c r="C67" s="34"/>
       <c r="D67" s="52"/>
       <c r="E67" s="52" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="F67" s="52"/>
       <c r="G67" s="52"/>
       <c r="H67" s="52"/>
       <c r="I67" s="52"/>
       <c r="J67" s="52" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="K67" s="52"/>
       <c r="L67" s="52"/>
       <c r="M67" s="52"/>
       <c r="N67" s="52" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="O67" s="52"/>
       <c r="P67" s="52"/>
@@ -10125,20 +10126,20 @@
         <v>125</v>
       </c>
       <c r="E68" s="18" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="F68" s="18" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="G68" s="18" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="H68" s="18" t="s">
         <v>132</v>
       </c>
       <c r="I68" s="18"/>
       <c r="J68" s="18" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="K68" s="18" t="s">
         <v>118</v>
@@ -10150,7 +10151,7 @@
         <v>127</v>
       </c>
       <c r="N68" s="18" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="O68" s="18"/>
       <c r="P68" s="18"/>
@@ -10180,7 +10181,7 @@
         <v>57</v>
       </c>
       <c r="I69" s="41" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="J69" s="41" t="s">
         <v>288</v>
@@ -10192,7 +10193,7 @@
         <v>43</v>
       </c>
       <c r="M69" s="41" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="N69" s="41" t="s">
         <v>270</v>
@@ -10211,35 +10212,35 @@
     <row r="70" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B70" s="22"/>
       <c r="D70" s="24" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="E70" s="24" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="F70" s="24" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="G70" s="24" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H70" s="24" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="I70" s="24"/>
       <c r="J70" s="24" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="K70" s="24" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="L70" s="24" t="s">
+        <v>608</v>
+      </c>
+      <c r="M70" s="24" t="s">
         <v>609</v>
       </c>
-      <c r="M70" s="24" t="s">
-        <v>610</v>
-      </c>
       <c r="N70" s="24" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="O70" s="24"/>
       <c r="P70" s="24"/>
@@ -10259,7 +10260,7 @@
       <c r="G71" s="52"/>
       <c r="H71" s="52"/>
       <c r="I71" s="52" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="J71" s="52"/>
       <c r="K71" s="52"/>
@@ -10278,28 +10279,28 @@
         <v>133</v>
       </c>
       <c r="E72" s="18" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="F72" s="18" t="s">
         <v>142</v>
       </c>
       <c r="G72" s="18" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="H72" s="18" t="s">
         <v>362</v>
       </c>
       <c r="I72" s="18" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="J72" s="18" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="K72" s="18" t="s">
         <v>116</v>
       </c>
       <c r="L72" s="18" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="M72" s="18"/>
       <c r="N72" s="18"/>
@@ -10331,7 +10332,7 @@
         <v>18</v>
       </c>
       <c r="I73" s="41" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="J73" s="41" t="s">
         <v>306</v>
@@ -10358,31 +10359,31 @@
     <row r="74" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B74" s="22"/>
       <c r="D74" s="24" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="E74" s="24" t="s">
+        <v>611</v>
+      </c>
+      <c r="F74" s="24" t="s">
+        <v>564</v>
+      </c>
+      <c r="G74" s="24" t="s">
+        <v>548</v>
+      </c>
+      <c r="H74" s="24" t="s">
         <v>612</v>
       </c>
-      <c r="F74" s="24" t="s">
-        <v>565</v>
-      </c>
-      <c r="G74" s="24" t="s">
-        <v>549</v>
-      </c>
-      <c r="H74" s="24" t="s">
-        <v>613</v>
-      </c>
       <c r="I74" s="24" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="J74" s="24" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="K74" s="24" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="L74" s="24" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="M74" s="24"/>
       <c r="N74" s="24"/>
@@ -10397,19 +10398,19 @@
       <c r="B75" s="12"/>
       <c r="C75" s="34"/>
       <c r="D75" s="52" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="E75" s="52"/>
       <c r="F75" s="52"/>
       <c r="G75" s="52"/>
       <c r="H75" s="52"/>
       <c r="I75" s="52" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="J75" s="52"/>
       <c r="K75" s="52"/>
       <c r="L75" s="52" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="M75" s="52"/>
       <c r="N75" s="52"/>
@@ -10422,25 +10423,25 @@
     <row r="76" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B76" s="17"/>
       <c r="D76" s="18" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="E76" s="18" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="F76" s="18" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="G76" s="18" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H76" s="18" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="I76" s="18" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="J76" s="18" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="K76" s="18" t="s">
         <v>122</v>
@@ -10469,7 +10470,7 @@
         <v>326</v>
       </c>
       <c r="F77" s="41" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="G77" s="41" t="s">
         <v>287</v>
@@ -10505,31 +10506,31 @@
     <row r="78" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B78" s="22"/>
       <c r="D78" s="24" t="s">
+        <v>700</v>
+      </c>
+      <c r="E78" s="24" t="s">
+        <v>508</v>
+      </c>
+      <c r="F78" s="24" t="s">
+        <v>510</v>
+      </c>
+      <c r="G78" s="24" t="s">
+        <v>504</v>
+      </c>
+      <c r="H78" s="24" t="s">
+        <v>556</v>
+      </c>
+      <c r="I78" s="24" t="s">
+        <v>692</v>
+      </c>
+      <c r="J78" s="24" t="s">
+        <v>558</v>
+      </c>
+      <c r="K78" s="24" t="s">
+        <v>559</v>
+      </c>
+      <c r="L78" s="24" t="s">
         <v>701</v>
-      </c>
-      <c r="E78" s="24" t="s">
-        <v>509</v>
-      </c>
-      <c r="F78" s="24" t="s">
-        <v>511</v>
-      </c>
-      <c r="G78" s="24" t="s">
-        <v>505</v>
-      </c>
-      <c r="H78" s="24" t="s">
-        <v>557</v>
-      </c>
-      <c r="I78" s="24" t="s">
-        <v>693</v>
-      </c>
-      <c r="J78" s="24" t="s">
-        <v>559</v>
-      </c>
-      <c r="K78" s="24" t="s">
-        <v>560</v>
-      </c>
-      <c r="L78" s="24" t="s">
-        <v>702</v>
       </c>
       <c r="M78" s="24"/>
       <c r="N78" s="24"/>
@@ -10545,18 +10546,18 @@
       <c r="C79" s="34"/>
       <c r="D79" s="52"/>
       <c r="E79" s="52" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="F79" s="52"/>
       <c r="G79" s="52"/>
       <c r="H79" s="52"/>
       <c r="I79" s="52" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="J79" s="52"/>
       <c r="K79" s="52"/>
       <c r="L79" s="52" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="M79" s="52"/>
       <c r="N79" s="52"/>
@@ -10569,31 +10570,31 @@
     <row r="80" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B80" s="17"/>
       <c r="D80" s="18" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="E80" s="18" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="F80" s="18" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="G80" s="18" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H80" s="18" t="s">
         <v>142</v>
       </c>
       <c r="I80" s="18" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="J80" s="18" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="K80" s="18" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="L80" s="18" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="M80" s="18"/>
       <c r="N80" s="18"/>
@@ -10652,31 +10653,31 @@
     <row r="82" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B82" s="22"/>
       <c r="D82" s="24" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="E82" s="24" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="F82" s="24" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="G82" s="24" t="s">
+        <v>563</v>
+      </c>
+      <c r="H82" s="24" t="s">
         <v>564</v>
       </c>
-      <c r="H82" s="24" t="s">
-        <v>565</v>
-      </c>
       <c r="I82" s="24" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="J82" s="24" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="K82" s="24" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="L82" s="24" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="M82" s="24"/>
       <c r="N82" s="24"/>
@@ -10691,26 +10692,26 @@
       <c r="B83" s="12"/>
       <c r="C83" s="34"/>
       <c r="D83" s="52" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="E83" s="52" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="F83" s="52" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="G83" s="52"/>
       <c r="H83" s="52"/>
       <c r="I83" s="52"/>
       <c r="J83" s="52"/>
       <c r="K83" s="52" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="L83" s="52" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="M83" s="52" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="N83" s="52"/>
       <c r="O83" s="52"/>
@@ -10722,35 +10723,35 @@
     <row r="84" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B84" s="17"/>
       <c r="D84" s="18" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="E84" s="18" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="F84" s="18" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="G84" s="18" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="H84" s="18" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="I84" s="18" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="J84" s="18"/>
       <c r="K84" s="18" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="L84" s="18" t="s">
         <v>124</v>
       </c>
       <c r="M84" s="18" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="N84" s="18" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="O84" s="18"/>
       <c r="P84" s="18"/>
@@ -10771,7 +10772,7 @@
         <v>22</v>
       </c>
       <c r="F85" s="57" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="G85" s="41" t="s">
         <v>347</v>
@@ -10783,7 +10784,7 @@
         <v>62</v>
       </c>
       <c r="J85" s="41" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="K85" s="41" t="s">
         <v>307</v>
@@ -10815,35 +10816,35 @@
     <row r="86" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B86" s="22"/>
       <c r="D86" s="24" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="E86" s="24" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="F86" s="24" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="G86" s="24" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="H86" s="24" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="I86" s="24" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="J86" s="24"/>
       <c r="K86" s="24" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="L86" s="24" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="M86" s="24" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="N86" s="24" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="O86" s="24"/>
       <c r="P86" s="24"/>
@@ -10859,14 +10860,14 @@
       <c r="E87" s="52"/>
       <c r="F87" s="52"/>
       <c r="G87" s="52" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="H87" s="52"/>
       <c r="I87" s="52" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="J87" s="52" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="K87" s="52"/>
       <c r="L87" s="52"/>
@@ -10884,37 +10885,37 @@
         <v>129</v>
       </c>
       <c r="E88" s="18" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="F88" s="18" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="G88" s="18" t="s">
+        <v>672</v>
+      </c>
+      <c r="H88" s="18" t="s">
+        <v>531</v>
+      </c>
+      <c r="I88" s="18" t="s">
         <v>673</v>
       </c>
-      <c r="H88" s="18" t="s">
-        <v>532</v>
-      </c>
-      <c r="I88" s="18" t="s">
+      <c r="J88" s="18" t="s">
         <v>674</v>
       </c>
-      <c r="J88" s="18" t="s">
-        <v>675</v>
-      </c>
       <c r="K88" s="18" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="L88" s="18" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="M88" s="18" t="s">
         <v>140</v>
       </c>
       <c r="N88" s="18" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="O88" s="18" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="P88" s="18"/>
       <c r="Q88" s="18"/>
@@ -10976,40 +10977,40 @@
     <row r="90" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B90" s="22"/>
       <c r="D90" s="24" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="E90" s="24" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="F90" s="24" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="G90" s="24" t="s">
+        <v>705</v>
+      </c>
+      <c r="H90" s="24" t="s">
+        <v>532</v>
+      </c>
+      <c r="I90" s="24" t="s">
         <v>706</v>
       </c>
-      <c r="H90" s="24" t="s">
-        <v>533</v>
-      </c>
-      <c r="I90" s="24" t="s">
+      <c r="J90" s="24" t="s">
         <v>707</v>
       </c>
-      <c r="J90" s="24" t="s">
-        <v>708</v>
-      </c>
       <c r="K90" s="24" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="L90" s="24" t="s">
+        <v>576</v>
+      </c>
+      <c r="M90" s="24" t="s">
         <v>577</v>
       </c>
-      <c r="M90" s="24" t="s">
-        <v>578</v>
-      </c>
       <c r="N90" s="24" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="O90" s="24" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="P90" s="24"/>
       <c r="Q90" s="24"/>
@@ -11030,10 +11031,10 @@
       <c r="K91" s="52"/>
       <c r="L91" s="52"/>
       <c r="M91" s="52" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="N91" s="52" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="O91" s="52"/>
       <c r="P91" s="52"/>
@@ -11044,32 +11045,32 @@
     <row r="92" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B92" s="17"/>
       <c r="D92" s="18" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="E92" s="18" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="F92" s="18" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="G92" s="18" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="H92" s="18" t="s">
         <v>135</v>
       </c>
       <c r="I92" s="18"/>
       <c r="J92" s="18" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="K92" s="18" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="L92" s="18" t="s">
         <v>134</v>
       </c>
       <c r="M92" s="18" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="N92" s="18" t="s">
         <v>137</v>
@@ -11102,7 +11103,7 @@
         <v>58</v>
       </c>
       <c r="I93" s="41" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="J93" s="41" t="s">
         <v>253</v>
@@ -11133,35 +11134,35 @@
     <row r="94" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B94" s="22"/>
       <c r="D94" s="24" t="s">
+        <v>708</v>
+      </c>
+      <c r="E94" s="24" t="s">
+        <v>581</v>
+      </c>
+      <c r="F94" s="24" t="s">
+        <v>521</v>
+      </c>
+      <c r="G94" s="24" t="s">
+        <v>583</v>
+      </c>
+      <c r="H94" s="24" t="s">
         <v>709</v>
-      </c>
-      <c r="E94" s="24" t="s">
-        <v>582</v>
-      </c>
-      <c r="F94" s="24" t="s">
-        <v>522</v>
-      </c>
-      <c r="G94" s="24" t="s">
-        <v>584</v>
-      </c>
-      <c r="H94" s="24" t="s">
-        <v>710</v>
       </c>
       <c r="I94" s="24"/>
       <c r="J94" s="24" t="s">
+        <v>585</v>
+      </c>
+      <c r="K94" s="24" t="s">
+        <v>583</v>
+      </c>
+      <c r="L94" s="24" t="s">
         <v>586</v>
       </c>
-      <c r="K94" s="24" t="s">
-        <v>584</v>
-      </c>
-      <c r="L94" s="24" t="s">
-        <v>587</v>
-      </c>
       <c r="M94" s="24" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="N94" s="24" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="O94" s="24"/>
       <c r="P94" s="24"/>
@@ -11174,24 +11175,24 @@
       <c r="B95" s="12"/>
       <c r="C95" s="34"/>
       <c r="D95" s="52" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="E95" s="52" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="F95" s="52"/>
       <c r="G95" s="52" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="H95" s="52" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="I95" s="52"/>
       <c r="J95" s="52"/>
       <c r="K95" s="52"/>
       <c r="L95" s="52"/>
       <c r="M95" s="52" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="N95" s="52"/>
       <c r="O95" s="52"/>
@@ -11203,41 +11204,41 @@
     <row r="96" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B96" s="17"/>
       <c r="D96" s="18" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="E96" s="18" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="F96" s="18" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="G96" s="18" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="H96" s="18" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="I96" s="18" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="J96" s="18" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="K96" s="18" t="s">
         <v>132</v>
       </c>
       <c r="L96" s="18"/>
       <c r="M96" s="18" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="N96" s="18" t="s">
         <v>142</v>
       </c>
       <c r="O96" s="18" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="P96" s="18" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="Q96" s="18"/>
       <c r="R96" s="18"/>
@@ -11274,7 +11275,7 @@
         <v>57</v>
       </c>
       <c r="L97" s="41" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="M97" s="41" t="s">
         <v>239</v>
@@ -11300,41 +11301,41 @@
     <row r="98" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B98" s="22"/>
       <c r="D98" s="24" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="E98" s="24" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="F98" s="24" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="G98" s="24" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="H98" s="24" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="I98" s="24" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="J98" s="24" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="K98" s="24" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="L98" s="24"/>
       <c r="M98" s="24" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="N98" s="24" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="O98" s="24" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="P98" s="24" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="Q98" s="24"/>
       <c r="R98" s="24"/>
@@ -11346,19 +11347,19 @@
       <c r="C99" s="34"/>
       <c r="D99" s="52"/>
       <c r="E99" s="52" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="F99" s="52"/>
       <c r="G99" s="52"/>
       <c r="H99" s="52"/>
       <c r="I99" s="52"/>
       <c r="J99" s="52" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="K99" s="52"/>
       <c r="L99" s="52"/>
       <c r="M99" s="52" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="N99" s="52"/>
       <c r="O99" s="52"/>
@@ -11373,38 +11374,38 @@
         <v>125</v>
       </c>
       <c r="E100" s="18" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="F100" s="18" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="G100" s="18" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="H100" s="18" t="s">
         <v>132</v>
       </c>
       <c r="I100" s="18"/>
       <c r="J100" s="18" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="K100" s="18" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="L100" s="18" t="s">
         <v>134</v>
       </c>
       <c r="M100" s="18" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="N100" s="18" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="O100" s="18" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="P100" s="18" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="Q100" s="18"/>
       <c r="R100" s="18"/>
@@ -11432,7 +11433,7 @@
         <v>57</v>
       </c>
       <c r="I101" s="41" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="J101" s="41" t="s">
         <v>288</v>
@@ -11467,41 +11468,41 @@
     <row r="102" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B102" s="22"/>
       <c r="D102" s="24" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="E102" s="24" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="F102" s="24" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="G102" s="24" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H102" s="24" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="I102" s="24"/>
       <c r="J102" s="24" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="K102" s="24" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="L102" s="24" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="M102" s="24" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="N102" s="24" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="O102" s="24" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="P102" s="24" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="Q102" s="24"/>
       <c r="R102" s="24"/>
@@ -11513,7 +11514,7 @@
       <c r="C103" s="34"/>
       <c r="D103" s="52"/>
       <c r="E103" s="52" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="F103" s="52"/>
       <c r="G103" s="52"/>
@@ -11536,25 +11537,25 @@
         <v>138</v>
       </c>
       <c r="E104" s="18" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="F104" s="18" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="G104" s="18" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="H104" s="18" t="s">
         <v>129</v>
       </c>
       <c r="I104" s="18" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="J104" s="18" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="K104" s="18" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="L104" s="18"/>
       <c r="M104" s="18"/>
@@ -11612,28 +11613,28 @@
     <row r="106" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B106" s="22"/>
       <c r="D106" s="24" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="E106" s="24" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="F106" s="24" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="G106" s="24" t="s">
+        <v>602</v>
+      </c>
+      <c r="H106" s="24" t="s">
         <v>603</v>
       </c>
-      <c r="H106" s="24" t="s">
-        <v>604</v>
-      </c>
       <c r="I106" s="24" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="J106" s="24" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="K106" s="24" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="L106" s="24"/>
       <c r="M106" s="24"/>
@@ -11659,7 +11660,7 @@
       <c r="L107" s="52"/>
       <c r="M107" s="52"/>
       <c r="N107" s="52" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="O107" s="52"/>
       <c r="P107" s="52"/>
@@ -11673,20 +11674,20 @@
         <v>125</v>
       </c>
       <c r="E108" s="18" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="F108" s="18" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="G108" s="18" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="H108" s="18" t="s">
         <v>132</v>
       </c>
       <c r="I108" s="18"/>
       <c r="J108" s="18" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="K108" s="18" t="s">
         <v>118</v>
@@ -11698,7 +11699,7 @@
         <v>127</v>
       </c>
       <c r="N108" s="18" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="O108" s="18"/>
       <c r="P108" s="18"/>
@@ -11728,7 +11729,7 @@
         <v>57</v>
       </c>
       <c r="I109" s="41" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="J109" s="41" t="s">
         <v>288</v>
@@ -11740,7 +11741,7 @@
         <v>43</v>
       </c>
       <c r="M109" s="41" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="N109" s="41" t="s">
         <v>270</v>
@@ -11759,35 +11760,35 @@
     <row r="110" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B110" s="22"/>
       <c r="D110" s="24" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="E110" s="24" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="F110" s="24" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="G110" s="24" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H110" s="24" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="I110" s="24"/>
       <c r="J110" s="24" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="K110" s="24" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="L110" s="24" t="s">
+        <v>608</v>
+      </c>
+      <c r="M110" s="24" t="s">
         <v>609</v>
       </c>
-      <c r="M110" s="24" t="s">
-        <v>610</v>
-      </c>
       <c r="N110" s="24" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="O110" s="24"/>
       <c r="P110" s="24"/>
@@ -11807,7 +11808,7 @@
       <c r="G111" s="52"/>
       <c r="H111" s="52"/>
       <c r="I111" s="52" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="J111" s="52"/>
       <c r="K111" s="52"/>
@@ -11832,22 +11833,22 @@
         <v>142</v>
       </c>
       <c r="G112" s="18" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="H112" s="18" t="s">
         <v>362</v>
       </c>
       <c r="I112" s="18" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="J112" s="18" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="K112" s="18" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="L112" s="18" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="M112" s="18"/>
       <c r="N112" s="18"/>
@@ -11879,7 +11880,7 @@
         <v>18</v>
       </c>
       <c r="I113" s="41" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="J113" s="41" t="s">
         <v>306</v>
@@ -11906,31 +11907,31 @@
     <row r="114" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B114" s="22"/>
       <c r="D114" s="24" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="E114" s="24" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="F114" s="24" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="G114" s="24" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="H114" s="24" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="I114" s="24" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="J114" s="24" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="K114" s="24" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="L114" s="24" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="M114" s="24"/>
       <c r="N114" s="24"/>
@@ -11955,7 +11956,7 @@
       <c r="L115" s="52"/>
       <c r="M115" s="52"/>
       <c r="N115" s="52" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="O115" s="52"/>
       <c r="P115" s="52"/>
@@ -11969,38 +11970,38 @@
         <v>125</v>
       </c>
       <c r="E116" s="18" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="F116" s="18" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="G116" s="18" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="H116" s="18" t="s">
         <v>132</v>
       </c>
       <c r="I116" s="18"/>
       <c r="J116" s="18" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="K116" s="18" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="L116" s="18" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="M116" s="18" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="N116" s="18" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="O116" s="18" t="s">
         <v>139</v>
       </c>
       <c r="P116" s="18" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="Q116" s="18"/>
       <c r="R116" s="18"/>
@@ -12028,7 +12029,7 @@
         <v>57</v>
       </c>
       <c r="I117" s="41" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="J117" s="41" t="s">
         <v>274</v>
@@ -12063,41 +12064,41 @@
     <row r="118" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B118" s="22"/>
       <c r="D118" s="24" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="E118" s="24" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="F118" s="24" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="G118" s="24" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H118" s="24" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="I118" s="24"/>
       <c r="J118" s="24" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="K118" s="24" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="L118" s="24" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="M118" s="24" t="s">
+        <v>620</v>
+      </c>
+      <c r="N118" s="24" t="s">
+        <v>747</v>
+      </c>
+      <c r="O118" s="24" t="s">
         <v>621</v>
       </c>
-      <c r="N118" s="24" t="s">
-        <v>748</v>
-      </c>
-      <c r="O118" s="24" t="s">
-        <v>622</v>
-      </c>
       <c r="P118" s="24" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="Q118" s="24"/>
       <c r="R118" s="24"/>
@@ -12109,19 +12110,19 @@
       <c r="C119" s="34"/>
       <c r="D119" s="52"/>
       <c r="E119" s="52" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="F119" s="52"/>
       <c r="G119" s="52" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="H119" s="52" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="I119" s="52"/>
       <c r="J119" s="52"/>
       <c r="K119" s="52" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="L119" s="52"/>
       <c r="M119" s="52"/>
@@ -12135,28 +12136,28 @@
     <row r="120" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B120" s="17"/>
       <c r="D120" s="18" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="E120" s="18" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="F120" s="18" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="G120" s="18" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="H120" s="18" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="I120" s="18" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="J120" s="18" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="K120" s="18" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="L120" s="18"/>
       <c r="M120" s="18"/>
@@ -12214,28 +12215,28 @@
     <row r="122" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B122" s="22"/>
       <c r="D122" s="24" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="E122" s="24" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="F122" s="24" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="G122" s="24" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="H122" s="24" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="I122" s="24" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="J122" s="24" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="K122" s="24" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="L122" s="24"/>
       <c r="M122" s="24"/>
@@ -12261,7 +12262,7 @@
       <c r="L123" s="52"/>
       <c r="M123" s="52"/>
       <c r="N123" s="52" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="O123" s="52"/>
       <c r="P123" s="52"/>
@@ -12275,13 +12276,13 @@
         <v>125</v>
       </c>
       <c r="E124" s="18" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="F124" s="18" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="G124" s="18" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="H124" s="18" t="s">
         <v>132</v>
@@ -12291,16 +12292,16 @@
         <v>142</v>
       </c>
       <c r="K124" s="18" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="L124" s="18" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="M124" s="18" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="N124" s="18" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="O124" s="18"/>
       <c r="P124" s="18"/>
@@ -12330,7 +12331,7 @@
         <v>57</v>
       </c>
       <c r="I125" s="41" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="J125" s="41" t="s">
         <v>23</v>
@@ -12361,35 +12362,35 @@
     <row r="126" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B126" s="22"/>
       <c r="D126" s="24" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="E126" s="24" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="F126" s="24" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="G126" s="24" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H126" s="24" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="I126" s="24"/>
       <c r="J126" s="24" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="K126" s="24" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="L126" s="24" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="M126" s="24" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="N126" s="24" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="O126" s="24"/>
       <c r="P126" s="24"/>
@@ -12405,7 +12406,7 @@
       <c r="E127" s="14"/>
       <c r="F127" s="14"/>
       <c r="G127" s="14" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="H127" s="14"/>
       <c r="I127" s="14" t="s">
@@ -12414,7 +12415,7 @@
       <c r="J127" s="14"/>
       <c r="K127" s="14"/>
       <c r="L127" s="14" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="M127" s="14"/>
       <c r="N127" s="14"/>
@@ -12427,7 +12428,7 @@
     <row r="128" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B128" s="17"/>
       <c r="D128" s="18" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="E128" s="18" t="s">
         <v>142</v>
@@ -12436,22 +12437,22 @@
         <v>128</v>
       </c>
       <c r="G128" s="18" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="H128" s="18" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="I128" s="18" t="s">
         <v>126</v>
       </c>
       <c r="J128" s="18" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="K128" s="18" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="L128" s="18" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="M128" s="18"/>
       <c r="N128" s="18"/>
@@ -12510,31 +12511,31 @@
     <row r="130" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B130" s="22"/>
       <c r="D130" s="24" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="E130" s="24" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="F130" s="24" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="G130" s="24" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="H130" s="24" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="I130" s="24" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="J130" s="24" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="K130" s="24" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="L130" s="24" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="M130" s="24"/>
       <c r="N130" s="24"/>
@@ -12571,16 +12572,16 @@
         <v>125</v>
       </c>
       <c r="E132" s="18" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="F132" s="18" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="G132" s="18" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="H132" s="18" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="I132" s="18"/>
       <c r="J132" s="18" t="s">
@@ -12590,13 +12591,13 @@
         <v>114</v>
       </c>
       <c r="L132" s="18" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="M132" s="18" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="N132" s="18" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="O132" s="18"/>
       <c r="P132" s="18"/>
@@ -12626,7 +12627,7 @@
         <v>311</v>
       </c>
       <c r="I133" s="41" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="J133" s="41" t="s">
         <v>52</v>
@@ -12657,35 +12658,35 @@
     <row r="134" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B134" s="22"/>
       <c r="D134" s="24" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="E134" s="24" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="F134" s="24" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="G134" s="24" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H134" s="24" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="I134" s="24"/>
       <c r="J134" s="24" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="K134" s="24" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="L134" s="24" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="M134" s="24" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="N134" s="24" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="O134" s="24"/>
       <c r="P134" s="24"/>
@@ -12720,28 +12721,28 @@
         <v>130</v>
       </c>
       <c r="E136" s="18" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="F136" s="18" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="G136" s="18" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H136" s="18" t="s">
         <v>363</v>
       </c>
       <c r="I136" s="18" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="J136" s="18" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="K136" s="18" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="L136" s="18" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="M136" s="18"/>
       <c r="N136" s="18"/>
@@ -12800,31 +12801,31 @@
     <row r="138" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B138" s="22"/>
       <c r="D138" s="24" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="E138" s="24" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="F138" s="24" t="s">
+        <v>649</v>
+      </c>
+      <c r="G138" s="24" t="s">
+        <v>563</v>
+      </c>
+      <c r="H138" s="24" t="s">
         <v>650</v>
       </c>
-      <c r="G138" s="24" t="s">
-        <v>564</v>
-      </c>
-      <c r="H138" s="24" t="s">
-        <v>651</v>
-      </c>
       <c r="I138" s="24" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="J138" s="24" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="K138" s="24" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="L138" s="24" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="M138" s="24"/>
       <c r="N138" s="24"/>
@@ -19718,11 +19719,11 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D99:R99">
-    <cfRule type="expression" dxfId="55" priority="29">
+    <cfRule type="expression" dxfId="55" priority="30">
+      <formula>"'= TRUE(顯示注音輸入)"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="54" priority="29">
       <formula>顯示注音輸入</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="54" priority="30">
-      <formula>"'= TRUE(顯示注音輸入)"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D103:R103">
@@ -19742,11 +19743,11 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D111:R111">
-    <cfRule type="expression" dxfId="49" priority="24">
+    <cfRule type="expression" dxfId="49" priority="23">
+      <formula>顯示注音輸入</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="48" priority="24">
       <formula>"'= TRUE(顯示注音輸入)"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="48" priority="23">
-      <formula>顯示注音輸入</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D115:R115">
@@ -19774,11 +19775,11 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D127:R127 D131:R131 D135:R135 D139:R139 D143:R143 D147:R147 D151:R151 D155:R155 D159:R159 D163:R163">
-    <cfRule type="expression" dxfId="41" priority="161">
+    <cfRule type="expression" dxfId="41" priority="162">
+      <formula>"'= TRUE(顯示注音輸入)"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="40" priority="161">
       <formula>顯示注音輸入</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="40" priority="162">
-      <formula>"'= TRUE(顯示注音輸入)"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D167:R167 D171:R171 D175:R175 D179:R179 D183:R183 D187:R187 D191:R191 D195:R195 D199:R199">
@@ -19814,19 +19815,19 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D247:R247 D251:R251 D255:R255 D259:R259 D263:R263 D267:R267 D271:R271 D275:R275 D279:R279">
-    <cfRule type="expression" dxfId="31" priority="110">
+    <cfRule type="expression" dxfId="31" priority="109">
+      <formula>顯示注音輸入</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="30" priority="110">
       <formula>"'= TRUE(顯示注音輸入)"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="30" priority="109">
-      <formula>顯示注音輸入</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D283:R283">
-    <cfRule type="expression" dxfId="29" priority="108">
+    <cfRule type="expression" dxfId="29" priority="107">
+      <formula>顯示注音輸入</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="28" priority="108">
       <formula>"'= TRUE(顯示注音輸入)"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="28" priority="107">
-      <formula>顯示注音輸入</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D287:R287">
@@ -19838,11 +19839,11 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D291:R291 D295:R295 D299:R299 D303:R303 D307:R307 D311:R311 D315:R315 D319:R319 D323:R323">
-    <cfRule type="expression" dxfId="25" priority="104">
+    <cfRule type="expression" dxfId="25" priority="103">
+      <formula>顯示注音輸入</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="24" priority="104">
       <formula>"'= TRUE(顯示注音輸入)"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="24" priority="103">
-      <formula>顯示注音輸入</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D327:R327">
@@ -19854,19 +19855,19 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D331:R331">
-    <cfRule type="expression" dxfId="21" priority="100">
+    <cfRule type="expression" dxfId="21" priority="99">
+      <formula>顯示注音輸入</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="20" priority="100">
       <formula>"'= TRUE(顯示注音輸入)"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="20" priority="99">
-      <formula>顯示注音輸入</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D335:R335 D339:R339 D343:R343 D347:R347 D351:R351 D355:R355 D359:R359 D363:R363 D367:R367">
-    <cfRule type="expression" dxfId="19" priority="98">
+    <cfRule type="expression" dxfId="19" priority="97">
+      <formula>顯示注音輸入</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="18" priority="98">
       <formula>"'= TRUE(顯示注音輸入)"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="18" priority="97">
-      <formula>顯示注音輸入</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D371:R371">
@@ -19902,19 +19903,19 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D419:R419">
-    <cfRule type="expression" dxfId="9" priority="88">
+    <cfRule type="expression" dxfId="9" priority="87">
+      <formula>顯示注音輸入</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="8" priority="88">
       <formula>"'= TRUE(顯示注音輸入)"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="8" priority="87">
-      <formula>顯示注音輸入</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D423:R423 D427:R427 D431:R431 D435:R435 D439:R439 D443:R443 D447:R447 D451:R451 D455:R455">
-    <cfRule type="expression" dxfId="7" priority="85">
+    <cfRule type="expression" dxfId="7" priority="86">
+      <formula>"'= TRUE(顯示注音輸入)"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="6" priority="85">
       <formula>顯示注音輸入</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="6" priority="86">
-      <formula>"'= TRUE(顯示注音輸入)"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D459:R459">
